--- a/PC移行時チェックリスト.xlsx
+++ b/PC移行時チェックリスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20204A28-D69A-4B4E-B388-08C7F55D726C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F567E414-44D0-4284-B1A5-55DCE16BFE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32385" yWindow="1230" windowWidth="32385" windowHeight="40695" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32385" yWindow="1230" windowWidth="32385" windowHeight="40695" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="セットアップ事項" sheetId="21" r:id="rId1"/>
@@ -8663,7 +8663,7 @@
       <alignment vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9186,9 +9186,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
@@ -70903,7 +70900,7 @@
       <c r="C85" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="D85" s="174" t="s">
+      <c r="D85" s="36" t="s">
         <v>1537</v>
       </c>
       <c r="E85" s="36" t="s">
@@ -70930,7 +70927,7 @@
       <c r="C86" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="D86" s="174" t="s">
+      <c r="D86" s="36" t="s">
         <v>1538</v>
       </c>
       <c r="E86" s="36" t="s">
@@ -70957,7 +70954,7 @@
       <c r="C87" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="174" t="s">
+      <c r="D87" s="36" t="s">
         <v>1539</v>
       </c>
       <c r="E87" s="36" t="s">
@@ -70984,7 +70981,7 @@
       <c r="C88" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="D88" s="174" t="s">
+      <c r="D88" s="36" t="s">
         <v>1540</v>
       </c>
       <c r="E88" s="36" t="s">

--- a/PC移行時チェックリスト.xlsx
+++ b/PC移行時チェックリスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADEC590-4622-4B44-BEA2-74D8E21F022A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813D983B-90DA-4EF4-8248-1E2B41FAD87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32385" yWindow="1230" windowWidth="32385" windowHeight="40695" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32385" yWindow="1230" windowWidth="32385" windowHeight="40695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="セットアップ事項" sheetId="21" r:id="rId1"/>
@@ -8583,7 +8583,7 @@
       <alignment vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9105,12 +9105,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -69461,7 +69455,7 @@
       <c r="B30" s="41" t="s">
         <v>1117</v>
       </c>
-      <c r="C30" s="174" t="s">
+      <c r="C30" s="36" t="s">
         <v>1515</v>
       </c>
       <c r="D30" s="133" t="s">
@@ -69488,14 +69482,14 @@
       <c r="B31" s="41" t="s">
         <v>1117</v>
       </c>
-      <c r="C31" s="174" t="s">
+      <c r="C31" s="36" t="s">
         <v>1519</v>
       </c>
-      <c r="D31" s="174" t="str">
+      <c r="D31" s="36" t="str">
         <f>$C31</f>
         <v>\cp -rf ~/_dotfiles/.bashrc ./.</v>
       </c>
-      <c r="E31" s="174" t="str">
+      <c r="E31" s="36" t="str">
         <f t="shared" ref="E31:E48" si="2">$C31</f>
         <v>\cp -rf ~/_dotfiles/.bashrc ./.</v>
       </c>
@@ -69517,14 +69511,14 @@
       <c r="B32" s="41" t="s">
         <v>1117</v>
       </c>
-      <c r="C32" s="174" t="s">
+      <c r="C32" s="36" t="s">
         <v>1520</v>
       </c>
-      <c r="D32" s="174" t="str">
+      <c r="D32" s="36" t="str">
         <f>$C32</f>
         <v>touch ~/_dotfiles/.bashrc_env</v>
       </c>
-      <c r="E32" s="174" t="str">
+      <c r="E32" s="36" t="str">
         <f t="shared" si="2"/>
         <v>touch ~/_dotfiles/.bashrc_env</v>
       </c>
@@ -69550,7 +69544,7 @@
         <v>1496</v>
       </c>
       <c r="D33" s="36" t="str">
-        <f t="shared" ref="D33:E48" si="3">$C33</f>
+        <f t="shared" ref="D33:D48" si="3">$C33</f>
         <v>createhardlink ~/_dotfiles/.bashrc              .bashrc</v>
       </c>
       <c r="E33" s="36" t="str">
@@ -73559,16 +73553,9 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="B2"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="3.83203125" defaultRowHeight="11.25"/>
-  <cols>
-    <col min="1" max="16384" width="3.83203125" style="175"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:2">
-      <c r="B2"/>
-    </row>
-  </sheetData>
+  <sheetData/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/PC移行時チェックリスト.xlsx
+++ b/PC移行時チェックリスト.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813D983B-90DA-4EF4-8248-1E2B41FAD87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE1E07F-841B-4CAA-9CEF-B4B414B6CB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32385" yWindow="1230" windowWidth="32385" windowHeight="40695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32385" yWindow="1230" windowWidth="32385" windowHeight="40695" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="セットアップ事項" sheetId="21" r:id="rId1"/>
@@ -34,12 +34,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">linux環境構築!#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">shortcut!$A$9:$AJ$220</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">symlink!$A$11:$L$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">symlink!$A$11:$L$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">セットアップ事項!$A$2:$M$83</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">linux環境構築!$A$6:$H$102</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">shortcut!$A$8:$AI$220</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">shortcut設定!$A$1:$O$38</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">symlink!$A$10:$L$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">symlink!$A$10:$L$66</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">セットアップ事項!$A$1:$H$83</definedName>
     <definedName name="カテゴリ" localSheetId="7">[1]shortcut設定!$F$13:$F$37</definedName>
     <definedName name="カテゴリ">shortcut設定!$F$13:$F$37</definedName>
@@ -238,7 +238,7 @@
     <author>Tatsuya Endo</author>
   </authors>
   <commentList>
-    <comment ref="F17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -256,7 +256,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+    <comment ref="F45" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -274,7 +274,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+    <comment ref="F53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -291,7 +291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
+    <comment ref="F54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -308,7 +308,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
+    <comment ref="B55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -757,7 +757,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6285" uniqueCount="1521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6294" uniqueCount="1524">
   <si>
     <t>○</t>
   </si>
@@ -7764,9 +7764,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>C:\Users\draem\.config\wezterm\wezterm.lua</t>
-  </si>
-  <si>
     <t>C:\codes\wezterm\wezterm.lua</t>
   </si>
   <si>
@@ -8021,6 +8018,21 @@
   <si>
     <t>touch ~/_dotfiles/.bashrc_env</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>%USERPROFILE%\.config\wezterm\wezterm.lua</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>%USERPROFILE%\_root\39_other\.ssh</t>
+  </si>
+  <si>
+    <t>.ssh</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>%USERPROFILE%\.ssh</t>
+    <phoneticPr fontId="7"/>
   </si>
 </sst>
 </file>
@@ -9358,6 +9370,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
@@ -44907,19 +44920,19 @@
     </row>
     <row r="140" spans="1:36">
       <c r="A140" s="9" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B140" s="9" t="s">
         <v>1475</v>
       </c>
-      <c r="B140" s="9" t="s">
+      <c r="C140" s="9" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D140" s="15" t="s">
         <v>1476</v>
       </c>
-      <c r="C140" s="9" t="s">
-        <v>1474</v>
-      </c>
-      <c r="D140" s="15" t="s">
-        <v>1477</v>
-      </c>
       <c r="E140" s="26" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="F140" s="15" t="s">
         <v>0</v>
@@ -47343,7 +47356,7 @@
         <v>867</v>
       </c>
       <c r="C150" s="9" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="D150" s="15" t="s">
         <v>40</v>
@@ -53571,13 +53584,13 @@
     </row>
     <row r="176" spans="1:36">
       <c r="A176" s="9" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="B176" s="9" t="s">
         <v>827</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="D176" s="15" t="s">
         <v>40</v>
@@ -57415,13 +57428,13 @@
     </row>
     <row r="192" spans="1:36">
       <c r="A192" s="9" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B192" s="9" t="s">
         <v>1483</v>
       </c>
-      <c r="B192" s="9" t="s">
-        <v>1484</v>
-      </c>
       <c r="C192" s="9" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="D192" s="15" t="s">
         <v>40</v>
@@ -57442,7 +57455,7 @@
         <v>66</v>
       </c>
       <c r="J192" s="15" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="K192" s="15" t="s">
         <v>66</v>
@@ -59593,7 +59606,7 @@
         <v>66</v>
       </c>
       <c r="J201" s="15" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="K201" s="15" t="s">
         <v>66</v>
@@ -59832,7 +59845,7 @@
         <v>66</v>
       </c>
       <c r="J202" s="15" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="K202" s="15" t="s">
         <v>66</v>
@@ -60044,13 +60057,13 @@
     </row>
     <row r="203" spans="1:36">
       <c r="A203" s="9" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B203" s="9" t="s">
         <v>1479</v>
       </c>
-      <c r="B203" s="9" t="s">
-        <v>1480</v>
-      </c>
       <c r="C203" s="9" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="D203" s="15" t="s">
         <v>40</v>
@@ -60071,7 +60084,7 @@
         <v>66</v>
       </c>
       <c r="J203" s="15" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="K203" s="15" t="s">
         <v>66</v>
@@ -60337,7 +60350,7 @@
         <v>66</v>
       </c>
       <c r="J204" s="15" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="K204" s="15" t="s">
         <v>66</v>
@@ -60549,19 +60562,19 @@
     </row>
     <row r="205" spans="1:36">
       <c r="A205" s="9" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B205" s="9" t="s">
         <v>1467</v>
       </c>
-      <c r="B205" s="9" t="s">
+      <c r="C205" s="9" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D205" s="15" t="s">
         <v>1468</v>
       </c>
-      <c r="C205" s="9" t="s">
-        <v>1466</v>
-      </c>
-      <c r="D205" s="15" t="s">
-        <v>1469</v>
-      </c>
       <c r="E205" s="26" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="F205" s="15" t="s">
         <v>0</v>
@@ -60573,31 +60586,31 @@
         <v>529</v>
       </c>
       <c r="I205" s="15" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J205" s="15" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="K205" s="15" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="L205" s="93" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="M205" s="94" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="N205" s="15" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="O205" s="26" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="P205" s="157" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="Q205" s="26" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="R205" s="9" t="str">
         <f t="shared" si="31"/>
@@ -60808,13 +60821,13 @@
     </row>
     <row r="206" spans="1:36">
       <c r="A206" s="9" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B206" s="9" t="s">
         <v>1512</v>
       </c>
-      <c r="B206" s="9" t="s">
-        <v>1513</v>
-      </c>
       <c r="C206" s="9" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D206" s="15" t="s">
         <v>40</v>
@@ -61047,13 +61060,13 @@
     </row>
     <row r="207" spans="1:36">
       <c r="A207" s="9" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="C207" s="9" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D207" s="15" t="s">
         <v>40</v>
@@ -61074,7 +61087,7 @@
         <v>40</v>
       </c>
       <c r="J207" s="15" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="K207" s="15" t="s">
         <v>40</v>
@@ -61286,13 +61299,13 @@
     </row>
     <row r="208" spans="1:36">
       <c r="A208" s="9" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C208" s="9" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="D208" s="15" t="s">
         <v>1449</v>
@@ -61313,7 +61326,7 @@
         <v>946</v>
       </c>
       <c r="J208" s="15" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="K208" s="15" t="s">
         <v>1449</v>
@@ -65711,7 +65724,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A2:M84"/>
+  <dimension ref="A2:M85"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -65866,7 +65879,7 @@
         <v>rename "C:\root" "root_bak"</v>
       </c>
       <c r="L12" s="1" t="str">
-        <f t="shared" ref="L12:L50" si="0">IF(
+        <f t="shared" ref="L12:L51" si="0">IF(
   F12="○",
   "mklink "&amp;IF(
     E12="folder",
@@ -65923,7 +65936,7 @@
         <v>robocopy "C:\codes" "%USERPROFILE%\_root\30_tool" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K13" s="1" t="str">
-        <f t="shared" ref="K13:K65" si="1">IF(F13="○","rename """&amp;G13&amp;""" """&amp;RIGHT(G13,LEN(G13)-FIND("●",SUBSTITUTE(G13,"\","●",LEN(G13)-LEN(SUBSTITUTE(G13,"\","")))))&amp;"_bak""","")</f>
+        <f t="shared" ref="K13:K66" si="1">IF(F13="○","rename """&amp;G13&amp;""" """&amp;RIGHT(G13,LEN(G13)-FIND("●",SUBSTITUTE(G13,"\","●",LEN(G13)-LEN(SUBSTITUTE(G13,"\","")))))&amp;"_bak""","")</f>
         <v>rename "C:\codes" "codes_bak"</v>
       </c>
       <c r="L13" s="1" t="str">
@@ -66041,17 +66054,17 @@
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="6" t="s">
-        <v>1154</v>
+      <c r="A16" s="1" t="s">
+        <v>1153</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>1522</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>17</v>
@@ -66060,14 +66073,14 @@
         <v>0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>15</v>
+        <v>1523</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>5</v>
+        <v>1521</v>
       </c>
       <c r="I16" s="1" t="str">
         <f>IF($F16="○","mkdir """&amp;[2]!getdirpath($H16)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vba\excel"</v>
+        <v>mkdir "%USERPROFILE%\_root\39_other"</v>
       </c>
       <c r="J16" s="1" t="str">
         <f>IF(
@@ -66079,18 +66092,26 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\Microsoft\AddIns" "C:\codes\vba\excel\AddIns" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\.ssh" "%USERPROFILE%\_root\39_other\.ssh" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K16" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\AppData\Roaming\Microsoft\AddIns" "AddIns_bak"</v>
+        <f t="shared" ref="K16" si="2">IF(F16="○","rename """&amp;G16&amp;""" """&amp;RIGHT(G16,LEN(G16)-FIND("●",SUBSTITUTE(G16,"\","●",LEN(G16)-LEN(SUBSTITUTE(G16,"\","")))))&amp;"_bak""","")</f>
+        <v>rename "%USERPROFILE%\.ssh" ".ssh_bak"</v>
       </c>
       <c r="L16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Microsoft\AddIns" "C:\codes\vba\excel\AddIns"</v>
+        <f t="shared" ref="L16" si="3">IF(
+  F16="○",
+  "mklink "&amp;IF(
+    E16="folder",
+    "/d ",
+    ""
+  )&amp;""""&amp;G16&amp;""" """&amp;H16&amp;"""",
+  ""
+)</f>
+        <v>mklink /d "%USERPROFILE%\.ssh" "%USERPROFILE%\_root\39_other\.ssh"</v>
       </c>
       <c r="M16" t="s">
-        <v>1298</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -66098,31 +66119,31 @@
         <v>1154</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>28</v>
+        <v>155</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>28</v>
+        <v>155</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G17" s="97" t="s">
-        <v>963</v>
-      </c>
-      <c r="H17" s="97" t="s">
-        <v>964</v>
-      </c>
-      <c r="I17" s="97" t="str">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="1" t="str">
         <f>IF($F17="○","mkdir """&amp;[2]!getdirpath($H17)&amp;"""","")</f>
-        <v/>
-      </c>
-      <c r="J17" s="97" t="str">
+        <v>mkdir "C:\codes\vba\excel"</v>
+      </c>
+      <c r="J17" s="1" t="str">
         <f>IF(
   $F17="○",
   IF(
@@ -66132,15 +66153,15 @@
   ),
   ""
 )</f>
-        <v/>
-      </c>
-      <c r="K17" s="97" t="str">
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\Microsoft\AddIns" "C:\codes\vba\excel\AddIns" /MIR /XD "System Volume Information"</v>
+      </c>
+      <c r="K17" s="1" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L17" s="97" t="str">
+        <v>rename "%USERPROFILE%\AppData\Roaming\Microsoft\AddIns" "AddIns_bak"</v>
+      </c>
+      <c r="L17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Microsoft\AddIns" "C:\codes\vba\excel\AddIns"</v>
       </c>
       <c r="M17" t="s">
         <v>1298</v>
@@ -66151,31 +66172,31 @@
         <v>1154</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>155</v>
+        <v>28</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>155</v>
+        <v>28</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I18" s="1" t="str">
+        <v>28</v>
+      </c>
+      <c r="G18" s="97" t="s">
+        <v>963</v>
+      </c>
+      <c r="H18" s="97" t="s">
+        <v>964</v>
+      </c>
+      <c r="I18" s="97" t="str">
         <f>IF($F18="○","mkdir """&amp;[2]!getdirpath($H18)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vba\outlook"</v>
-      </c>
-      <c r="J18" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J18" s="97" t="str">
         <f>IF(
   $F18="○",
   IF(
@@ -66185,26 +66206,26 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\Microsoft\Outlook" "C:\codes\vba\outlook\AddIns" /MIR /XD "System Volume Information"</v>
-      </c>
-      <c r="K18" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K18" s="97" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\AppData\Roaming\Microsoft\Outlook" "Outlook_bak"</v>
-      </c>
-      <c r="L18" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L18" s="97" t="str">
         <f t="shared" si="0"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Microsoft\Outlook" "C:\codes\vba\outlook\AddIns"</v>
+        <v/>
       </c>
       <c r="M18" t="s">
         <v>1298</v>
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="1" t="s">
-        <v>163</v>
+      <c r="A19" s="6" t="s">
+        <v>1154</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1155</v>
+        <v>37</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>155</v>
@@ -66213,20 +66234,20 @@
         <v>155</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>966</v>
+        <v>27</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>164</v>
+        <v>26</v>
       </c>
       <c r="I19" s="1" t="str">
         <f>IF($F19="○","mkdir """&amp;[2]!getdirpath($H19)&amp;"""","")</f>
-        <v>mkdir "C:\other\template"</v>
+        <v>mkdir "C:\codes\vba\outlook"</v>
       </c>
       <c r="J19" s="1" t="str">
         <f>IF(
@@ -66238,26 +66259,26 @@
   ),
   ""
 )</f>
-        <v>copy "%MYDIRPATH_DOCUMENTS%\個人用図形\fav.vssx" "C:\other\template"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\Microsoft\Outlook" "C:\codes\vba\outlook\AddIns" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K19" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%MYDIRPATH_DOCUMENTS%\個人用図形\fav.vssx" "fav.vssx_bak"</v>
+        <v>rename "%USERPROFILE%\AppData\Roaming\Microsoft\Outlook" "Outlook_bak"</v>
       </c>
       <c r="L19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink "%MYDIRPATH_DOCUMENTS%\個人用図形\fav.vssx" "C:\other\template\fav.vssx"</v>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Microsoft\Outlook" "C:\codes\vba\outlook\AddIns"</v>
       </c>
       <c r="M19" t="s">
         <v>1298</v>
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="6" t="s">
-        <v>887</v>
+      <c r="A20" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>38</v>
+        <v>1155</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>155</v>
@@ -66266,20 +66287,20 @@
         <v>155</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G20" s="172" t="s">
-        <v>154</v>
+      <c r="G20" s="1" t="s">
+        <v>966</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>9</v>
+        <v>164</v>
       </c>
       <c r="I20" s="1" t="str">
         <f>IF($F20="○","mkdir """&amp;[2]!getdirpath($H20)&amp;"""","")</f>
-        <v>mkdir "C:\codes"</v>
+        <v>mkdir "C:\other\template"</v>
       </c>
       <c r="J20" s="1" t="str">
         <f>IF(
@@ -66291,15 +66312,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "C:\prg_exe\Hidemaru\macro" "C:\codes\hmac" /MIR /XD "System Volume Information"</v>
+        <v>copy "%MYDIRPATH_DOCUMENTS%\個人用図形\fav.vssx" "C:\other\template"</v>
       </c>
       <c r="K20" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "C:\prg_exe\Hidemaru\macro" "macro_bak"</v>
+        <v>rename "%MYDIRPATH_DOCUMENTS%\個人用図形\fav.vssx" "fav.vssx_bak"</v>
       </c>
       <c r="L20" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink /d "C:\prg_exe\Hidemaru\macro" "C:\codes\hmac"</v>
+        <v>mklink "%MYDIRPATH_DOCUMENTS%\個人用図形\fav.vssx" "C:\other\template\fav.vssx"</v>
       </c>
       <c r="M20" t="s">
         <v>1298</v>
@@ -66310,7 +66331,7 @@
         <v>887</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>155</v>
@@ -66325,10 +66346,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="172" t="s">
-        <v>892</v>
+        <v>154</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>893</v>
+        <v>9</v>
       </c>
       <c r="I21" s="1" t="str">
         <f>IF($F21="○","mkdir """&amp;[2]!getdirpath($H21)&amp;"""","")</f>
@@ -66344,15 +66365,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "C:\prg_exe\Hidemaru\setting" "C:\codes\hidemaru" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "C:\prg_exe\Hidemaru\macro" "C:\codes\hmac" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K21" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "C:\prg_exe\Hidemaru\setting" "setting_bak"</v>
+        <v>rename "C:\prg_exe\Hidemaru\macro" "macro_bak"</v>
       </c>
       <c r="L21" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink /d "C:\prg_exe\Hidemaru\setting" "C:\codes\hidemaru"</v>
+        <v>mklink /d "C:\prg_exe\Hidemaru\macro" "C:\codes\hmac"</v>
       </c>
       <c r="M21" t="s">
         <v>1298</v>
@@ -66363,7 +66384,7 @@
         <v>887</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>891</v>
+        <v>39</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>155</v>
@@ -66372,20 +66393,20 @@
         <v>155</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>12</v>
+      <c r="G22" s="172" t="s">
+        <v>892</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>3</v>
+        <v>893</v>
       </c>
       <c r="I22" s="1" t="str">
         <f>IF($F22="○","mkdir """&amp;[2]!getdirpath($H22)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim"</v>
+        <v>mkdir "C:\codes"</v>
       </c>
       <c r="J22" s="1" t="str">
         <f>IF(
@@ -66397,15 +66418,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_gvimrc" "C:\codes\vim"</v>
+        <v>robocopy "C:\prg_exe\Hidemaru\setting" "C:\codes\hidemaru" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K22" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "C:\prg_exe\Vim\_gvimrc" "_gvimrc_bak"</v>
+        <v>rename "C:\prg_exe\Hidemaru\setting" "setting_bak"</v>
       </c>
       <c r="L22" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink "C:\prg_exe\Vim\_gvimrc" "C:\codes\vim\_gvimrc"</v>
+        <v>mklink /d "C:\prg_exe\Hidemaru\setting" "C:\codes\hidemaru"</v>
       </c>
       <c r="M22" t="s">
         <v>1298</v>
@@ -66416,7 +66437,7 @@
         <v>887</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>155</v>
@@ -66431,10 +66452,10 @@
         <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I23" s="1" t="str">
         <f>IF($F23="○","mkdir """&amp;[2]!getdirpath($H23)&amp;"""","")</f>
@@ -66450,15 +66471,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_vimrc" "C:\codes\vim"</v>
+        <v>copy "C:\prg_exe\Vim\_gvimrc" "C:\codes\vim"</v>
       </c>
       <c r="K23" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "C:\prg_exe\Vim\_vimrc" "_vimrc_bak"</v>
+        <v>rename "C:\prg_exe\Vim\_gvimrc" "_gvimrc_bak"</v>
       </c>
       <c r="L23" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink "C:\prg_exe\Vim\_vimrc" "C:\codes\vim\_vimrc"</v>
+        <v>mklink "C:\prg_exe\Vim\_gvimrc" "C:\codes\vim\_gvimrc"</v>
       </c>
       <c r="M23" t="s">
         <v>1298</v>
@@ -66469,7 +66490,7 @@
         <v>887</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>155</v>
@@ -66483,15 +66504,15 @@
       <c r="F24" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G24" s="172" t="s">
-        <v>907</v>
+      <c r="G24" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>906</v>
+        <v>4</v>
       </c>
       <c r="I24" s="1" t="str">
         <f>IF($F24="○","mkdir """&amp;[2]!getdirpath($H24)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim\_plugins_user\bufferlist.vim\plugin"</v>
+        <v>mkdir "C:\codes\vim"</v>
       </c>
       <c r="J24" s="1" t="str">
         <f>IF(
@@ -66503,15 +66524,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_plugins_user\bufferlist.vim\plugin\bufferlist.vim" "C:\codes\vim\_plugins_user\bufferlist.vim\plugin"</v>
+        <v>copy "C:\prg_exe\Vim\_vimrc" "C:\codes\vim"</v>
       </c>
       <c r="K24" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "C:\prg_exe\Vim\_plugins_user\bufferlist.vim\plugin\bufferlist.vim" "bufferlist.vim_bak"</v>
+        <v>rename "C:\prg_exe\Vim\_vimrc" "_vimrc_bak"</v>
       </c>
       <c r="L24" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink "C:\prg_exe\Vim\_plugins_user\bufferlist.vim\plugin\bufferlist.vim" "C:\codes\vim\_plugins_user\bufferlist.vim\plugin\bufferlist.vim"</v>
+        <v>mklink "C:\prg_exe\Vim\_vimrc" "C:\codes\vim\_vimrc"</v>
       </c>
       <c r="M24" t="s">
         <v>1298</v>
@@ -66522,7 +66543,7 @@
         <v>887</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>155</v>
@@ -66537,14 +66558,14 @@
         <v>0</v>
       </c>
       <c r="G25" s="172" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>6</v>
+        <v>906</v>
       </c>
       <c r="I25" s="1" t="str">
         <f>IF($F25="○","mkdir """&amp;[2]!getdirpath($H25)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim\_plugins_user\FavEx\plugin"</v>
+        <v>mkdir "C:\codes\vim\_plugins_user\bufferlist.vim\plugin"</v>
       </c>
       <c r="J25" s="1" t="str">
         <f>IF(
@@ -66556,15 +66577,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_plugins_user\FavEx\plugin\favex.vim" "C:\codes\vim\_plugins_user\FavEx\plugin"</v>
+        <v>copy "C:\prg_exe\Vim\_plugins_user\bufferlist.vim\plugin\bufferlist.vim" "C:\codes\vim\_plugins_user\bufferlist.vim\plugin"</v>
       </c>
       <c r="K25" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "C:\prg_exe\Vim\_plugins_user\FavEx\plugin\favex.vim" "favex.vim_bak"</v>
+        <v>rename "C:\prg_exe\Vim\_plugins_user\bufferlist.vim\plugin\bufferlist.vim" "bufferlist.vim_bak"</v>
       </c>
       <c r="L25" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink "C:\prg_exe\Vim\_plugins_user\FavEx\plugin\favex.vim" "C:\codes\vim\_plugins_user\FavEx\plugin\favex.vim"</v>
+        <v>mklink "C:\prg_exe\Vim\_plugins_user\bufferlist.vim\plugin\bufferlist.vim" "C:\codes\vim\_plugins_user\bufferlist.vim\plugin\bufferlist.vim"</v>
       </c>
       <c r="M25" t="s">
         <v>1298</v>
@@ -66575,7 +66596,7 @@
         <v>887</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>155</v>
@@ -66590,14 +66611,14 @@
         <v>0</v>
       </c>
       <c r="G26" s="172" t="s">
-        <v>14</v>
+        <v>908</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I26" s="1" t="str">
         <f>IF($F26="○","mkdir """&amp;[2]!getdirpath($H26)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim\_plugins_user\FavEx"</v>
+        <v>mkdir "C:\codes\vim\_plugins_user\FavEx\plugin"</v>
       </c>
       <c r="J26" s="1" t="str">
         <f>IF(
@@ -66609,15 +66630,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_plugins_user\FavEx\favlist" "C:\codes\vim\_plugins_user\FavEx"</v>
+        <v>copy "C:\prg_exe\Vim\_plugins_user\FavEx\plugin\favex.vim" "C:\codes\vim\_plugins_user\FavEx\plugin"</v>
       </c>
       <c r="K26" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "C:\prg_exe\Vim\_plugins_user\FavEx\favlist" "favlist_bak"</v>
+        <v>rename "C:\prg_exe\Vim\_plugins_user\FavEx\plugin\favex.vim" "favex.vim_bak"</v>
       </c>
       <c r="L26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink "C:\prg_exe\Vim\_plugins_user\FavEx\favlist" "C:\codes\vim\_plugins_user\FavEx\favlist"</v>
+        <v>mklink "C:\prg_exe\Vim\_plugins_user\FavEx\plugin\favex.vim" "C:\codes\vim\_plugins_user\FavEx\plugin\favex.vim"</v>
       </c>
       <c r="M26" t="s">
         <v>1298</v>
@@ -66628,7 +66649,7 @@
         <v>887</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>155</v>
@@ -66643,14 +66664,14 @@
         <v>0</v>
       </c>
       <c r="G27" s="172" t="s">
-        <v>909</v>
+        <v>14</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I27" s="1" t="str">
         <f>IF($F27="○","mkdir """&amp;[2]!getdirpath($H27)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim\_plugins_user\jellybeans.vim\colors"</v>
+        <v>mkdir "C:\codes\vim\_plugins_user\FavEx"</v>
       </c>
       <c r="J27" s="1" t="str">
         <f>IF(
@@ -66662,15 +66683,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_plugins_user\jellybeans.vim\colors\jellybeans.vim" "C:\codes\vim\_plugins_user\jellybeans.vim\colors"</v>
+        <v>copy "C:\prg_exe\Vim\_plugins_user\FavEx\favlist" "C:\codes\vim\_plugins_user\FavEx"</v>
       </c>
       <c r="K27" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "C:\prg_exe\Vim\_plugins_user\jellybeans.vim\colors\jellybeans.vim" "jellybeans.vim_bak"</v>
+        <v>rename "C:\prg_exe\Vim\_plugins_user\FavEx\favlist" "favlist_bak"</v>
       </c>
       <c r="L27" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink "C:\prg_exe\Vim\_plugins_user\jellybeans.vim\colors\jellybeans.vim" "C:\codes\vim\_plugins_user\jellybeans.vim\colors\jellybeans.vim"</v>
+        <v>mklink "C:\prg_exe\Vim\_plugins_user\FavEx\favlist" "C:\codes\vim\_plugins_user\FavEx\favlist"</v>
       </c>
       <c r="M27" t="s">
         <v>1298</v>
@@ -66681,7 +66702,7 @@
         <v>887</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>155</v>
@@ -66696,14 +66717,14 @@
         <v>0</v>
       </c>
       <c r="G28" s="172" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I28" s="1" t="str">
         <f>IF($F28="○","mkdir """&amp;[2]!getdirpath($H28)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim\_plugins_user\mark.vim\plugin"</v>
+        <v>mkdir "C:\codes\vim\_plugins_user\jellybeans.vim\colors"</v>
       </c>
       <c r="J28" s="1" t="str">
         <f>IF(
@@ -66715,15 +66736,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_plugins_user\mark.vim\plugin\mark.vim" "C:\codes\vim\_plugins_user\mark.vim\plugin"</v>
+        <v>copy "C:\prg_exe\Vim\_plugins_user\jellybeans.vim\colors\jellybeans.vim" "C:\codes\vim\_plugins_user\jellybeans.vim\colors"</v>
       </c>
       <c r="K28" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "C:\prg_exe\Vim\_plugins_user\mark.vim\plugin\mark.vim" "mark.vim_bak"</v>
+        <v>rename "C:\prg_exe\Vim\_plugins_user\jellybeans.vim\colors\jellybeans.vim" "jellybeans.vim_bak"</v>
       </c>
       <c r="L28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink "C:\prg_exe\Vim\_plugins_user\mark.vim\plugin\mark.vim" "C:\codes\vim\_plugins_user\mark.vim\plugin\mark.vim"</v>
+        <v>mklink "C:\prg_exe\Vim\_plugins_user\jellybeans.vim\colors\jellybeans.vim" "C:\codes\vim\_plugins_user\jellybeans.vim\colors\jellybeans.vim"</v>
       </c>
       <c r="M28" t="s">
         <v>1298</v>
@@ -66734,7 +66755,7 @@
         <v>887</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>155</v>
@@ -66749,14 +66770,14 @@
         <v>0</v>
       </c>
       <c r="G29" s="172" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I29" s="1" t="str">
         <f>IF($F29="○","mkdir """&amp;[2]!getdirpath($H29)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim\_plugins_user\qfixapp\autoload"</v>
+        <v>mkdir "C:\codes\vim\_plugins_user\mark.vim\plugin"</v>
       </c>
       <c r="J29" s="1" t="str">
         <f>IF(
@@ -66768,15 +66789,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_plugins_user\qfixapp\autoload\qfixgrep.vim" "C:\codes\vim\_plugins_user\qfixapp\autoload"</v>
+        <v>copy "C:\prg_exe\Vim\_plugins_user\mark.vim\plugin\mark.vim" "C:\codes\vim\_plugins_user\mark.vim\plugin"</v>
       </c>
       <c r="K29" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "C:\prg_exe\Vim\_plugins_user\qfixapp\autoload\qfixgrep.vim" "qfixgrep.vim_bak"</v>
+        <v>rename "C:\prg_exe\Vim\_plugins_user\mark.vim\plugin\mark.vim" "mark.vim_bak"</v>
       </c>
       <c r="L29" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink "C:\prg_exe\Vim\_plugins_user\qfixapp\autoload\qfixgrep.vim" "C:\codes\vim\_plugins_user\qfixapp\autoload\qfixgrep.vim"</v>
+        <v>mklink "C:\prg_exe\Vim\_plugins_user\mark.vim\plugin\mark.vim" "C:\codes\vim\_plugins_user\mark.vim\plugin\mark.vim"</v>
       </c>
       <c r="M29" t="s">
         <v>1298</v>
@@ -66787,7 +66808,7 @@
         <v>887</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>888</v>
+        <v>899</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>155</v>
@@ -66802,14 +66823,14 @@
         <v>0</v>
       </c>
       <c r="G30" s="172" t="s">
-        <v>158</v>
+        <v>911</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
       <c r="I30" s="1" t="str">
         <f>IF($F30="○","mkdir """&amp;[2]!getdirpath($H30)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vscode"</v>
+        <v>mkdir "C:\codes\vim\_plugins_user\qfixapp\autoload"</v>
       </c>
       <c r="J30" s="1" t="str">
         <f>IF(
@@ -66821,15 +66842,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\VSCode\data\user-data\User\keybindings.json" "C:\codes\vscode"</v>
+        <v>copy "C:\prg_exe\Vim\_plugins_user\qfixapp\autoload\qfixgrep.vim" "C:\codes\vim\_plugins_user\qfixapp\autoload"</v>
       </c>
       <c r="K30" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "C:\prg_exe\VSCode\data\user-data\User\keybindings.json" "keybindings.json_bak"</v>
+        <v>rename "C:\prg_exe\Vim\_plugins_user\qfixapp\autoload\qfixgrep.vim" "qfixgrep.vim_bak"</v>
       </c>
       <c r="L30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink "C:\prg_exe\VSCode\data\user-data\User\keybindings.json" "C:\codes\vscode\keybindings.json"</v>
+        <v>mklink "C:\prg_exe\Vim\_plugins_user\qfixapp\autoload\qfixgrep.vim" "C:\codes\vim\_plugins_user\qfixapp\autoload\qfixgrep.vim"</v>
       </c>
       <c r="M30" t="s">
         <v>1298</v>
@@ -66840,7 +66861,7 @@
         <v>887</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>155</v>
@@ -66855,10 +66876,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="172" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I31" s="1" t="str">
         <f>IF($F31="○","mkdir """&amp;[2]!getdirpath($H31)&amp;"""","")</f>
@@ -66874,15 +66895,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\VSCode\data\user-data\User\settings.json" "C:\codes\vscode"</v>
+        <v>copy "C:\prg_exe\VSCode\data\user-data\User\keybindings.json" "C:\codes\vscode"</v>
       </c>
       <c r="K31" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "C:\prg_exe\VSCode\data\user-data\User\settings.json" "settings.json_bak"</v>
+        <v>rename "C:\prg_exe\VSCode\data\user-data\User\keybindings.json" "keybindings.json_bak"</v>
       </c>
       <c r="L31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink "C:\prg_exe\VSCode\data\user-data\User\settings.json" "C:\codes\vscode\settings.json"</v>
+        <v>mklink "C:\prg_exe\VSCode\data\user-data\User\keybindings.json" "C:\codes\vscode\keybindings.json"</v>
       </c>
       <c r="M31" t="s">
         <v>1298</v>
@@ -66893,7 +66914,7 @@
         <v>887</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>1140</v>
+        <v>889</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>155</v>
@@ -66908,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="172" t="s">
-        <v>1139</v>
+        <v>160</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>1138</v>
+        <v>161</v>
       </c>
       <c r="I32" s="1" t="str">
         <f>IF($F32="○","mkdir """&amp;[2]!getdirpath($H32)&amp;"""","")</f>
@@ -66927,23 +66948,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\VSCode\_update.ps1" "C:\codes\vscode"</v>
+        <v>copy "C:\prg_exe\VSCode\data\user-data\User\settings.json" "C:\codes\vscode"</v>
       </c>
       <c r="K32" s="1" t="str">
-        <f t="shared" ref="K32:K37" si="2">IF(F32="○","rename """&amp;G32&amp;""" """&amp;RIGHT(G32,LEN(G32)-FIND("●",SUBSTITUTE(G32,"\","●",LEN(G32)-LEN(SUBSTITUTE(G32,"\","")))))&amp;"_bak""","")</f>
-        <v>rename "C:\prg_exe\VSCode\_update.ps1" "_update.ps1_bak"</v>
+        <f t="shared" si="1"/>
+        <v>rename "C:\prg_exe\VSCode\data\user-data\User\settings.json" "settings.json_bak"</v>
       </c>
       <c r="L32" s="1" t="str">
-        <f t="shared" ref="L32:L37" si="3">IF(
-  F32="○",
-  "mklink "&amp;IF(
-    E32="folder",
-    "/d ",
-    ""
-  )&amp;""""&amp;G32&amp;""" """&amp;H32&amp;"""",
-  ""
-)</f>
-        <v>mklink "C:\prg_exe\VSCode\_update.ps1" "C:\codes\vscode\update.ps1"</v>
+        <f t="shared" si="0"/>
+        <v>mklink "C:\prg_exe\VSCode\data\user-data\User\settings.json" "C:\codes\vscode\settings.json"</v>
       </c>
       <c r="M32" t="s">
         <v>1298</v>
@@ -66954,13 +66967,13 @@
         <v>887</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>1152</v>
+        <v>1140</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>16</v>
@@ -66969,14 +66982,14 @@
         <v>0</v>
       </c>
       <c r="G33" s="172" t="s">
-        <v>1151</v>
+        <v>1139</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>1147</v>
+        <v>1138</v>
       </c>
       <c r="I33" s="1" t="str">
         <f>IF($F33="○","mkdir """&amp;[2]!getdirpath($H33)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vbs\tools\x-finder"</v>
+        <v>mkdir "C:\codes\vscode"</v>
       </c>
       <c r="J33" s="1" t="str">
         <f>IF(
@@ -66988,15 +67001,23 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\X-Finder\MergeToIniFromTabbak.vbs" "C:\codes\vbs\tools\x-finder"</v>
+        <v>copy "C:\prg_exe\VSCode\_update.ps1" "C:\codes\vscode"</v>
       </c>
       <c r="K33" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>rename "C:\prg_exe\X-Finder\MergeToIniFromTabbak.vbs" "MergeToIniFromTabbak.vbs_bak"</v>
+        <f t="shared" ref="K33:K38" si="4">IF(F33="○","rename """&amp;G33&amp;""" """&amp;RIGHT(G33,LEN(G33)-FIND("●",SUBSTITUTE(G33,"\","●",LEN(G33)-LEN(SUBSTITUTE(G33,"\","")))))&amp;"_bak""","")</f>
+        <v>rename "C:\prg_exe\VSCode\_update.ps1" "_update.ps1_bak"</v>
       </c>
       <c r="L33" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>mklink "C:\prg_exe\X-Finder\MergeToIniFromTabbak.vbs" "C:\codes\vbs\tools\x-finder\MergeToIniFromTabbak.vbs"</v>
+        <f t="shared" ref="L33:L38" si="5">IF(
+  F33="○",
+  "mklink "&amp;IF(
+    E33="folder",
+    "/d ",
+    ""
+  )&amp;""""&amp;G33&amp;""" """&amp;H33&amp;"""",
+  ""
+)</f>
+        <v>mklink "C:\prg_exe\VSCode\_update.ps1" "C:\codes\vscode\update.ps1"</v>
       </c>
       <c r="M33" t="s">
         <v>1298</v>
@@ -67007,7 +67028,7 @@
         <v>887</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>0</v>
@@ -67022,14 +67043,14 @@
         <v>0</v>
       </c>
       <c r="G34" s="172" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="I34" s="1" t="str">
         <f>IF($F34="○","mkdir """&amp;[2]!getdirpath($H34)&amp;"""","")</f>
-        <v>mkdir "C:\codes\bat\tools\x-finder"</v>
+        <v>mkdir "C:\codes\vbs\tools\x-finder"</v>
       </c>
       <c r="J34" s="1" t="str">
         <f>IF(
@@ -67041,15 +67062,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\X-Finder\BackupIniToTabbak.bat" "C:\codes\bat\tools\x-finder"</v>
+        <v>copy "C:\prg_exe\X-Finder\MergeToIniFromTabbak.vbs" "C:\codes\vbs\tools\x-finder"</v>
       </c>
       <c r="K34" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>rename "C:\prg_exe\X-Finder\BackupIniToTabbak.bat" "BackupIniToTabbak.bat_bak"</v>
+        <f t="shared" si="4"/>
+        <v>rename "C:\prg_exe\X-Finder\MergeToIniFromTabbak.vbs" "MergeToIniFromTabbak.vbs_bak"</v>
       </c>
       <c r="L34" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>mklink "C:\prg_exe\X-Finder\BackupIniToTabbak.bat" "C:\codes\bat\tools\x-finder\BackupIniToTabbak.bat"</v>
+        <f t="shared" si="5"/>
+        <v>mklink "C:\prg_exe\X-Finder\MergeToIniFromTabbak.vbs" "C:\codes\vbs\tools\x-finder\MergeToIniFromTabbak.vbs"</v>
       </c>
       <c r="M34" t="s">
         <v>1298</v>
@@ -67060,13 +67081,13 @@
         <v>887</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>886</v>
+        <v>1150</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>16</v>
@@ -67074,15 +67095,15 @@
       <c r="F35" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>1134</v>
+      <c r="G35" s="172" t="s">
+        <v>1149</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>153</v>
+        <v>1148</v>
       </c>
       <c r="I35" s="1" t="str">
         <f>IF($F35="○","mkdir """&amp;[2]!getdirpath($H35)&amp;"""","")</f>
-        <v>mkdir "C:\codes\winterm"</v>
+        <v>mkdir "C:\codes\bat\tools\x-finder"</v>
       </c>
       <c r="J35" s="1" t="str">
         <f>IF(
@@ -67094,15 +67115,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\WindowsTerminal\settings\settings.json" "C:\codes\winterm"</v>
+        <v>copy "C:\prg_exe\X-Finder\BackupIniToTabbak.bat" "C:\codes\bat\tools\x-finder"</v>
       </c>
       <c r="K35" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>rename "C:\prg_exe\WindowsTerminal\settings\settings.json" "settings.json_bak"</v>
+        <f t="shared" si="4"/>
+        <v>rename "C:\prg_exe\X-Finder\BackupIniToTabbak.bat" "BackupIniToTabbak.bat_bak"</v>
       </c>
       <c r="L35" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>mklink "C:\prg_exe\WindowsTerminal\settings\settings.json" "C:\codes\winterm\settings.json"</v>
+        <f t="shared" si="5"/>
+        <v>mklink "C:\prg_exe\X-Finder\BackupIniToTabbak.bat" "C:\codes\bat\tools\x-finder\BackupIniToTabbak.bat"</v>
       </c>
       <c r="M35" t="s">
         <v>1298</v>
@@ -67113,13 +67134,13 @@
         <v>887</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1161</v>
+        <v>886</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>320</v>
+        <v>155</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>321</v>
+        <v>155</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>16</v>
@@ -67127,15 +67148,15 @@
       <c r="F36" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G36" s="6" t="s">
-        <v>879</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>1163</v>
+      <c r="G36" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="I36" s="1" t="str">
         <f>IF($F36="○","mkdir """&amp;[2]!getdirpath($H36)&amp;"""","")</f>
-        <v>mkdir "C:\codes\git\setting_alluser"</v>
+        <v>mkdir "C:\codes\winterm"</v>
       </c>
       <c r="J36" s="1" t="str">
         <f>IF(
@@ -67147,15 +67168,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg\Git\etc\gitconfig" "C:\codes\git\setting_alluser"</v>
+        <v>copy "C:\prg_exe\WindowsTerminal\settings\settings.json" "C:\codes\winterm"</v>
       </c>
       <c r="K36" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>rename "C:\prg\Git\etc\gitconfig" "gitconfig_bak"</v>
+        <f t="shared" si="4"/>
+        <v>rename "C:\prg_exe\WindowsTerminal\settings\settings.json" "settings.json_bak"</v>
       </c>
       <c r="L36" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>mklink "C:\prg\Git\etc\gitconfig" "C:\codes\git\setting_alluser\gitconfig"</v>
+        <f t="shared" si="5"/>
+        <v>mklink "C:\prg_exe\WindowsTerminal\settings\settings.json" "C:\codes\winterm\settings.json"</v>
       </c>
       <c r="M36" t="s">
         <v>1298</v>
@@ -67166,7 +67187,7 @@
         <v>887</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>320</v>
@@ -67180,15 +67201,15 @@
       <c r="F37" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>881</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>1162</v>
+      <c r="G37" s="6" t="s">
+        <v>879</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>1163</v>
       </c>
       <c r="I37" s="1" t="str">
         <f>IF($F37="○","mkdir """&amp;[2]!getdirpath($H37)&amp;"""","")</f>
-        <v>mkdir "C:\codes\git\setting_myuser"</v>
+        <v>mkdir "C:\codes\git\setting_alluser"</v>
       </c>
       <c r="J37" s="1" t="str">
         <f>IF(
@@ -67200,15 +67221,15 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\.gitconfig" "C:\codes\git\setting_myuser"</v>
+        <v>copy "C:\prg\Git\etc\gitconfig" "C:\codes\git\setting_alluser"</v>
       </c>
       <c r="K37" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>rename "%USERPROFILE%\.gitconfig" ".gitconfig_bak"</v>
+        <f t="shared" si="4"/>
+        <v>rename "C:\prg\Git\etc\gitconfig" "gitconfig_bak"</v>
       </c>
       <c r="L37" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>mklink "%USERPROFILE%\.gitconfig" "C:\codes\git\setting_myuser\.gitconfig"</v>
+        <f t="shared" si="5"/>
+        <v>mklink "C:\prg\Git\etc\gitconfig" "C:\codes\git\setting_alluser\gitconfig"</v>
       </c>
       <c r="M37" t="s">
         <v>1298</v>
@@ -67219,13 +67240,13 @@
         <v>887</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1465</v>
+        <v>1160</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>155</v>
+        <v>320</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>155</v>
+        <v>321</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>16</v>
@@ -67234,14 +67255,14 @@
         <v>0</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>1463</v>
+        <v>881</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>1464</v>
+        <v>1162</v>
       </c>
       <c r="I38" s="1" t="str">
         <f>IF($F38="○","mkdir """&amp;[2]!getdirpath($H38)&amp;"""","")</f>
-        <v>mkdir "C:\codes\wezterm"</v>
+        <v>mkdir "C:\codes\git\setting_myuser"</v>
       </c>
       <c r="J38" s="1" t="str">
         <f>IF(
@@ -67253,56 +67274,48 @@
   ),
   ""
 )</f>
-        <v>copy "C:\Users\draem\.config\wezterm\wezterm.lua" "C:\codes\wezterm"</v>
+        <v>copy "%USERPROFILE%\.gitconfig" "C:\codes\git\setting_myuser"</v>
       </c>
       <c r="K38" s="1" t="str">
-        <f t="shared" ref="K38" si="4">IF(F38="○","rename """&amp;G38&amp;""" """&amp;RIGHT(G38,LEN(G38)-FIND("●",SUBSTITUTE(G38,"\","●",LEN(G38)-LEN(SUBSTITUTE(G38,"\","")))))&amp;"_bak""","")</f>
-        <v>rename "C:\Users\draem\.config\wezterm\wezterm.lua" "wezterm.lua_bak"</v>
+        <f t="shared" si="4"/>
+        <v>rename "%USERPROFILE%\.gitconfig" ".gitconfig_bak"</v>
       </c>
       <c r="L38" s="1" t="str">
-        <f t="shared" ref="L38" si="5">IF(
-  F38="○",
-  "mklink "&amp;IF(
-    E38="folder",
-    "/d ",
-    ""
-  )&amp;""""&amp;G38&amp;""" """&amp;H38&amp;"""",
-  ""
-)</f>
-        <v>mklink "C:\Users\draem\.config\wezterm\wezterm.lua" "C:\codes\wezterm\wezterm.lua"</v>
+        <f t="shared" si="5"/>
+        <v>mklink "%USERPROFILE%\.gitconfig" "C:\codes\git\setting_myuser\.gitconfig"</v>
       </c>
       <c r="M38" t="s">
         <v>1298</v>
       </c>
     </row>
     <row r="39" spans="1:13">
-      <c r="A39" s="1" t="s">
-        <v>885</v>
+      <c r="A39" s="6" t="s">
+        <v>887</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>82</v>
+        <v>1464</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>320</v>
+        <v>155</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>321</v>
+        <v>155</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>1419</v>
+        <v>1520</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>1081</v>
+        <v>1463</v>
       </c>
       <c r="I39" s="1" t="str">
         <f>IF($F39="○","mkdir """&amp;[2]!getdirpath($H39)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\HNXgrep"</v>
+        <v>mkdir "C:\codes\wezterm"</v>
       </c>
       <c r="J39" s="1" t="str">
         <f>IF(
@@ -67314,15 +67327,23 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Local\HNXgrep" "G:\マイドライブ\100_programs\120_setting\HNXgrep\HNXgrep" /MIR /XD "System Volume Information"</v>
+        <v>copy "%USERPROFILE%\.config\wezterm\wezterm.lua" "C:\codes\wezterm"</v>
       </c>
       <c r="K39" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\AppData\Local\HNXgrep" "HNXgrep_bak"</v>
+        <f t="shared" ref="K39" si="6">IF(F39="○","rename """&amp;G39&amp;""" """&amp;RIGHT(G39,LEN(G39)-FIND("●",SUBSTITUTE(G39,"\","●",LEN(G39)-LEN(SUBSTITUTE(G39,"\","")))))&amp;"_bak""","")</f>
+        <v>rename "%USERPROFILE%\.config\wezterm\wezterm.lua" "wezterm.lua_bak"</v>
       </c>
       <c r="L39" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Local\HNXgrep" "G:\マイドライブ\100_programs\120_setting\HNXgrep\HNXgrep"</v>
+        <f t="shared" ref="L39" si="7">IF(
+  F39="○",
+  "mklink "&amp;IF(
+    E39="folder",
+    "/d ",
+    ""
+  )&amp;""""&amp;G39&amp;""" """&amp;H39&amp;"""",
+  ""
+)</f>
+        <v>mklink "%USERPROFILE%\.config\wezterm\wezterm.lua" "C:\codes\wezterm\wezterm.lua"</v>
       </c>
       <c r="M39" t="s">
         <v>1298</v>
@@ -67333,7 +67354,7 @@
         <v>885</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>320</v>
@@ -67348,14 +67369,14 @@
         <v>0</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>912</v>
+        <v>1419</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="I40" s="1" t="str">
         <f>IF($F40="○","mkdir """&amp;[2]!getdirpath($H40)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Icaros"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\HNXgrep"</v>
       </c>
       <c r="J40" s="1" t="str">
         <f>IF(
@@ -67367,15 +67388,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Local\Icaros" "G:\マイドライブ\100_programs\120_setting\Icaros\Icaros" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Local\HNXgrep" "G:\マイドライブ\100_programs\120_setting\HNXgrep\HNXgrep" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K40" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\AppData\Local\Icaros" "Icaros_bak"</v>
+        <v>rename "%USERPROFILE%\AppData\Local\HNXgrep" "HNXgrep_bak"</v>
       </c>
       <c r="L40" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Local\Icaros" "G:\マイドライブ\100_programs\120_setting\Icaros\Icaros"</v>
+        <v>mklink /d "%USERPROFILE%\AppData\Local\HNXgrep" "G:\マイドライブ\100_programs\120_setting\HNXgrep\HNXgrep"</v>
       </c>
       <c r="M40" t="s">
         <v>1298</v>
@@ -67386,7 +67407,7 @@
         <v>885</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>320</v>
@@ -67401,14 +67422,14 @@
         <v>0</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>883</v>
+        <v>912</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="I41" s="1" t="str">
         <f>IF($F41="○","mkdir """&amp;[2]!getdirpath($H41)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\EasyShot"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Icaros"</v>
       </c>
       <c r="J41" s="1" t="str">
         <f>IF(
@@ -67420,15 +67441,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\GZ20" "G:\マイドライブ\100_programs\120_setting\EasyShot\GZ20" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Local\Icaros" "G:\マイドライブ\100_programs\120_setting\Icaros\Icaros" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K41" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\AppData\Roaming\GZ20" "GZ20_bak"</v>
+        <v>rename "%USERPROFILE%\AppData\Local\Icaros" "Icaros_bak"</v>
       </c>
       <c r="L41" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\GZ20" "G:\マイドライブ\100_programs\120_setting\EasyShot\GZ20"</v>
+        <v>mklink /d "%USERPROFILE%\AppData\Local\Icaros" "G:\マイドライブ\100_programs\120_setting\Icaros\Icaros"</v>
       </c>
       <c r="M41" t="s">
         <v>1298</v>
@@ -67439,7 +67460,7 @@
         <v>885</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>320</v>
@@ -67454,14 +67475,14 @@
         <v>0</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>913</v>
+        <v>883</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I42" s="1" t="str">
         <f>IF($F42="○","mkdir """&amp;[2]!getdirpath($H42)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\DeInput"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\EasyShot"</v>
       </c>
       <c r="J42" s="1" t="str">
         <f>IF(
@@ -67473,15 +67494,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\KT Software" "G:\マイドライブ\100_programs\120_setting\DeInput\KT Software" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\GZ20" "G:\マイドライブ\100_programs\120_setting\EasyShot\GZ20" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K42" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\AppData\Roaming\KT Software" "KT Software_bak"</v>
+        <v>rename "%USERPROFILE%\AppData\Roaming\GZ20" "GZ20_bak"</v>
       </c>
       <c r="L42" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\KT Software" "G:\マイドライブ\100_programs\120_setting\DeInput\KT Software"</v>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\GZ20" "G:\マイドライブ\100_programs\120_setting\EasyShot\GZ20"</v>
       </c>
       <c r="M42" t="s">
         <v>1298</v>
@@ -67492,7 +67513,7 @@
         <v>885</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>468</v>
+        <v>76</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>320</v>
@@ -67507,14 +67528,14 @@
         <v>0</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>1267</v>
+        <v>913</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="I43" s="1" t="str">
         <f>IF($F43="○","mkdir """&amp;[2]!getdirpath($H43)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\MP3Tag"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\DeInput"</v>
       </c>
       <c r="J43" s="1" t="str">
         <f>IF(
@@ -67526,15 +67547,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\Mp3tag" "G:\マイドライブ\100_programs\120_setting\MP3Tag\MP3Tag" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\KT Software" "G:\マイドライブ\100_programs\120_setting\DeInput\KT Software" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K43" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\AppData\Roaming\Mp3tag" "Mp3tag_bak"</v>
+        <v>rename "%USERPROFILE%\AppData\Roaming\KT Software" "KT Software_bak"</v>
       </c>
       <c r="L43" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Mp3tag" "G:\マイドライブ\100_programs\120_setting\MP3Tag\MP3Tag"</v>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\KT Software" "G:\マイドライブ\100_programs\120_setting\DeInput\KT Software"</v>
       </c>
       <c r="M43" t="s">
         <v>1298</v>
@@ -67545,7 +67566,7 @@
         <v>885</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>88</v>
+        <v>468</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>320</v>
@@ -67557,19 +67578,19 @@
         <v>17</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G44" s="97" t="s">
-        <v>1268</v>
-      </c>
-      <c r="H44" s="97" t="s">
-        <v>1269</v>
-      </c>
-      <c r="I44" s="97" t="str">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I44" s="1" t="str">
         <f>IF($F44="○","mkdir """&amp;[2]!getdirpath($H44)&amp;"""","")</f>
-        <v/>
-      </c>
-      <c r="J44" s="97" t="str">
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\MP3Tag"</v>
+      </c>
+      <c r="J44" s="1" t="str">
         <f>IF(
   $F44="○",
   IF(
@@ -67579,15 +67600,15 @@
   ),
   ""
 )</f>
-        <v/>
-      </c>
-      <c r="K44" s="97" t="str">
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\Mp3tag" "G:\マイドライブ\100_programs\120_setting\MP3Tag\MP3Tag" /MIR /XD "System Volume Information"</v>
+      </c>
+      <c r="K44" s="1" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L44" s="97" t="str">
+        <v>rename "%USERPROFILE%\AppData\Roaming\Mp3tag" "Mp3tag_bak"</v>
+      </c>
+      <c r="L44" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Mp3tag" "G:\マイドライブ\100_programs\120_setting\MP3Tag\MP3Tag"</v>
       </c>
       <c r="M44" t="s">
         <v>1298</v>
@@ -67598,7 +67619,7 @@
         <v>885</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>320</v>
@@ -67610,19 +67631,19 @@
         <v>17</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>877</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="I45" s="1" t="str">
+        <v>28</v>
+      </c>
+      <c r="G45" s="97" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H45" s="97" t="s">
+        <v>1269</v>
+      </c>
+      <c r="I45" s="97" t="str">
         <f>IF($F45="○","mkdir """&amp;[2]!getdirpath($H45)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Audacity"</v>
-      </c>
-      <c r="J45" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J45" s="97" t="str">
         <f>IF(
   $F45="○",
   IF(
@@ -67632,15 +67653,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\Audacity" "G:\マイドライブ\100_programs\120_setting\Audacity\Audacity" /MIR /XD "System Volume Information"</v>
-      </c>
-      <c r="K45" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K45" s="97" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\AppData\Roaming\Audacity" "Audacity_bak"</v>
-      </c>
-      <c r="L45" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L45" s="97" t="str">
         <f t="shared" si="0"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Audacity" "G:\マイドライブ\100_programs\120_setting\Audacity\Audacity"</v>
+        <v/>
       </c>
       <c r="M45" t="s">
         <v>1298</v>
@@ -67651,7 +67672,7 @@
         <v>885</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>470</v>
+        <v>72</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>320</v>
@@ -67666,14 +67687,14 @@
         <v>0</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>1497</v>
+        <v>877</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="I46" s="1" t="str">
         <f>IF($F46="○","mkdir """&amp;[2]!getdirpath($H46)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Subversion"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Audacity"</v>
       </c>
       <c r="J46" s="1" t="str">
         <f>IF(
@@ -67685,15 +67706,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\Subversion" "G:\マイドライブ\100_programs\120_setting\Subversion\Subversion" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\Audacity" "G:\マイドライブ\100_programs\120_setting\Audacity\Audacity" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K46" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\AppData\Roaming\Subversion" "Subversion_bak"</v>
+        <v>rename "%USERPROFILE%\AppData\Roaming\Audacity" "Audacity_bak"</v>
       </c>
       <c r="L46" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Subversion" "G:\マイドライブ\100_programs\120_setting\Subversion\Subversion"</v>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Audacity" "G:\マイドライブ\100_programs\120_setting\Audacity\Audacity"</v>
       </c>
       <c r="M46" t="s">
         <v>1298</v>
@@ -67704,7 +67725,7 @@
         <v>885</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>51</v>
+        <v>470</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>320</v>
@@ -67719,14 +67740,14 @@
         <v>0</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>901</v>
+        <v>1496</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="I47" s="1" t="str">
         <f>IF($F47="○","mkdir """&amp;[2]!getdirpath($H47)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\TortoiseGit"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Subversion"</v>
       </c>
       <c r="J47" s="1" t="str">
         <f>IF(
@@ -67738,15 +67759,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\TortoiseGit" "G:\マイドライブ\100_programs\120_setting\TortoiseGit\TortoiseGit" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\Subversion" "G:\マイドライブ\100_programs\120_setting\Subversion\Subversion" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K47" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\AppData\Roaming\TortoiseGit" "TortoiseGit_bak"</v>
+        <v>rename "%USERPROFILE%\AppData\Roaming\Subversion" "Subversion_bak"</v>
       </c>
       <c r="L47" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\TortoiseGit" "G:\マイドライブ\100_programs\120_setting\TortoiseGit\TortoiseGit"</v>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Subversion" "G:\マイドライブ\100_programs\120_setting\Subversion\Subversion"</v>
       </c>
       <c r="M47" t="s">
         <v>1298</v>
@@ -67757,7 +67778,7 @@
         <v>885</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>320</v>
@@ -67772,14 +67793,14 @@
         <v>0</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>878</v>
+        <v>901</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="I48" s="1" t="str">
         <f>IF($F48="○","mkdir """&amp;[2]!getdirpath($H48)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\TortoiseSVN"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\TortoiseGit"</v>
       </c>
       <c r="J48" s="1" t="str">
         <f>IF(
@@ -67791,15 +67812,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\TortoiseSVN" "G:\マイドライブ\100_programs\120_setting\TortoiseSVN\TortoiseSVN" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\TortoiseGit" "G:\マイドライブ\100_programs\120_setting\TortoiseGit\TortoiseGit" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K48" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\AppData\Roaming\TortoiseSVN" "TortoiseSVN_bak"</v>
+        <v>rename "%USERPROFILE%\AppData\Roaming\TortoiseGit" "TortoiseGit_bak"</v>
       </c>
       <c r="L48" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\TortoiseSVN" "G:\マイドライブ\100_programs\120_setting\TortoiseSVN\TortoiseSVN"</v>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\TortoiseGit" "G:\マイドライブ\100_programs\120_setting\TortoiseGit\TortoiseGit"</v>
       </c>
       <c r="M48" t="s">
         <v>1298</v>
@@ -67810,13 +67831,13 @@
         <v>885</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>961</v>
+        <v>55</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>17</v>
@@ -67825,14 +67846,14 @@
         <v>0</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>958</v>
+        <v>878</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>1157</v>
+        <v>1089</v>
       </c>
       <c r="I49" s="1" t="str">
         <f>IF($F49="○","mkdir """&amp;[2]!getdirpath($H49)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Anki2"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\TortoiseSVN"</v>
       </c>
       <c r="J49" s="1" t="str">
         <f>IF(
@@ -67844,23 +67865,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\Anki2" "G:\マイドライブ\100_programs\120_setting\Anki2\Anki2" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\TortoiseSVN" "G:\マイドライブ\100_programs\120_setting\TortoiseSVN\TortoiseSVN" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K49" s="1" t="str">
-        <f>IF(F49="○","rename """&amp;G49&amp;""" """&amp;RIGHT(G49,LEN(G49)-FIND("●",SUBSTITUTE(G49,"\","●",LEN(G49)-LEN(SUBSTITUTE(G49,"\","")))))&amp;"_bak""","")</f>
-        <v>rename "%USERPROFILE%\AppData\Roaming\Anki2" "Anki2_bak"</v>
+        <f t="shared" si="1"/>
+        <v>rename "%USERPROFILE%\AppData\Roaming\TortoiseSVN" "TortoiseSVN_bak"</v>
       </c>
       <c r="L49" s="1" t="str">
-        <f>IF(
-  F49="○",
-  "mklink "&amp;IF(
-    E49="folder",
-    "/d ",
-    ""
-  )&amp;""""&amp;G49&amp;""" """&amp;H49&amp;"""",
-  ""
-)</f>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Anki2" "G:\マイドライブ\100_programs\120_setting\Anki2\Anki2"</v>
+        <f t="shared" si="0"/>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\TortoiseSVN" "G:\マイドライブ\100_programs\120_setting\TortoiseSVN\TortoiseSVN"</v>
       </c>
       <c r="M49" t="s">
         <v>1298</v>
@@ -67871,13 +67884,13 @@
         <v>885</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>469</v>
+        <v>961</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>17</v>
@@ -67886,14 +67899,14 @@
         <v>0</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>1420</v>
+        <v>958</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>1090</v>
+        <v>1157</v>
       </c>
       <c r="I50" s="1" t="str">
         <f>IF($F50="○","mkdir """&amp;[2]!getdirpath($H50)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Serato"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Anki2"</v>
       </c>
       <c r="J50" s="1" t="str">
         <f>IF(
@@ -67905,15 +67918,23 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\Music\_Serato_" "G:\マイドライブ\100_programs\120_setting\Serato\_Serato_" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\Anki2" "G:\マイドライブ\100_programs\120_setting\Anki2\Anki2" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K50" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\Music\_Serato_" "_Serato__bak"</v>
+        <f>IF(F50="○","rename """&amp;G50&amp;""" """&amp;RIGHT(G50,LEN(G50)-FIND("●",SUBSTITUTE(G50,"\","●",LEN(G50)-LEN(SUBSTITUTE(G50,"\","")))))&amp;"_bak""","")</f>
+        <v>rename "%USERPROFILE%\AppData\Roaming\Anki2" "Anki2_bak"</v>
       </c>
       <c r="L50" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>mklink /d "%USERPROFILE%\Music\_Serato_" "G:\マイドライブ\100_programs\120_setting\Serato\_Serato_"</v>
+        <f>IF(
+  F50="○",
+  "mklink "&amp;IF(
+    E50="folder",
+    "/d ",
+    ""
+  )&amp;""""&amp;G50&amp;""" """&amp;H50&amp;"""",
+  ""
+)</f>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Anki2" "G:\マイドライブ\100_programs\120_setting\Anki2\Anki2"</v>
       </c>
       <c r="M50" t="s">
         <v>1298</v>
@@ -67924,7 +67945,7 @@
         <v>885</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>884</v>
+        <v>469</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>320</v>
@@ -67939,10 +67960,10 @@
         <v>0</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>880</v>
+        <v>1420</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="I51" s="1" t="str">
         <f>IF($F51="○","mkdir """&amp;[2]!getdirpath($H51)&amp;"""","")</f>
@@ -67958,23 +67979,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\Music\_Serato_Backup" "G:\マイドライブ\100_programs\120_setting\Serato\_Serato_Backup" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\Music\_Serato_" "G:\マイドライブ\100_programs\120_setting\Serato\_Serato_" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K51" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\Music\_Serato_Backup" "_Serato_Backup_bak"</v>
+        <v>rename "%USERPROFILE%\Music\_Serato_" "_Serato__bak"</v>
       </c>
       <c r="L51" s="1" t="str">
-        <f t="shared" ref="L51:L65" si="6">IF(
-  F51="○",
-  "mklink "&amp;IF(
-    E51="folder",
-    "/d ",
-    ""
-  )&amp;""""&amp;G51&amp;""" """&amp;H51&amp;"""",
-  ""
-)</f>
-        <v>mklink /d "%USERPROFILE%\Music\_Serato_Backup" "G:\マイドライブ\100_programs\120_setting\Serato\_Serato_Backup"</v>
+        <f t="shared" si="0"/>
+        <v>mklink /d "%USERPROFILE%\Music\_Serato_" "G:\マイドライブ\100_programs\120_setting\Serato\_Serato_"</v>
       </c>
       <c r="M51" t="s">
         <v>1298</v>
@@ -67985,31 +67998,31 @@
         <v>885</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>960</v>
+        <v>884</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G52" s="97" t="s">
-        <v>959</v>
-      </c>
-      <c r="H52" s="97" t="s">
-        <v>1098</v>
-      </c>
-      <c r="I52" s="97" t="str">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I52" s="1" t="str">
         <f>IF($F52="○","mkdir """&amp;[2]!getdirpath($H52)&amp;"""","")</f>
-        <v/>
-      </c>
-      <c r="J52" s="97" t="str">
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Serato"</v>
+      </c>
+      <c r="J52" s="1" t="str">
         <f>IF(
   $F52="○",
   IF(
@@ -68019,14 +68032,14 @@
   ),
   ""
 )</f>
-        <v/>
-      </c>
-      <c r="K52" s="97" t="str">
-        <f>IF(F52="○","rename """&amp;G52&amp;""" """&amp;RIGHT(G52,LEN(G52)-FIND("●",SUBSTITUTE(G52,"\","●",LEN(G52)-LEN(SUBSTITUTE(G52,"\","")))))&amp;"_bak""","")</f>
-        <v/>
-      </c>
-      <c r="L52" s="97" t="str">
-        <f>IF(
+        <v>robocopy "%USERPROFILE%\Music\_Serato_Backup" "G:\マイドライブ\100_programs\120_setting\Serato\_Serato_Backup" /MIR /XD "System Volume Information"</v>
+      </c>
+      <c r="K52" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>rename "%USERPROFILE%\Music\_Serato_Backup" "_Serato_Backup_bak"</v>
+      </c>
+      <c r="L52" s="1" t="str">
+        <f t="shared" ref="L52:L66" si="8">IF(
   F52="○",
   "mklink "&amp;IF(
     E52="folder",
@@ -68035,7 +68048,7 @@
   )&amp;""""&amp;G52&amp;""" """&amp;H52&amp;"""",
   ""
 )</f>
-        <v/>
+        <v>mklink /d "%USERPROFILE%\Music\_Serato_Backup" "G:\マイドライブ\100_programs\120_setting\Serato\_Serato_Backup"</v>
       </c>
       <c r="M52" t="s">
         <v>1298</v>
@@ -68055,16 +68068,16 @@
         <v>0</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G53" s="97" t="s">
-        <v>1166</v>
+        <v>959</v>
       </c>
       <c r="H53" s="97" t="s">
-        <v>1167</v>
+        <v>1098</v>
       </c>
       <c r="I53" s="97" t="str">
         <f>IF($F53="○","mkdir """&amp;[2]!getdirpath($H53)&amp;"""","")</f>
@@ -68107,31 +68120,31 @@
         <v>885</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>1156</v>
+        <v>960</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>1159</v>
-      </c>
-      <c r="I54" s="1" t="str">
+        <v>28</v>
+      </c>
+      <c r="G54" s="97" t="s">
+        <v>1166</v>
+      </c>
+      <c r="H54" s="97" t="s">
+        <v>1167</v>
+      </c>
+      <c r="I54" s="97" t="str">
         <f>IF($F54="○","mkdir """&amp;[2]!getdirpath($H54)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\X-Finder"</v>
-      </c>
-      <c r="J54" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J54" s="97" t="str">
         <f>IF(
   $F54="○",
   IF(
@@ -68141,14 +68154,14 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\X-Finder\XF.ini" "G:\マイドライブ\100_programs\120_setting\X-Finder"</v>
-      </c>
-      <c r="K54" s="1" t="str">
-        <f t="shared" ref="K54" si="7">IF(F54="○","rename """&amp;G54&amp;""" """&amp;RIGHT(G54,LEN(G54)-FIND("●",SUBSTITUTE(G54,"\","●",LEN(G54)-LEN(SUBSTITUTE(G54,"\","")))))&amp;"_bak""","")</f>
-        <v>rename "C:\prg_exe\X-Finder\XF.ini" "XF.ini_bak"</v>
-      </c>
-      <c r="L54" s="1" t="str">
-        <f t="shared" ref="L54" si="8">IF(
+        <v/>
+      </c>
+      <c r="K54" s="97" t="str">
+        <f>IF(F54="○","rename """&amp;G54&amp;""" """&amp;RIGHT(G54,LEN(G54)-FIND("●",SUBSTITUTE(G54,"\","●",LEN(G54)-LEN(SUBSTITUTE(G54,"\","")))))&amp;"_bak""","")</f>
+        <v/>
+      </c>
+      <c r="L54" s="97" t="str">
+        <f>IF(
   F54="○",
   "mklink "&amp;IF(
     E54="folder",
@@ -68157,7 +68170,7 @@
   )&amp;""""&amp;G54&amp;""" """&amp;H54&amp;"""",
   ""
 )</f>
-        <v>mklink "C:\prg_exe\X-Finder\XF.ini" "G:\マイドライブ\100_programs\120_setting\X-Finder\XF.ini"</v>
+        <v/>
       </c>
       <c r="M54" t="s">
         <v>1298</v>
@@ -68168,29 +68181,29 @@
         <v>885</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>918</v>
+        <v>1156</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>321</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>1421</v>
+        <v>1158</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>1092</v>
+        <v>1159</v>
       </c>
       <c r="I55" s="1" t="str">
         <f>IF($F55="○","mkdir """&amp;[2]!getdirpath($H55)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\X-Finder"</v>
       </c>
       <c r="J55" s="1" t="str">
         <f>IF(
@@ -68202,15 +68215,23 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\Music\iTunes\Previous iTunes Libraries" "G:\マイドライブ\100_programs\120_setting\iTunes\Previous iTunes Libraries" /MIR /XD "System Volume Information"</v>
+        <v>copy "C:\prg_exe\X-Finder\XF.ini" "G:\マイドライブ\100_programs\120_setting\X-Finder"</v>
       </c>
       <c r="K55" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\Music\iTunes\Previous iTunes Libraries" "Previous iTunes Libraries_bak"</v>
+        <f t="shared" ref="K55" si="9">IF(F55="○","rename """&amp;G55&amp;""" """&amp;RIGHT(G55,LEN(G55)-FIND("●",SUBSTITUTE(G55,"\","●",LEN(G55)-LEN(SUBSTITUTE(G55,"\","")))))&amp;"_bak""","")</f>
+        <v>rename "C:\prg_exe\X-Finder\XF.ini" "XF.ini_bak"</v>
       </c>
       <c r="L55" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>mklink /d "%USERPROFILE%\Music\iTunes\Previous iTunes Libraries" "G:\マイドライブ\100_programs\120_setting\iTunes\Previous iTunes Libraries"</v>
+        <f t="shared" ref="L55" si="10">IF(
+  F55="○",
+  "mklink "&amp;IF(
+    E55="folder",
+    "/d ",
+    ""
+  )&amp;""""&amp;G55&amp;""" """&amp;H55&amp;"""",
+  ""
+)</f>
+        <v>mklink "C:\prg_exe\X-Finder\XF.ini" "G:\マイドライブ\100_programs\120_setting\X-Finder\XF.ini"</v>
       </c>
       <c r="M55" t="s">
         <v>1298</v>
@@ -68221,7 +68242,7 @@
         <v>885</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>320</v>
@@ -68230,16 +68251,16 @@
         <v>321</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>915</v>
+        <v>1421</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="I56" s="1" t="str">
         <f>IF($F56="○","mkdir """&amp;[2]!getdirpath($H56)&amp;"""","")</f>
@@ -68255,15 +68276,15 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Library Extras.itdb" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
+        <v>robocopy "%USERPROFILE%\Music\iTunes\Previous iTunes Libraries" "G:\マイドライブ\100_programs\120_setting\iTunes\Previous iTunes Libraries" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K56" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\Music\iTunes\iTunes Library Extras.itdb" "iTunes Library Extras.itdb_bak"</v>
+        <v>rename "%USERPROFILE%\Music\iTunes\Previous iTunes Libraries" "Previous iTunes Libraries_bak"</v>
       </c>
       <c r="L56" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>mklink "%USERPROFILE%\Music\iTunes\iTunes Library Extras.itdb" "G:\マイドライブ\100_programs\120_setting\iTunes\iTunes Library Extras.itdb"</v>
+        <f t="shared" si="8"/>
+        <v>mklink /d "%USERPROFILE%\Music\iTunes\Previous iTunes Libraries" "G:\マイドライブ\100_programs\120_setting\iTunes\Previous iTunes Libraries"</v>
       </c>
       <c r="M56" t="s">
         <v>1298</v>
@@ -68274,7 +68295,7 @@
         <v>885</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>320</v>
@@ -68289,10 +68310,10 @@
         <v>0</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="I57" s="1" t="str">
         <f>IF($F57="○","mkdir """&amp;[2]!getdirpath($H57)&amp;"""","")</f>
@@ -68308,15 +68329,15 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Library Genius.itdb" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
+        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Library Extras.itdb" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
       </c>
       <c r="K57" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\Music\iTunes\iTunes Library Genius.itdb" "iTunes Library Genius.itdb_bak"</v>
+        <v>rename "%USERPROFILE%\Music\iTunes\iTunes Library Extras.itdb" "iTunes Library Extras.itdb_bak"</v>
       </c>
       <c r="L57" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>mklink "%USERPROFILE%\Music\iTunes\iTunes Library Genius.itdb" "G:\マイドライブ\100_programs\120_setting\iTunes\iTunes Library Genius.itdb"</v>
+        <f t="shared" si="8"/>
+        <v>mklink "%USERPROFILE%\Music\iTunes\iTunes Library Extras.itdb" "G:\マイドライブ\100_programs\120_setting\iTunes\iTunes Library Extras.itdb"</v>
       </c>
       <c r="M57" t="s">
         <v>1298</v>
@@ -68327,7 +68348,7 @@
         <v>885</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>320</v>
@@ -68342,10 +68363,10 @@
         <v>0</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="I58" s="1" t="str">
         <f>IF($F58="○","mkdir """&amp;[2]!getdirpath($H58)&amp;"""","")</f>
@@ -68361,15 +68382,15 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Library.itl" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
+        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Library Genius.itdb" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
       </c>
       <c r="K58" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\Music\iTunes\iTunes Library.itl" "iTunes Library.itl_bak"</v>
+        <v>rename "%USERPROFILE%\Music\iTunes\iTunes Library Genius.itdb" "iTunes Library Genius.itdb_bak"</v>
       </c>
       <c r="L58" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>mklink "%USERPROFILE%\Music\iTunes\iTunes Library.itl" "G:\マイドライブ\100_programs\120_setting\iTunes\iTunes Library.itl"</v>
+        <f t="shared" si="8"/>
+        <v>mklink "%USERPROFILE%\Music\iTunes\iTunes Library Genius.itdb" "G:\マイドライブ\100_programs\120_setting\iTunes\iTunes Library Genius.itdb"</v>
       </c>
       <c r="M58" t="s">
         <v>1298</v>
@@ -68380,7 +68401,7 @@
         <v>885</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>320</v>
@@ -68395,10 +68416,10 @@
         <v>0</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="I59" s="1" t="str">
         <f>IF($F59="○","mkdir """&amp;[2]!getdirpath($H59)&amp;"""","")</f>
@@ -68414,15 +68435,15 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Music Library.xml" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
+        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Library.itl" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
       </c>
       <c r="K59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\Music\iTunes\iTunes Music Library.xml" "iTunes Music Library.xml_bak"</v>
+        <v>rename "%USERPROFILE%\Music\iTunes\iTunes Library.itl" "iTunes Library.itl_bak"</v>
       </c>
       <c r="L59" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>mklink "%USERPROFILE%\Music\iTunes\iTunes Music Library.xml" "G:\マイドライブ\100_programs\120_setting\iTunes\iTunes Music Library.xml"</v>
+        <f t="shared" si="8"/>
+        <v>mklink "%USERPROFILE%\Music\iTunes\iTunes Library.itl" "G:\マイドライブ\100_programs\120_setting\iTunes\iTunes Library.itl"</v>
       </c>
       <c r="M59" t="s">
         <v>1298</v>
@@ -68433,7 +68454,7 @@
         <v>885</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>320</v>
@@ -68447,11 +68468,11 @@
       <c r="F60" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G60" s="172" t="s">
-        <v>924</v>
+      <c r="G60" s="1" t="s">
+        <v>923</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="I60" s="1" t="str">
         <f>IF($F60="○","mkdir """&amp;[2]!getdirpath($H60)&amp;"""","")</f>
@@ -68467,15 +68488,15 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\Music\iTunes\sentinel" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
+        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Music Library.xml" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
       </c>
       <c r="K60" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\Music\iTunes\sentinel" "sentinel_bak"</v>
+        <v>rename "%USERPROFILE%\Music\iTunes\iTunes Music Library.xml" "iTunes Music Library.xml_bak"</v>
       </c>
       <c r="L60" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>mklink "%USERPROFILE%\Music\iTunes\sentinel" "G:\マイドライブ\100_programs\120_setting\iTunes\sentinel"</v>
+        <f t="shared" si="8"/>
+        <v>mklink "%USERPROFILE%\Music\iTunes\iTunes Music Library.xml" "G:\マイドライブ\100_programs\120_setting\iTunes\iTunes Music Library.xml"</v>
       </c>
       <c r="M60" t="s">
         <v>1298</v>
@@ -68483,10 +68504,10 @@
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="1" t="s">
-        <v>900</v>
+        <v>885</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>320</v>
@@ -68495,20 +68516,20 @@
         <v>321</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>1389</v>
+      <c r="G61" s="172" t="s">
+        <v>924</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>319</v>
+        <v>1097</v>
       </c>
       <c r="I61" s="1" t="str">
         <f>IF($F61="○","mkdir """&amp;[2]!getdirpath($H61)&amp;"""","")</f>
-        <v>mkdir "X:\720_Evacuate_iTunes\MobileSync"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
       </c>
       <c r="J61" s="1" t="str">
         <f>IF(
@@ -68520,15 +68541,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\Apple\MobileSync\Backup" "X:\720_Evacuate_iTunes\MobileSync\BackUp" /MIR /XD "System Volume Information"</v>
+        <v>copy "%USERPROFILE%\Music\iTunes\sentinel" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
       </c>
       <c r="K61" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\Apple\MobileSync\Backup" "Backup_bak"</v>
+        <v>rename "%USERPROFILE%\Music\iTunes\sentinel" "sentinel_bak"</v>
       </c>
       <c r="L61" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>mklink /d "%USERPROFILE%\Apple\MobileSync\Backup" "X:\720_Evacuate_iTunes\MobileSync\BackUp"</v>
+        <f t="shared" si="8"/>
+        <v>mklink "%USERPROFILE%\Music\iTunes\sentinel" "G:\マイドライブ\100_programs\120_setting\iTunes\sentinel"</v>
       </c>
       <c r="M61" t="s">
         <v>1298</v>
@@ -68539,7 +68560,7 @@
         <v>900</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>320</v>
@@ -68554,14 +68575,14 @@
         <v>0</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>322</v>
+        <v>1389</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="I62" s="1" t="str">
         <f>IF($F62="○","mkdir """&amp;[2]!getdirpath($H62)&amp;"""","")</f>
-        <v>mkdir "X:\720_Evacuate_iTunes"</v>
+        <v>mkdir "X:\720_Evacuate_iTunes\MobileSync"</v>
       </c>
       <c r="J62" s="1" t="str">
         <f>IF(
@@ -68573,15 +68594,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\Music\iTunes\Album Artwork" "X:\720_Evacuate_iTunes\iTunes Media" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\Apple\MobileSync\Backup" "X:\720_Evacuate_iTunes\MobileSync\BackUp" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K62" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\Music\iTunes\Album Artwork" "Album Artwork_bak"</v>
+        <v>rename "%USERPROFILE%\Apple\MobileSync\Backup" "Backup_bak"</v>
       </c>
       <c r="L62" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>mklink /d "%USERPROFILE%\Music\iTunes\Album Artwork" "X:\720_Evacuate_iTunes\iTunes Media"</v>
+        <f t="shared" si="8"/>
+        <v>mklink /d "%USERPROFILE%\Apple\MobileSync\Backup" "X:\720_Evacuate_iTunes\MobileSync\BackUp"</v>
       </c>
       <c r="M62" t="s">
         <v>1298</v>
@@ -68592,7 +68613,7 @@
         <v>900</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>320</v>
@@ -68607,10 +68628,10 @@
         <v>0</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I63" s="1" t="str">
         <f>IF($F63="○","mkdir """&amp;[2]!getdirpath($H63)&amp;"""","")</f>
@@ -68626,32 +68647,48 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\Music\iTunes\iTunes Media" "X:\720_Evacuate_iTunes\MobileSync" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\Music\iTunes\Album Artwork" "X:\720_Evacuate_iTunes\iTunes Media" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K63" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>rename "%USERPROFILE%\Music\iTunes\iTunes Media" "iTunes Media_bak"</v>
+        <v>rename "%USERPROFILE%\Music\iTunes\Album Artwork" "Album Artwork_bak"</v>
       </c>
       <c r="L63" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>mklink /d "%USERPROFILE%\Music\iTunes\iTunes Media" "X:\720_Evacuate_iTunes\MobileSync"</v>
+        <f t="shared" si="8"/>
+        <v>mklink /d "%USERPROFILE%\Music\iTunes\Album Artwork" "X:\720_Evacuate_iTunes\iTunes Media"</v>
       </c>
       <c r="M63" t="s">
         <v>1298</v>
       </c>
     </row>
     <row r="64" spans="1:13">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
+      <c r="A64" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>325</v>
+      </c>
       <c r="I64" s="1" t="str">
         <f>IF($F64="○","mkdir """&amp;[2]!getdirpath($H64)&amp;"""","")</f>
-        <v/>
+        <v>mkdir "X:\720_Evacuate_iTunes"</v>
       </c>
       <c r="J64" s="1" t="str">
         <f>IF(
@@ -68663,15 +68700,15 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>robocopy "%USERPROFILE%\Music\iTunes\iTunes Media" "X:\720_Evacuate_iTunes\MobileSync" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K64" s="1" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>rename "%USERPROFILE%\Music\iTunes\iTunes Media" "iTunes Media_bak"</v>
       </c>
       <c r="L64" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f t="shared" si="8"/>
+        <v>mklink /d "%USERPROFILE%\Music\iTunes\iTunes Media" "X:\720_Evacuate_iTunes\MobileSync"</v>
       </c>
       <c r="M64" t="s">
         <v>1298</v>
@@ -68707,111 +68744,148 @@
         <v/>
       </c>
       <c r="L65" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="M65" t="s">
         <v>1298</v>
       </c>
     </row>
-    <row r="67" spans="1:13">
-      <c r="A67" t="s">
-        <v>938</v>
+    <row r="66" spans="1:13">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1" t="str">
+        <f>IF($F66="○","mkdir """&amp;[2]!getdirpath($H66)&amp;"""","")</f>
+        <v/>
+      </c>
+      <c r="J66" s="1" t="str">
+        <f>IF(
+  $F66="○",
+  IF(
+    $E66="file",
+    "copy """&amp;$G66&amp;""" """&amp;[2]!getdirpath($H66)&amp;"""",
+    "robocopy """&amp;$G66&amp;""" """&amp;H66&amp;""" /MIR /XD ""System Volume Information"""
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="K66" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L66" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="M66" t="s">
+        <v>1298</v>
       </c>
     </row>
     <row r="68" spans="1:13">
-      <c r="A68" s="95" t="s">
-        <v>937</v>
+      <c r="A68" t="s">
+        <v>938</v>
       </c>
     </row>
     <row r="69" spans="1:13">
-      <c r="A69" t="s">
-        <v>903</v>
+      <c r="A69" s="95" t="s">
+        <v>937</v>
       </c>
     </row>
     <row r="70" spans="1:13">
-      <c r="A70" s="95" t="s">
-        <v>902</v>
+      <c r="A70" t="s">
+        <v>903</v>
       </c>
     </row>
     <row r="71" spans="1:13">
-      <c r="A71" t="s">
-        <v>904</v>
+      <c r="A71" s="95" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="73" spans="1:13">
       <c r="A73" t="s">
-        <v>930</v>
+        <v>905</v>
       </c>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="75" spans="1:13">
       <c r="A75" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="76" spans="1:13">
       <c r="A76" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
     </row>
     <row r="77" spans="1:13">
       <c r="A77" t="s">
-        <v>956</v>
+        <v>936</v>
       </c>
     </row>
     <row r="78" spans="1:13">
-      <c r="A78" s="95" t="s">
-        <v>933</v>
+      <c r="A78" t="s">
+        <v>956</v>
       </c>
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="95" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
     </row>
     <row r="80" spans="1:13">
-      <c r="A80" t="s">
-        <v>957</v>
+      <c r="A80" s="95" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>1108</v>
+        <v>967</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
         <v>1135</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A11:L65" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A11:L66" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <phoneticPr fontId="7"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12:E65" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12:E66" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"file,folder"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12:F65 C12:D65" xr:uid="{00000000-0002-0000-0300-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12:D66 F12:F66" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"○,×"</formula1>
     </dataValidation>
   </dataValidations>
@@ -69370,7 +69444,7 @@
         <v>299</v>
       </c>
       <c r="B27" s="32" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="C27" s="34" t="s">
         <v>1430</v>
@@ -69424,7 +69498,7 @@
     <row r="29" spans="1:9">
       <c r="A29" s="144"/>
       <c r="B29" s="45" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="C29" s="36" t="s">
         <v>1111</v>
@@ -69456,7 +69530,7 @@
         <v>1117</v>
       </c>
       <c r="C30" s="36" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="D30" s="133" t="s">
         <v>1112</v>
@@ -69483,7 +69557,7 @@
         <v>1117</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="D31" s="36" t="str">
         <f>$C31</f>
@@ -69512,7 +69586,7 @@
         <v>1117</v>
       </c>
       <c r="C32" s="36" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="D32" s="36" t="str">
         <f>$C32</f>
@@ -69538,10 +69612,10 @@
         <v>1116</v>
       </c>
       <c r="B33" s="45" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="D33" s="36" t="str">
         <f t="shared" ref="D33:D48" si="3">$C33</f>
@@ -69570,7 +69644,7 @@
         <v>1117</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="D34" s="36" t="str">
         <f t="shared" si="3"/>
@@ -69599,7 +69673,7 @@
         <v>1117</v>
       </c>
       <c r="C35" s="36" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="D35" s="36" t="str">
         <f t="shared" si="3"/>
@@ -69628,7 +69702,7 @@
         <v>1117</v>
       </c>
       <c r="C36" s="36" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="D36" s="36" t="str">
         <f t="shared" si="3"/>
@@ -69657,7 +69731,7 @@
         <v>1117</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="D37" s="36" t="str">
         <f t="shared" si="3"/>
@@ -69686,7 +69760,7 @@
         <v>1117</v>
       </c>
       <c r="C38" s="36" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="D38" s="36" t="str">
         <f t="shared" si="3"/>
@@ -69715,7 +69789,7 @@
         <v>1117</v>
       </c>
       <c r="C39" s="36" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="D39" s="36" t="str">
         <f t="shared" si="3"/>
@@ -69744,7 +69818,7 @@
         <v>1117</v>
       </c>
       <c r="C40" s="36" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D40" s="36" t="str">
         <f t="shared" si="3"/>
@@ -69773,7 +69847,7 @@
         <v>1117</v>
       </c>
       <c r="C41" s="36" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="D41" s="36" t="str">
         <f t="shared" si="3"/>
@@ -69802,7 +69876,7 @@
         <v>1117</v>
       </c>
       <c r="C42" s="36" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="D42" s="36" t="str">
         <f t="shared" si="3"/>
@@ -69831,7 +69905,7 @@
         <v>1117</v>
       </c>
       <c r="C43" s="36" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="D43" s="36" t="str">
         <f t="shared" si="3"/>
@@ -69860,7 +69934,7 @@
         <v>1117</v>
       </c>
       <c r="C44" s="36" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="D44" s="36" t="str">
         <f t="shared" si="3"/>
@@ -69889,7 +69963,7 @@
         <v>1117</v>
       </c>
       <c r="C45" s="36" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="D45" s="36" t="str">
         <f t="shared" si="3"/>
@@ -70488,13 +70562,13 @@
       </c>
       <c r="B67" s="41"/>
       <c r="C67" s="36" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="D67" s="36" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="E67" s="36" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="F67" s="37" t="s">
         <v>0</v>

--- a/PC移行時チェックリスト.xlsx
+++ b/PC移行時チェックリスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE1E07F-841B-4CAA-9CEF-B4B414B6CB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B66C244-337B-4B94-8640-26BD2044B49D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32385" yWindow="1230" windowWidth="32385" windowHeight="40695" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5715" windowWidth="38640" windowHeight="42225" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="セットアップ事項" sheetId="21" r:id="rId1"/>

--- a/PC移行時チェックリスト.xlsx
+++ b/PC移行時チェックリスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3CA889-4CFD-4D4C-9E61-2FE116E5A190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BAC9E10-07E7-4FBB-B553-D14FC5025353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28815" yWindow="-5580" windowWidth="38385" windowHeight="41970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28815" yWindow="-5580" windowWidth="38385" windowHeight="41970" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="セットアップ事項" sheetId="21" r:id="rId1"/>
@@ -33,11 +33,11 @@
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">linux環境構築!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">shortcut!$A$9:$AJ$229</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">shortcut!$A$9:$AJ$228</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">symlink!$A$11:$L$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">セットアップ事項!$A$2:$M$83</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">linux環境構築!$A$6:$H$102</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">shortcut!$A$8:$AI$229</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">shortcut!$A$8:$AI$228</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">shortcut設定!$A$1:$O$38</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">symlink!$A$10:$L$66</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">セットアップ事項!$A$1:$H$83</definedName>
@@ -757,7 +757,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6397" uniqueCount="1545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6393" uniqueCount="1545">
   <si>
     <t>○</t>
   </si>
@@ -8092,10 +8092,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>k</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
     <t>C:\prg\TurboVNC\vncviewerw.bat</t>
   </si>
   <si>
@@ -8130,6 +8126,10 @@
   <si>
     <t>C:\root\30_tool\ScheduledBackup.bat</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>VIMプラグイン（jellybeans.vim）</t>
+    <phoneticPr fontId="7"/>
   </si>
 </sst>
 </file>
@@ -11267,7 +11267,7 @@
         <v>154</v>
       </c>
       <c r="D54" s="116" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="E54" s="142" t="s">
         <v>942</v>
@@ -11275,7 +11275,7 @@
       <c r="F54" s="143"/>
       <c r="G54" s="117"/>
       <c r="H54" s="117" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="I54" s="104" t="s">
         <v>29</v>
@@ -13586,7 +13586,7 @@
     <tabColor theme="8" tint="0.79998168889431442"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AN236"/>
+  <dimension ref="A1:AN235"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="11.25" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="42" style="7" bestFit="1" customWidth="1"/>
@@ -46739,13 +46739,13 @@
     </row>
     <row r="143" spans="1:36">
       <c r="A143" s="9" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B143" s="9" t="s">
         <v>1539</v>
       </c>
-      <c r="B143" s="9" t="s">
-        <v>1540</v>
-      </c>
       <c r="C143" s="9" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="D143" s="15" t="s">
         <v>40</v>
@@ -57459,7 +57459,7 @@
         <v/>
       </c>
       <c r="S186" s="9" t="str">
-        <f t="shared" ref="S186:S227" si="28">IF(
+        <f t="shared" ref="S186:S226" si="28">IF(
   OR(
     $H186="",
     $H186="-",
@@ -57590,7 +57590,7 @@
         <v>200</v>
       </c>
       <c r="AC186" s="20" t="str">
-        <f t="shared" ref="AC186:AC227" si="29">IF(AND($M186&lt;&gt;"",$M186&lt;&gt;"-")," (&amp;"&amp;$M186&amp;")","")</f>
+        <f t="shared" ref="AC186:AC226" si="29">IF(AND($M186&lt;&gt;"",$M186&lt;&gt;"-")," (&amp;"&amp;$M186&amp;")","")</f>
         <v/>
       </c>
       <c r="AD186" s="13" t="str">
@@ -57624,7 +57624,7 @@
         <v/>
       </c>
       <c r="AG186" s="13" t="str">
-        <f t="shared" ref="AG186:AG227" si="30">IF(
+        <f t="shared" ref="AG186:AG226" si="30">IF(
   AND($A186&lt;&gt;"",$O186&lt;&gt;"-",$O186&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O186&amp;""" /tr """&amp;$C186&amp;""" /sc daily /st "&amp;$P186&amp;" /rl highest"
@@ -57634,7 +57634,7 @@
         <v/>
       </c>
       <c r="AH186" s="13" t="str">
-        <f t="shared" ref="AH186:AH227" si="31">IF(
+        <f t="shared" ref="AH186:AH226" si="31">IF(
   AND($A186&lt;&gt;"",$O186&lt;&gt;"-",$O186&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O186&amp;""""
@@ -61605,7 +61605,7 @@
         <v>1532</v>
       </c>
       <c r="C203" s="9" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="D203" s="15" t="s">
         <v>40</v>
@@ -62117,7 +62117,7 @@
         <v>845</v>
       </c>
       <c r="C205" s="174" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="D205" s="175" t="s">
         <v>40</v>
@@ -66864,15 +66864,9 @@
       </c>
     </row>
     <row r="224" spans="1:36">
-      <c r="A224" s="9" t="s">
-        <v>1539</v>
-      </c>
-      <c r="B224" s="9" t="s">
-        <v>1540</v>
-      </c>
-      <c r="C224" s="9" t="s">
-        <v>1538</v>
-      </c>
+      <c r="A224" s="9"/>
+      <c r="B224" s="9"/>
+      <c r="C224" s="9"/>
       <c r="D224" s="15"/>
       <c r="E224" s="26"/>
       <c r="F224" s="15"/>
@@ -67535,7 +67529,15 @@
         <v/>
       </c>
       <c r="S227" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="S227" si="32">IF(
+  OR(
+    $H227="",
+    $H227="-",
+    COUNTIF(カテゴリ,$H227)&gt;0
+  ),
+  "",
+  "★NG★"
+)</f>
         <v/>
       </c>
       <c r="T227" s="13" t="str">
@@ -67658,7 +67660,7 @@
         <v/>
       </c>
       <c r="AC227" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="AC227" si="33">IF(AND($M227&lt;&gt;"",$M227&lt;&gt;"-")," (&amp;"&amp;$M227&amp;")","")</f>
         <v/>
       </c>
       <c r="AD227" s="13" t="str">
@@ -67692,11 +67694,23 @@
         <v/>
       </c>
       <c r="AG227" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="AG227" si="34">IF(
+  AND($A227&lt;&gt;"",$O227&lt;&gt;"-",$O227&lt;&gt;""),
+  (
+    "schtasks /create /tn """&amp;$O227&amp;""" /tr """&amp;$C227&amp;""" /sc daily /st "&amp;$P227&amp;" /rl highest"
+  ),
+  ""
+)</f>
         <v/>
       </c>
       <c r="AH227" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="AH227" si="35">IF(
+  AND($A227&lt;&gt;"",$O227&lt;&gt;"-",$O227&lt;&gt;""),
+  (
+    "schtasks /delete /tn """&amp;$O227&amp;""""
+  ),
+  ""
+)</f>
         <v/>
       </c>
       <c r="AI227" s="13" t="str">
@@ -67717,67 +67731,141 @@
         <v>179</v>
       </c>
     </row>
-    <row r="228" spans="1:36">
-      <c r="A228" s="9"/>
-      <c r="B228" s="9"/>
-      <c r="C228" s="9"/>
-      <c r="D228" s="15"/>
-      <c r="E228" s="26"/>
-      <c r="F228" s="15"/>
-      <c r="G228" s="15"/>
-      <c r="H228" s="9"/>
-      <c r="I228" s="15"/>
-      <c r="J228" s="15"/>
-      <c r="K228" s="15"/>
-      <c r="L228" s="93"/>
-      <c r="M228" s="94"/>
-      <c r="N228" s="15"/>
-      <c r="O228" s="26"/>
-      <c r="P228" s="157"/>
-      <c r="Q228" s="26"/>
-      <c r="R228" s="9" t="str">
+    <row r="228" spans="1:36" ht="1.5" customHeight="1">
+      <c r="A228" s="16"/>
+      <c r="B228" s="16"/>
+      <c r="C228" s="16"/>
+      <c r="D228" s="16"/>
+      <c r="E228" s="16"/>
+      <c r="F228" s="16"/>
+      <c r="G228" s="16"/>
+      <c r="H228" s="16"/>
+      <c r="I228" s="16"/>
+      <c r="J228" s="16"/>
+      <c r="K228" s="16"/>
+      <c r="L228" s="17"/>
+      <c r="M228" s="18"/>
+      <c r="N228" s="16"/>
+      <c r="O228" s="16"/>
+      <c r="P228" s="158"/>
+      <c r="Q228" s="96"/>
+      <c r="R228" s="16"/>
+      <c r="S228" s="16"/>
+      <c r="T228" s="17"/>
+      <c r="U228" s="16"/>
+      <c r="V228" s="17"/>
+      <c r="W228" s="17"/>
+      <c r="X228" s="18"/>
+      <c r="Y228" s="17"/>
+      <c r="Z228" s="18"/>
+      <c r="AA228" s="17"/>
+      <c r="AB228" s="16"/>
+      <c r="AC228" s="90"/>
+      <c r="AD228" s="17"/>
+      <c r="AE228" s="17"/>
+      <c r="AF228" s="16"/>
+      <c r="AG228" s="17"/>
+      <c r="AH228" s="17"/>
+      <c r="AI228" s="17"/>
+      <c r="AJ228" s="91" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="230" spans="1:36">
+      <c r="A230" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="B230" s="9" t="s">
+        <v>793</v>
+      </c>
+      <c r="C230" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="D230" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E230" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="F230" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="G230" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="H230" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="I230" s="15" t="s">
+        <v>849</v>
+      </c>
+      <c r="J230" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="K230" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="L230" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="M230" s="94" t="s">
+        <v>553</v>
+      </c>
+      <c r="N230" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="O230" s="26" t="s">
+        <v>1246</v>
+      </c>
+      <c r="P230" s="157" t="s">
+        <v>1246</v>
+      </c>
+      <c r="Q230" s="26" t="s">
+        <v>943</v>
+      </c>
+      <c r="R230" s="9" t="str">
         <f>IF(
   AND(
-    $A228&lt;&gt;"",
-    COUNTIF(C:C,$A228)&gt;1
+    $A230&lt;&gt;"",
+    COUNTIF(C:C,$A230)&gt;1
   ),
   "★NG★",
   ""
 )</f>
         <v/>
       </c>
-      <c r="S228" s="9" t="str">
-        <f t="shared" ref="S228" si="32">IF(
+      <c r="S230" s="9" t="str">
+        <f t="shared" ref="S230:S235" si="36">IF(
   OR(
-    $H228="",
-    $H228="-",
-    COUNTIF(カテゴリ,$H228)&gt;0
+    $H230="",
+    $H230="-",
+    COUNTIF(カテゴリ,$H230)&gt;0
   ),
   "",
   "★NG★"
 )</f>
         <v/>
       </c>
-      <c r="T228" s="13" t="str">
-        <f>IF(
-  AND($A228&lt;&gt;"",$I228="○"),
-  (
-    "mkdir """&amp;V228&amp;""" &amp; "
+      <c r="T230" s="13" t="str">
+        <f ca="1">IF(
+  AND($A230&lt;&gt;"",$I230="○"),
+  (
+    "mkdir """&amp;V230&amp;""" &amp; "
   )&amp;(
     """"&amp;shortcut設定!$F$7&amp;""""&amp;
-    " """&amp;V228&amp;"\"&amp;$A228&amp;"（"&amp;$B228&amp;"）.lnk"""&amp;
-    " """&amp;$C228&amp;""""&amp;
-    IF($D228="-"," """""," """&amp;$D228&amp;"""")&amp;
-    IF($E228="-"," """""," """&amp;$E228&amp;"""")
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="U228" s="9" t="str">
-        <f>IFERROR(
+    " """&amp;V230&amp;"\"&amp;$A230&amp;"（"&amp;$B230&amp;"）.lnk"""&amp;
+    " """&amp;$C230&amp;""""&amp;
+    IF($D230="-"," """""," """&amp;$D230&amp;"""")&amp;
+    IF($E230="-"," """""," """&amp;$E230&amp;"""")
+  ),
+  ""
+)</f>
+        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\153_Picture_Edit" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\153_Picture_Edit\iMazingConverter（HEIC→JPG変換）.lnk" "C:\prg\DigiDNA\iMazing Converter\iMazing Converter.exe" "" ""</v>
+      </c>
+      <c r="U230" s="9" t="str">
+        <f ca="1">IFERROR(
   VLOOKUP(
-    $H228,
+    $H230,
     shortcut設定!$F:$J,
     MATCH(
       "ProgramsIndex",
@@ -67788,83 +67876,83 @@
   ),
   ""
 )</f>
-        <v/>
-      </c>
-      <c r="V228" s="13" t="str">
-        <f>IF(
-  AND($A228&lt;&gt;"",$I228="○"),
-  shortcut設定!$F$4&amp;"\"&amp;U228&amp;"_"&amp;H228,
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="W228" s="13" t="str">
-        <f>IF(
-  AND($A228&lt;&gt;"",$J228&lt;&gt;"-",$J228&lt;&gt;""),
+        <v>153</v>
+      </c>
+      <c r="V230" s="13" t="str">
+        <f ca="1">IF(
+  AND($A230&lt;&gt;"",$I230="○"),
+  shortcut設定!$F$4&amp;"\"&amp;U230&amp;"_"&amp;H230,
+  ""
+)</f>
+        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\153_Picture_Edit</v>
+      </c>
+      <c r="W230" s="13" t="str">
+        <f>IF(
+  AND($A230&lt;&gt;"",$J230&lt;&gt;"-",$J230&lt;&gt;""),
   (
     "mkdir """&amp;shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$8&amp;""" &amp; "
   )&amp;(
     """"&amp;shortcut設定!$F$7&amp;""""&amp;
-    " """&amp;$X228&amp;""""&amp;
-    " """&amp;$C228&amp;""""&amp;
-    IF($D228="-"," """""," """&amp;$D228&amp;"""")&amp;
-    IF($E228="-"," """""," """&amp;$E228&amp;"""")
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="X228" s="14" t="str">
-        <f>IF(
-  AND($A228&lt;&gt;"",$J228&lt;&gt;"-",$J228&lt;&gt;""),
-  shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$8&amp;"\"&amp;$J228&amp;"（"&amp;$B228&amp;"）.lnk",
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="Y228" s="13" t="str">
-        <f>IF(
-  AND($A228&lt;&gt;"",$K228&lt;&gt;"-",$K228&lt;&gt;""),
+    " """&amp;$X230&amp;""""&amp;
+    " """&amp;$C230&amp;""""&amp;
+    IF($D230="-"," """""," """&amp;$D230&amp;"""")&amp;
+    IF($E230="-"," """""," """&amp;$E230&amp;"""")
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="X230" s="14" t="str">
+        <f>IF(
+  AND($A230&lt;&gt;"",$J230&lt;&gt;"-",$J230&lt;&gt;""),
+  shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$8&amp;"\"&amp;$J230&amp;"（"&amp;$B230&amp;"）.lnk",
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="Y230" s="13" t="str">
+        <f>IF(
+  AND($A230&lt;&gt;"",$K230&lt;&gt;"-",$K230&lt;&gt;""),
   (
     "mkdir """&amp;shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$9&amp;""" &amp; "
   )&amp;(
     """"&amp;shortcut設定!$F$7&amp;""""&amp;
-    " """&amp;$Z228&amp;""""&amp;
-    " """&amp;$C228&amp;""""&amp;
-    IF($D228="-"," """""," """&amp;$D228&amp;"""")&amp;
-    IF($E228="-"," """""," """&amp;$E228&amp;"""")&amp;
-    IF($K228="-"," """""," """&amp;$K228&amp;"""")
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="Z228" s="14" t="str">
-        <f>IF(
-  AND($A228&lt;&gt;"",$K228&lt;&gt;"-",$K228&lt;&gt;""),
-  shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$9&amp;"\"&amp;$A228&amp;"（"&amp;$B228&amp;"）.lnk",
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AA228" s="13" t="str">
-        <f>IF(
-  AND($A228&lt;&gt;"",$L228&lt;&gt;"-",$L228&lt;&gt;""),
-  (
-    """"&amp;shortcut設定!$F$7&amp;""""&amp;
-    " """&amp;$AD228&amp;""""&amp;
-    " """&amp;$C228&amp;""""&amp;
-    IF($D228="-"," """""," """&amp;$D228&amp;"""")&amp;
-    IF($E228="-"," """""," """&amp;$E228&amp;"""")
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AB228" s="9" t="str">
-        <f>IFERROR(
+    " """&amp;$Z230&amp;""""&amp;
+    " """&amp;$C230&amp;""""&amp;
+    IF($D230="-"," """""," """&amp;$D230&amp;"""")&amp;
+    IF($E230="-"," """""," """&amp;$E230&amp;"""")&amp;
+    IF($K230="-"," """""," """&amp;$K230&amp;"""")
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="Z230" s="14" t="str">
+        <f>IF(
+  AND($A230&lt;&gt;"",$K230&lt;&gt;"-",$K230&lt;&gt;""),
+  shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$9&amp;"\"&amp;$A230&amp;"（"&amp;$B230&amp;"）.lnk",
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AA230" s="13" t="str">
+        <f>IF(
+  AND($A230&lt;&gt;"",$L230&lt;&gt;"-",$L230&lt;&gt;""),
+  (
+    """"&amp;shortcut設定!$F$7&amp;""""&amp;
+    " """&amp;$AD230&amp;""""&amp;
+    " """&amp;$C230&amp;""""&amp;
+    IF($D230="-"," """""," """&amp;$D230&amp;"""")&amp;
+    IF($E230="-"," """""," """&amp;$E230&amp;"""")
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AB230" s="9" t="str">
+        <f ca="1">IFERROR(
   VLOOKUP(
-    $H228,
+    $H230,
     shortcut設定!$F:$J,
     MATCH(
       "ProgramsIndex",
@@ -67875,129 +67963,89 @@
   ),
   ""
 )</f>
-        <v/>
-      </c>
-      <c r="AC228" s="20" t="str">
-        <f t="shared" ref="AC228" si="33">IF(AND($M228&lt;&gt;"",$M228&lt;&gt;"-")," (&amp;"&amp;$M228&amp;")","")</f>
-        <v/>
-      </c>
-      <c r="AD228" s="13" t="str">
-        <f>IF(
-  AND($A228&lt;&gt;"",$L228="○"),
-  shortcut設定!$F$5&amp;"\"&amp;AB228&amp;"_"&amp;A228&amp;"（"&amp;B228&amp;"）"&amp;AC228&amp;".lnk",
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AE228" s="13" t="str">
-        <f>IF(
-  AND($A228&lt;&gt;"",$N228="○"),
-  (
-    """"&amp;shortcut設定!$F$7&amp;""""&amp;
-    " """&amp;$AF228&amp;""""&amp;
-    " """&amp;$C228&amp;""""&amp;
-    IF($D228="-"," """""," """&amp;$D228&amp;"""")&amp;
-    IF($E228="-"," """""," """&amp;$E228&amp;"""")
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AF228" s="9" t="str">
-        <f>IF(
-  AND($A228&lt;&gt;"",$N228="○"),
-  shortcut設定!$F$6&amp;"\"&amp;A228&amp;"（"&amp;B228&amp;"）.lnk",
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AG228" s="13" t="str">
-        <f t="shared" ref="AG228" si="34">IF(
-  AND($A228&lt;&gt;"",$O228&lt;&gt;"-",$O228&lt;&gt;""),
-  (
-    "schtasks /create /tn """&amp;$O228&amp;""" /tr """&amp;$C228&amp;""" /sc daily /st "&amp;$P228&amp;" /rl highest"
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AH228" s="13" t="str">
-        <f t="shared" ref="AH228" si="35">IF(
-  AND($A228&lt;&gt;"",$O228&lt;&gt;"-",$O228&lt;&gt;""),
-  (
-    "schtasks /delete /tn """&amp;$O228&amp;""""
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AI228" s="13" t="str">
-        <f>IF(
-  AND($A228&lt;&gt;"",$Q228&lt;&gt;"-",$Q228&lt;&gt;""),
-  (
-    """"&amp;shortcut設定!$F$7&amp;""""&amp;
-    " """&amp;$Q228&amp;".lnk"""&amp;
-    " """&amp;$C228&amp;""""&amp;
-    IF($D228="-"," """""," """&amp;$D228&amp;"""")&amp;
-    IF($E228="-"," """""," """&amp;$E228&amp;"""")
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AJ228" s="91" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="229" spans="1:36" ht="1.5" customHeight="1">
-      <c r="A229" s="16"/>
-      <c r="B229" s="16"/>
-      <c r="C229" s="16"/>
-      <c r="D229" s="16"/>
-      <c r="E229" s="16"/>
-      <c r="F229" s="16"/>
-      <c r="G229" s="16"/>
-      <c r="H229" s="16"/>
-      <c r="I229" s="16"/>
-      <c r="J229" s="16"/>
-      <c r="K229" s="16"/>
-      <c r="L229" s="17"/>
-      <c r="M229" s="18"/>
-      <c r="N229" s="16"/>
-      <c r="O229" s="16"/>
-      <c r="P229" s="158"/>
-      <c r="Q229" s="96"/>
-      <c r="R229" s="16"/>
-      <c r="S229" s="16"/>
-      <c r="T229" s="17"/>
-      <c r="U229" s="16"/>
-      <c r="V229" s="17"/>
-      <c r="W229" s="17"/>
-      <c r="X229" s="18"/>
-      <c r="Y229" s="17"/>
-      <c r="Z229" s="18"/>
-      <c r="AA229" s="17"/>
-      <c r="AB229" s="16"/>
-      <c r="AC229" s="90"/>
-      <c r="AD229" s="17"/>
-      <c r="AE229" s="17"/>
-      <c r="AF229" s="16"/>
-      <c r="AG229" s="17"/>
-      <c r="AH229" s="17"/>
-      <c r="AI229" s="17"/>
-      <c r="AJ229" s="91" t="s">
+        <v>153</v>
+      </c>
+      <c r="AC230" s="20" t="str">
+        <f t="shared" ref="AC230:AC235" si="37">IF(AND($M230&lt;&gt;"",$M230&lt;&gt;"-")," (&amp;"&amp;$M230&amp;")","")</f>
+        <v/>
+      </c>
+      <c r="AD230" s="13" t="str">
+        <f>IF(
+  AND($A230&lt;&gt;"",$L230="○"),
+  shortcut設定!$F$5&amp;"\"&amp;AB230&amp;"_"&amp;A230&amp;"（"&amp;B230&amp;"）"&amp;AC230&amp;".lnk",
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AE230" s="13" t="str">
+        <f>IF(
+  AND($A230&lt;&gt;"",$N230="○"),
+  (
+    """"&amp;shortcut設定!$F$7&amp;""""&amp;
+    " """&amp;$AF230&amp;""""&amp;
+    " """&amp;$C230&amp;""""&amp;
+    IF($D230="-"," """""," """&amp;$D230&amp;"""")&amp;
+    IF($E230="-"," """""," """&amp;$E230&amp;"""")
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AF230" s="9" t="str">
+        <f>IF(
+  AND($A230&lt;&gt;"",$N230="○"),
+  shortcut設定!$F$6&amp;"\"&amp;A230&amp;"（"&amp;B230&amp;"）.lnk",
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AG230" s="13" t="str">
+        <f t="shared" ref="AG230:AG235" si="38">IF(
+  AND($A230&lt;&gt;"",$O230&lt;&gt;"-",$O230&lt;&gt;""),
+  (
+    "schtasks /create /tn """&amp;$O230&amp;""" /tr """&amp;$C230&amp;""" /sc daily /st "&amp;$P230&amp;" /rl highest"
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AH230" s="13" t="str">
+        <f t="shared" ref="AH230:AH235" si="39">IF(
+  AND($A230&lt;&gt;"",$O230&lt;&gt;"-",$O230&lt;&gt;""),
+  (
+    "schtasks /delete /tn """&amp;$O230&amp;""""
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AI230" s="13" t="str">
+        <f>IF(
+  AND($A230&lt;&gt;"",$Q230&lt;&gt;"-",$Q230&lt;&gt;""),
+  (
+    """"&amp;shortcut設定!$F$7&amp;""""&amp;
+    " """&amp;$Q230&amp;".lnk"""&amp;
+    " """&amp;$C230&amp;""""&amp;
+    IF($D230="-"," """""," """&amp;$D230&amp;"""")&amp;
+    IF($E230="-"," """""," """&amp;$E230&amp;"""")
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AJ230" s="91" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="231" spans="1:36">
       <c r="A231" s="9" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C231" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D231" s="15" t="s">
         <v>40</v>
@@ -68006,13 +68054,13 @@
         <v>40</v>
       </c>
       <c r="F231" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="G231" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="G231" s="15" t="s">
-        <v>154</v>
-      </c>
       <c r="H231" s="9" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="I231" s="15" t="s">
         <v>849</v>
@@ -68053,15 +68101,7 @@
         <v/>
       </c>
       <c r="S231" s="9" t="str">
-        <f t="shared" ref="S231:S236" si="36">IF(
-  OR(
-    $H231="",
-    $H231="-",
-    COUNTIF(カテゴリ,$H231)&gt;0
-  ),
-  "",
-  "★NG★"
-)</f>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="T231" s="13" t="str">
@@ -68078,7 +68118,7 @@
   ),
   ""
 )</f>
-        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\153_Picture_Edit" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\153_Picture_Edit\iMazingConverter（HEIC→JPG変換）.lnk" "C:\prg\DigiDNA\iMazing Converter\iMazing Converter.exe" "" ""</v>
+        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global\VcXsrv（X11サーバー）.lnk" "C:\prg\VcXsrv\xlaunch.exe" "" ""</v>
       </c>
       <c r="U231" s="9" t="str">
         <f ca="1">IFERROR(
@@ -68094,7 +68134,7 @@
   ),
   ""
 )</f>
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="V231" s="13" t="str">
         <f ca="1">IF(
@@ -68102,7 +68142,7 @@
   shortcut設定!$F$4&amp;"\"&amp;U231&amp;"_"&amp;H231,
   ""
 )</f>
-        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\153_Picture_Edit</v>
+        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global</v>
       </c>
       <c r="W231" s="13" t="str">
         <f>IF(
@@ -68181,10 +68221,10 @@
   ),
   ""
 )</f>
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="AC231" s="20" t="str">
-        <f t="shared" ref="AC231:AC236" si="37">IF(AND($M231&lt;&gt;"",$M231&lt;&gt;"-")," (&amp;"&amp;$M231&amp;")","")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD231" s="13" t="str">
@@ -68218,23 +68258,11 @@
         <v/>
       </c>
       <c r="AG231" s="13" t="str">
-        <f t="shared" ref="AG231:AG236" si="38">IF(
-  AND($A231&lt;&gt;"",$O231&lt;&gt;"-",$O231&lt;&gt;""),
-  (
-    "schtasks /create /tn """&amp;$O231&amp;""" /tr """&amp;$C231&amp;""" /sc daily /st "&amp;$P231&amp;" /rl highest"
-  ),
-  ""
-)</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AH231" s="13" t="str">
-        <f t="shared" ref="AH231:AH236" si="39">IF(
-  AND($A231&lt;&gt;"",$O231&lt;&gt;"-",$O231&lt;&gt;""),
-  (
-    "schtasks /delete /tn """&amp;$O231&amp;""""
-  ),
-  ""
-)</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AI231" s="13" t="str">
@@ -68257,55 +68285,55 @@
     </row>
     <row r="232" spans="1:36">
       <c r="A232" s="9" t="s">
-        <v>657</v>
+        <v>1284</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>794</v>
+        <v>1285</v>
       </c>
       <c r="C232" s="9" t="s">
-        <v>167</v>
+        <v>1283</v>
       </c>
       <c r="D232" s="15" t="s">
         <v>40</v>
       </c>
       <c r="E232" s="26" t="s">
+        <v>1286</v>
+      </c>
+      <c r="F232" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G232" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="H232" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I232" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="J232" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F232" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="G232" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="H232" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I232" s="15" t="s">
-        <v>849</v>
-      </c>
-      <c r="J232" s="15" t="s">
-        <v>66</v>
-      </c>
       <c r="K232" s="15" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="L232" s="93" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="M232" s="94" t="s">
-        <v>553</v>
+        <v>40</v>
       </c>
       <c r="N232" s="15" t="s">
-        <v>66</v>
+        <v>942</v>
       </c>
       <c r="O232" s="26" t="s">
-        <v>1246</v>
+        <v>40</v>
       </c>
       <c r="P232" s="157" t="s">
-        <v>1246</v>
+        <v>40</v>
       </c>
       <c r="Q232" s="26" t="s">
-        <v>943</v>
+        <v>40</v>
       </c>
       <c r="R232" s="9" t="str">
         <f>IF(
@@ -68336,7 +68364,7 @@
   ),
   ""
 )</f>
-        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global\VcXsrv（X11サーバー）.lnk" "C:\prg\VcXsrv\xlaunch.exe" "" ""</v>
+        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\172_Utility_Other" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\172_Utility_Other\壁カレ４（デスクトップカレンダー）.lnk" "C:\prg\KABE4\KABE4.exe" "" "C:\prg\KABE4"</v>
       </c>
       <c r="U232" s="9" t="str">
         <f ca="1">IFERROR(
@@ -68352,7 +68380,7 @@
   ),
   ""
 )</f>
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="V232" s="13" t="str">
         <f ca="1">IF(
@@ -68360,7 +68388,7 @@
   shortcut設定!$F$4&amp;"\"&amp;U232&amp;"_"&amp;H232,
   ""
 )</f>
-        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global</v>
+        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\172_Utility_Other</v>
       </c>
       <c r="W232" s="13" t="str">
         <f>IF(
@@ -68439,7 +68467,7 @@
   ),
   ""
 )</f>
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="AC232" s="20" t="str">
         <f t="shared" si="37"/>
@@ -68503,55 +68531,55 @@
     </row>
     <row r="233" spans="1:36">
       <c r="A233" s="9" t="s">
-        <v>1284</v>
+        <v>56</v>
       </c>
       <c r="B233" s="9" t="s">
-        <v>1285</v>
+        <v>791</v>
       </c>
       <c r="C233" s="9" t="s">
-        <v>1283</v>
+        <v>95</v>
       </c>
       <c r="D233" s="15" t="s">
         <v>40</v>
       </c>
       <c r="E233" s="26" t="s">
-        <v>1286</v>
+        <v>40</v>
       </c>
       <c r="F233" s="15" t="s">
-        <v>28</v>
+        <v>171</v>
       </c>
       <c r="G233" s="15" t="s">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="H233" s="9" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="I233" s="15" t="s">
-        <v>0</v>
+        <v>849</v>
       </c>
       <c r="J233" s="15" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="K233" s="15" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="L233" s="93" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="M233" s="94" t="s">
-        <v>40</v>
+        <v>553</v>
       </c>
       <c r="N233" s="15" t="s">
-        <v>942</v>
+        <v>66</v>
       </c>
       <c r="O233" s="26" t="s">
-        <v>40</v>
+        <v>1246</v>
       </c>
       <c r="P233" s="157" t="s">
-        <v>40</v>
+        <v>1246</v>
       </c>
       <c r="Q233" s="26" t="s">
-        <v>40</v>
+        <v>943</v>
       </c>
       <c r="R233" s="9" t="str">
         <f>IF(
@@ -68582,7 +68610,7 @@
   ),
   ""
 )</f>
-        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\172_Utility_Other" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\172_Utility_Other\壁カレ４（デスクトップカレンダー）.lnk" "C:\prg\KABE4\KABE4.exe" "" "C:\prg\KABE4"</v>
+        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\143_Movie_Edit" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\143_Movie_Edit\DVD Shrink（DVDリッピング）.lnk" "C:\prg\DVD Shrink\DVD Shrink 3.2.exe" "" ""</v>
       </c>
       <c r="U233" s="9" t="str">
         <f ca="1">IFERROR(
@@ -68598,7 +68626,7 @@
   ),
   ""
 )</f>
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="V233" s="13" t="str">
         <f ca="1">IF(
@@ -68606,7 +68634,7 @@
   shortcut設定!$F$4&amp;"\"&amp;U233&amp;"_"&amp;H233,
   ""
 )</f>
-        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\172_Utility_Other</v>
+        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\143_Movie_Edit</v>
       </c>
       <c r="W233" s="13" t="str">
         <f>IF(
@@ -68685,7 +68713,7 @@
   ),
   ""
 )</f>
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="AC233" s="20" t="str">
         <f t="shared" si="37"/>
@@ -68749,13 +68777,13 @@
     </row>
     <row r="234" spans="1:36">
       <c r="A234" s="9" t="s">
-        <v>56</v>
+        <v>654</v>
       </c>
       <c r="B234" s="9" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C234" s="9" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="D234" s="15" t="s">
         <v>40</v>
@@ -68770,7 +68798,7 @@
         <v>154</v>
       </c>
       <c r="H234" s="9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I234" s="15" t="s">
         <v>849</v>
@@ -68828,7 +68856,7 @@
   ),
   ""
 )</f>
-        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\143_Movie_Edit" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\143_Movie_Edit\DVD Shrink（DVDリッピング）.lnk" "C:\prg\DVD Shrink\DVD Shrink 3.2.exe" "" ""</v>
+        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\162_Network_Local" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\162_Network_Local\UltraVNC Viewer（RDP-Mac）.lnk" "C:\prg\uvnc bvba\UltraVNC\vncviewer.exe" "" ""</v>
       </c>
       <c r="U234" s="9" t="str">
         <f ca="1">IFERROR(
@@ -68844,7 +68872,7 @@
   ),
   ""
 )</f>
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="V234" s="13" t="str">
         <f ca="1">IF(
@@ -68852,7 +68880,7 @@
   shortcut設定!$F$4&amp;"\"&amp;U234&amp;"_"&amp;H234,
   ""
 )</f>
-        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\143_Movie_Edit</v>
+        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\162_Network_Local</v>
       </c>
       <c r="W234" s="13" t="str">
         <f>IF(
@@ -68931,7 +68959,7 @@
   ),
   ""
 )</f>
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="AC234" s="20" t="str">
         <f t="shared" si="37"/>
@@ -68995,46 +69023,46 @@
     </row>
     <row r="235" spans="1:36">
       <c r="A235" s="9" t="s">
-        <v>654</v>
+        <v>1169</v>
       </c>
       <c r="B235" s="9" t="s">
-        <v>789</v>
+        <v>1170</v>
       </c>
       <c r="C235" s="9" t="s">
-        <v>161</v>
+        <v>1168</v>
       </c>
       <c r="D235" s="15" t="s">
-        <v>40</v>
+        <v>942</v>
       </c>
       <c r="E235" s="26" t="s">
         <v>40</v>
       </c>
       <c r="F235" s="15" t="s">
-        <v>171</v>
+        <v>28</v>
       </c>
       <c r="G235" s="15" t="s">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="H235" s="9" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="I235" s="15" t="s">
-        <v>849</v>
+        <v>0</v>
       </c>
       <c r="J235" s="15" t="s">
-        <v>66</v>
+        <v>942</v>
       </c>
       <c r="K235" s="15" t="s">
-        <v>66</v>
+        <v>942</v>
       </c>
       <c r="L235" s="93" t="s">
-        <v>66</v>
+        <v>942</v>
       </c>
       <c r="M235" s="94" t="s">
-        <v>553</v>
+        <v>942</v>
       </c>
       <c r="N235" s="15" t="s">
-        <v>66</v>
+        <v>942</v>
       </c>
       <c r="O235" s="26" t="s">
         <v>1246</v>
@@ -69043,7 +69071,7 @@
         <v>1246</v>
       </c>
       <c r="Q235" s="26" t="s">
-        <v>943</v>
+        <v>40</v>
       </c>
       <c r="R235" s="9" t="str">
         <f>IF(
@@ -69074,7 +69102,7 @@
   ),
   ""
 )</f>
-        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\162_Network_Local" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\162_Network_Local\UltraVNC Viewer（RDP-Mac）.lnk" "C:\prg\uvnc bvba\UltraVNC\vncviewer.exe" "" ""</v>
+        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global\Steam（ゲーム）.lnk" "C:\prg\Steam\steam.exe" "" ""</v>
       </c>
       <c r="U235" s="9" t="str">
         <f ca="1">IFERROR(
@@ -69090,7 +69118,7 @@
   ),
   ""
 )</f>
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="V235" s="13" t="str">
         <f ca="1">IF(
@@ -69098,7 +69126,7 @@
   shortcut設定!$F$4&amp;"\"&amp;U235&amp;"_"&amp;H235,
   ""
 )</f>
-        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\162_Network_Local</v>
+        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global</v>
       </c>
       <c r="W235" s="13" t="str">
         <f>IF(
@@ -69177,7 +69205,7 @@
   ),
   ""
 )</f>
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AC235" s="20" t="str">
         <f t="shared" si="37"/>
@@ -69239,263 +69267,17 @@
         <v>179</v>
       </c>
     </row>
-    <row r="236" spans="1:36">
-      <c r="A236" s="9" t="s">
-        <v>1169</v>
-      </c>
-      <c r="B236" s="9" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C236" s="9" t="s">
-        <v>1168</v>
-      </c>
-      <c r="D236" s="15" t="s">
-        <v>942</v>
-      </c>
-      <c r="E236" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="F236" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="G236" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="H236" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I236" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="J236" s="15" t="s">
-        <v>942</v>
-      </c>
-      <c r="K236" s="15" t="s">
-        <v>942</v>
-      </c>
-      <c r="L236" s="93" t="s">
-        <v>942</v>
-      </c>
-      <c r="M236" s="94" t="s">
-        <v>942</v>
-      </c>
-      <c r="N236" s="15" t="s">
-        <v>942</v>
-      </c>
-      <c r="O236" s="26" t="s">
-        <v>1246</v>
-      </c>
-      <c r="P236" s="157" t="s">
-        <v>1246</v>
-      </c>
-      <c r="Q236" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="R236" s="9" t="str">
-        <f>IF(
-  AND(
-    $A236&lt;&gt;"",
-    COUNTIF(C:C,$A236)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="S236" s="9" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="T236" s="13" t="str">
-        <f ca="1">IF(
-  AND($A236&lt;&gt;"",$I236="○"),
-  (
-    "mkdir """&amp;V236&amp;""" &amp; "
-  )&amp;(
-    """"&amp;shortcut設定!$F$7&amp;""""&amp;
-    " """&amp;V236&amp;"\"&amp;$A236&amp;"（"&amp;$B236&amp;"）.lnk"""&amp;
-    " """&amp;$C236&amp;""""&amp;
-    IF($D236="-"," """""," """&amp;$D236&amp;"""")&amp;
-    IF($E236="-"," """""," """&amp;$E236&amp;"""")
-  ),
-  ""
-)</f>
-        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global\Steam（ゲーム）.lnk" "C:\prg\Steam\steam.exe" "" ""</v>
-      </c>
-      <c r="U236" s="9" t="str">
-        <f ca="1">IFERROR(
-  VLOOKUP(
-    $H236,
-    shortcut設定!$F:$J,
-    MATCH(
-      "ProgramsIndex",
-      shortcut設定!$F$12:$J$12,
-      0
-    ),
-    FALSE
-  ),
-  ""
-)</f>
-        <v>161</v>
-      </c>
-      <c r="V236" s="13" t="str">
-        <f ca="1">IF(
-  AND($A236&lt;&gt;"",$I236="○"),
-  shortcut設定!$F$4&amp;"\"&amp;U236&amp;"_"&amp;H236,
-  ""
-)</f>
-        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global</v>
-      </c>
-      <c r="W236" s="13" t="str">
-        <f>IF(
-  AND($A236&lt;&gt;"",$J236&lt;&gt;"-",$J236&lt;&gt;""),
-  (
-    "mkdir """&amp;shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$8&amp;""" &amp; "
-  )&amp;(
-    """"&amp;shortcut設定!$F$7&amp;""""&amp;
-    " """&amp;$X236&amp;""""&amp;
-    " """&amp;$C236&amp;""""&amp;
-    IF($D236="-"," """""," """&amp;$D236&amp;"""")&amp;
-    IF($E236="-"," """""," """&amp;$E236&amp;"""")
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="X236" s="14" t="str">
-        <f>IF(
-  AND($A236&lt;&gt;"",$J236&lt;&gt;"-",$J236&lt;&gt;""),
-  shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$8&amp;"\"&amp;$J236&amp;"（"&amp;$B236&amp;"）.lnk",
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="Y236" s="13" t="str">
-        <f>IF(
-  AND($A236&lt;&gt;"",$K236&lt;&gt;"-",$K236&lt;&gt;""),
-  (
-    "mkdir """&amp;shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$9&amp;""" &amp; "
-  )&amp;(
-    """"&amp;shortcut設定!$F$7&amp;""""&amp;
-    " """&amp;$Z236&amp;""""&amp;
-    " """&amp;$C236&amp;""""&amp;
-    IF($D236="-"," """""," """&amp;$D236&amp;"""")&amp;
-    IF($E236="-"," """""," """&amp;$E236&amp;"""")&amp;
-    IF($K236="-"," """""," """&amp;$K236&amp;"""")
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="Z236" s="14" t="str">
-        <f>IF(
-  AND($A236&lt;&gt;"",$K236&lt;&gt;"-",$K236&lt;&gt;""),
-  shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$9&amp;"\"&amp;$A236&amp;"（"&amp;$B236&amp;"）.lnk",
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AA236" s="13" t="str">
-        <f>IF(
-  AND($A236&lt;&gt;"",$L236&lt;&gt;"-",$L236&lt;&gt;""),
-  (
-    """"&amp;shortcut設定!$F$7&amp;""""&amp;
-    " """&amp;$AD236&amp;""""&amp;
-    " """&amp;$C236&amp;""""&amp;
-    IF($D236="-"," """""," """&amp;$D236&amp;"""")&amp;
-    IF($E236="-"," """""," """&amp;$E236&amp;"""")
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AB236" s="9" t="str">
-        <f ca="1">IFERROR(
-  VLOOKUP(
-    $H236,
-    shortcut設定!$F:$J,
-    MATCH(
-      "ProgramsIndex",
-      shortcut設定!$F$12:$J$12,
-      0
-    ),
-    FALSE
-  ),
-  ""
-)</f>
-        <v>161</v>
-      </c>
-      <c r="AC236" s="20" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="AD236" s="13" t="str">
-        <f>IF(
-  AND($A236&lt;&gt;"",$L236="○"),
-  shortcut設定!$F$5&amp;"\"&amp;AB236&amp;"_"&amp;A236&amp;"（"&amp;B236&amp;"）"&amp;AC236&amp;".lnk",
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AE236" s="13" t="str">
-        <f>IF(
-  AND($A236&lt;&gt;"",$N236="○"),
-  (
-    """"&amp;shortcut設定!$F$7&amp;""""&amp;
-    " """&amp;$AF236&amp;""""&amp;
-    " """&amp;$C236&amp;""""&amp;
-    IF($D236="-"," """""," """&amp;$D236&amp;"""")&amp;
-    IF($E236="-"," """""," """&amp;$E236&amp;"""")
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AF236" s="9" t="str">
-        <f>IF(
-  AND($A236&lt;&gt;"",$N236="○"),
-  shortcut設定!$F$6&amp;"\"&amp;A236&amp;"（"&amp;B236&amp;"）.lnk",
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AG236" s="13" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AH236" s="13" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AI236" s="13" t="str">
-        <f>IF(
-  AND($A236&lt;&gt;"",$Q236&lt;&gt;"-",$Q236&lt;&gt;""),
-  (
-    """"&amp;shortcut設定!$F$7&amp;""""&amp;
-    " """&amp;$Q236&amp;".lnk"""&amp;
-    " """&amp;$C236&amp;""""&amp;
-    IF($D236="-"," """""," """&amp;$D236&amp;"""")&amp;
-    IF($E236="-"," """""," """&amp;$E236&amp;"""")
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AJ236" s="91" t="s">
-        <v>179</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A9:AJ229" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A9:AJ228" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <phoneticPr fontId="2"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H231:H236 H206:H228 H11:H205" xr:uid="{00000000-0002-0000-0200-000000000000}">
+  <dataValidations disablePrompts="1" count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H230:H235 H11:H227" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>カテゴリ</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F231:G236 F206:G228 F11:G205" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F230:G235 F11:G227" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"○,×"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I231:I236 L231:L236 N231:N236 I206:I228 I11:I205 L206:L228 L11:L205 N206:N228 N11:N205" xr:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I230:I235 L230:L235 N230:N235 N11:N227 L11:L227 I11:I227" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"○,-"</formula1>
     </dataValidation>
   </dataValidations>
@@ -70495,7 +70277,7 @@
         <v>884</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1537</v>
+        <v>1544</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>154</v>

--- a/PC移行時チェックリスト.xlsx
+++ b/PC移行時チェックリスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EEE659D-2B08-464A-A562-44EEA2B195FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F01687A-D9EF-4AA0-860B-F80D91783400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28815" yWindow="-5580" windowWidth="38385" windowHeight="41970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13862,7 +13862,7 @@
         <v>938</v>
       </c>
       <c r="R11" s="9" t="str">
-        <f>IF(
+        <f t="shared" ref="R11:R74" si="0">IF(
   AND(
     $A11&lt;&gt;"",
     COUNTIF(C:C,$A11)&gt;1
@@ -13873,7 +13873,7 @@
         <v/>
       </c>
       <c r="S11" s="9" t="str">
-        <f t="shared" ref="S11:S42" si="0">IF(
+        <f t="shared" ref="S11:S42" si="1">IF(
   OR(
     $H11="",
     $H11="-",
@@ -14004,7 +14004,7 @@
         <v>113</v>
       </c>
       <c r="AC11" s="20" t="str">
-        <f t="shared" ref="AC11:AC42" si="1">IF(AND($M11&lt;&gt;"",$M11&lt;&gt;"-")," (&amp;"&amp;$M11&amp;")","")</f>
+        <f t="shared" ref="AC11:AC42" si="2">IF(AND($M11&lt;&gt;"",$M11&lt;&gt;"-")," (&amp;"&amp;$M11&amp;")","")</f>
         <v/>
       </c>
       <c r="AD11" s="13" t="str">
@@ -14038,7 +14038,7 @@
         <v/>
       </c>
       <c r="AG11" s="13" t="str">
-        <f t="shared" ref="AG11:AG42" si="2">IF(
+        <f t="shared" ref="AG11:AG42" si="3">IF(
   AND($A11&lt;&gt;"",$O11&lt;&gt;"-",$O11&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O11&amp;""" /tr """&amp;$C11&amp;""" /sc daily /st "&amp;$P11&amp;" /rl highest"
@@ -14048,7 +14048,7 @@
         <v/>
       </c>
       <c r="AH11" s="13" t="str">
-        <f t="shared" ref="AH11:AH42" si="3">IF(
+        <f t="shared" ref="AH11:AH42" si="4">IF(
   AND($A11&lt;&gt;"",$O11&lt;&gt;"-",$O11&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O11&amp;""""
@@ -14128,18 +14128,11 @@
         <v>938</v>
       </c>
       <c r="R12" s="9" t="str">
-        <f>IF(
-  AND(
-    $A12&lt;&gt;"",
-    COUNTIF(C:C,$A12)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S12" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T12" s="13" t="str">
@@ -14262,7 +14255,7 @@
         <v>122</v>
       </c>
       <c r="AC12" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD12" s="13" t="str">
@@ -14296,11 +14289,11 @@
         <v/>
       </c>
       <c r="AG12" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH12" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI12" s="13" t="str">
@@ -14374,18 +14367,11 @@
         <v>938</v>
       </c>
       <c r="R13" s="9" t="str">
-        <f>IF(
-  AND(
-    $A13&lt;&gt;"",
-    COUNTIF(C:C,$A13)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S13" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T13" s="13" t="str">
@@ -14508,7 +14494,7 @@
         <v>142</v>
       </c>
       <c r="AC13" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD13" s="13" t="str">
@@ -14542,11 +14528,11 @@
         <v/>
       </c>
       <c r="AG13" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH13" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI13" s="13" t="str">
@@ -14620,18 +14606,11 @@
         <v>938</v>
       </c>
       <c r="R14" s="9" t="str">
-        <f>IF(
-  AND(
-    $A14&lt;&gt;"",
-    COUNTIF(C:C,$A14)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S14" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T14" s="13" t="str">
@@ -14754,7 +14733,7 @@
         <v>142</v>
       </c>
       <c r="AC14" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD14" s="13" t="str">
@@ -14788,11 +14767,11 @@
         <v/>
       </c>
       <c r="AG14" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH14" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI14" s="13" t="str">
@@ -14866,18 +14845,11 @@
         <v>938</v>
       </c>
       <c r="R15" s="9" t="str">
-        <f>IF(
-  AND(
-    $A15&lt;&gt;"",
-    COUNTIF(C:C,$A15)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S15" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T15" s="13" t="str">
@@ -15000,7 +14972,7 @@
         <v>121</v>
       </c>
       <c r="AC15" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD15" s="13" t="str">
@@ -15034,11 +15006,11 @@
         <v/>
       </c>
       <c r="AG15" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH15" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI15" s="13" t="str">
@@ -15113,18 +15085,11 @@
         <v>938</v>
       </c>
       <c r="R16" s="9" t="str">
-        <f>IF(
-  AND(
-    $A16&lt;&gt;"",
-    COUNTIF(C:C,$A16)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S16" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T16" s="13" t="str">
@@ -15247,7 +15212,7 @@
         <v>121</v>
       </c>
       <c r="AC16" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD16" s="13" t="str">
@@ -15281,11 +15246,11 @@
         <v/>
       </c>
       <c r="AG16" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH16" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI16" s="13" t="str">
@@ -15359,18 +15324,11 @@
         <v>938</v>
       </c>
       <c r="R17" s="9" t="str">
-        <f>IF(
-  AND(
-    $A17&lt;&gt;"",
-    COUNTIF(C:C,$A17)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S17" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T17" s="13" t="str">
@@ -15493,7 +15451,7 @@
         <v>172</v>
       </c>
       <c r="AC17" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD17" s="13" t="str">
@@ -15527,11 +15485,11 @@
         <v/>
       </c>
       <c r="AG17" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH17" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI17" s="13" t="str">
@@ -15605,18 +15563,11 @@
         <v>938</v>
       </c>
       <c r="R18" s="9" t="str">
-        <f>IF(
-  AND(
-    $A18&lt;&gt;"",
-    COUNTIF(C:C,$A18)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S18" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T18" s="13" t="str">
@@ -15739,7 +15690,7 @@
         <v>161</v>
       </c>
       <c r="AC18" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD18" s="13" t="str">
@@ -15773,11 +15724,11 @@
         <v/>
       </c>
       <c r="AG18" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH18" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI18" s="13" t="str">
@@ -15851,18 +15802,11 @@
         <v>938</v>
       </c>
       <c r="R19" s="9" t="str">
-        <f>IF(
-  AND(
-    $A19&lt;&gt;"",
-    COUNTIF(C:C,$A19)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S19" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T19" s="13" t="str">
@@ -15985,7 +15929,7 @@
         <v>134</v>
       </c>
       <c r="AC19" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD19" s="13" t="str">
@@ -16019,11 +15963,11 @@
         <v/>
       </c>
       <c r="AG19" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH19" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI19" s="13" t="str">
@@ -16097,18 +16041,11 @@
         <v>938</v>
       </c>
       <c r="R20" s="9" t="str">
-        <f>IF(
-  AND(
-    $A20&lt;&gt;"",
-    COUNTIF(C:C,$A20)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S20" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T20" s="13" t="str">
@@ -16231,7 +16168,7 @@
         <v>172</v>
       </c>
       <c r="AC20" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD20" s="13" t="str">
@@ -16265,11 +16202,11 @@
         <v/>
       </c>
       <c r="AG20" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH20" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI20" s="13" t="str">
@@ -16343,18 +16280,11 @@
         <v>938</v>
       </c>
       <c r="R21" s="9" t="str">
-        <f>IF(
-  AND(
-    $A21&lt;&gt;"",
-    COUNTIF(C:C,$A21)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S21" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T21" s="13" t="str">
@@ -16477,7 +16407,7 @@
         <v>172</v>
       </c>
       <c r="AC21" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD21" s="13" t="str">
@@ -16511,11 +16441,11 @@
         <v/>
       </c>
       <c r="AG21" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH21" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI21" s="13" t="str">
@@ -16589,18 +16519,11 @@
         <v>938</v>
       </c>
       <c r="R22" s="9" t="str">
-        <f>IF(
-  AND(
-    $A22&lt;&gt;"",
-    COUNTIF(C:C,$A22)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S22" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T22" s="13" t="str">
@@ -16723,7 +16646,7 @@
         <v>171</v>
       </c>
       <c r="AC22" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD22" s="13" t="str">
@@ -16757,11 +16680,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\AutoMute（自動ミュート）.lnk</v>
       </c>
       <c r="AG22" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH22" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI22" s="13" t="str">
@@ -16835,18 +16758,11 @@
         <v>938</v>
       </c>
       <c r="R23" s="9" t="str">
-        <f>IF(
-  AND(
-    $A23&lt;&gt;"",
-    COUNTIF(C:C,$A23)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S23" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T23" s="13" t="str">
@@ -16969,7 +16885,7 @@
         <v>172</v>
       </c>
       <c r="AC23" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD23" s="13" t="str">
@@ -17003,11 +16919,11 @@
         <v/>
       </c>
       <c r="AG23" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH23" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI23" s="13" t="str">
@@ -17081,18 +16997,11 @@
         <v>938</v>
       </c>
       <c r="R24" s="9" t="str">
-        <f>IF(
-  AND(
-    $A24&lt;&gt;"",
-    COUNTIF(C:C,$A24)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S24" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T24" s="13" t="str">
@@ -17215,7 +17124,7 @@
         <v>113</v>
       </c>
       <c r="AC24" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD24" s="13" t="str">
@@ -17249,11 +17158,11 @@
         <v/>
       </c>
       <c r="AG24" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH24" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI24" s="13" t="str">
@@ -17327,18 +17236,11 @@
         <v>938</v>
       </c>
       <c r="R25" s="9" t="str">
-        <f>IF(
-  AND(
-    $A25&lt;&gt;"",
-    COUNTIF(C:C,$A25)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S25" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T25" s="13" t="str">
@@ -17461,7 +17363,7 @@
         <v>113</v>
       </c>
       <c r="AC25" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD25" s="13" t="str">
@@ -17495,11 +17397,11 @@
         <v/>
       </c>
       <c r="AG25" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH25" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI25" s="13" t="str">
@@ -17573,18 +17475,11 @@
         <v>938</v>
       </c>
       <c r="R26" s="9" t="str">
-        <f>IF(
-  AND(
-    $A26&lt;&gt;"",
-    COUNTIF(C:C,$A26)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S26" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T26" s="13" t="str">
@@ -17707,7 +17602,7 @@
         <v>113</v>
       </c>
       <c r="AC26" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD26" s="13" t="str">
@@ -17741,11 +17636,11 @@
         <v/>
       </c>
       <c r="AG26" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH26" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI26" s="13" t="str">
@@ -17819,18 +17714,11 @@
         <v>938</v>
       </c>
       <c r="R27" s="9" t="str">
-        <f>IF(
-  AND(
-    $A27&lt;&gt;"",
-    COUNTIF(C:C,$A27)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S27" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T27" s="13" t="str">
@@ -17953,7 +17841,7 @@
         <v>113</v>
       </c>
       <c r="AC27" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD27" s="13" t="str">
@@ -17987,11 +17875,11 @@
         <v/>
       </c>
       <c r="AG27" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH27" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI27" s="13" t="str">
@@ -18065,18 +17953,11 @@
         <v>938</v>
       </c>
       <c r="R28" s="9" t="str">
-        <f>IF(
-  AND(
-    $A28&lt;&gt;"",
-    COUNTIF(C:C,$A28)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S28" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T28" s="13" t="str">
@@ -18199,7 +18080,7 @@
         <v>113</v>
       </c>
       <c r="AC28" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD28" s="13" t="str">
@@ -18233,11 +18114,11 @@
         <v/>
       </c>
       <c r="AG28" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH28" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI28" s="13" t="str">
@@ -18311,18 +18192,11 @@
         <v>938</v>
       </c>
       <c r="R29" s="9" t="str">
-        <f>IF(
-  AND(
-    $A29&lt;&gt;"",
-    COUNTIF(C:C,$A29)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S29" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T29" s="13" t="str">
@@ -18445,7 +18319,7 @@
         <v>112</v>
       </c>
       <c r="AC29" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD29" s="13" t="str">
@@ -18479,11 +18353,11 @@
         <v/>
       </c>
       <c r="AG29" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH29" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI29" s="13" t="str">
@@ -18557,18 +18431,11 @@
         <v>938</v>
       </c>
       <c r="R30" s="9" t="str">
-        <f>IF(
-  AND(
-    $A30&lt;&gt;"",
-    COUNTIF(C:C,$A30)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S30" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T30" s="13" t="str">
@@ -18691,7 +18558,7 @@
         <v>112</v>
       </c>
       <c r="AC30" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD30" s="13" t="str">
@@ -18725,11 +18592,11 @@
         <v/>
       </c>
       <c r="AG30" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH30" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI30" s="13" t="str">
@@ -18803,18 +18670,11 @@
         <v>938</v>
       </c>
       <c r="R31" s="9" t="str">
-        <f>IF(
-  AND(
-    $A31&lt;&gt;"",
-    COUNTIF(C:C,$A31)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S31" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T31" s="13" t="str">
@@ -18937,7 +18797,7 @@
         <v>112</v>
       </c>
       <c r="AC31" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD31" s="13" t="str">
@@ -18971,11 +18831,11 @@
         <v/>
       </c>
       <c r="AG31" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH31" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI31" s="13" t="str">
@@ -19049,18 +18909,11 @@
         <v>938</v>
       </c>
       <c r="R32" s="9" t="str">
-        <f>IF(
-  AND(
-    $A32&lt;&gt;"",
-    COUNTIF(C:C,$A32)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S32" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T32" s="13" t="str">
@@ -19183,7 +19036,7 @@
         <v>121</v>
       </c>
       <c r="AC32" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD32" s="13" t="str">
@@ -19217,11 +19070,11 @@
         <v/>
       </c>
       <c r="AG32" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH32" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI32" s="13" t="str">
@@ -19295,18 +19148,11 @@
         <v>938</v>
       </c>
       <c r="R33" s="9" t="str">
-        <f>IF(
-  AND(
-    $A33&lt;&gt;"",
-    COUNTIF(C:C,$A33)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S33" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T33" s="13" t="str">
@@ -19429,7 +19275,7 @@
         <v>172</v>
       </c>
       <c r="AC33" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD33" s="13" t="str">
@@ -19463,11 +19309,11 @@
         <v/>
       </c>
       <c r="AG33" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH33" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI33" s="13" t="str">
@@ -19541,18 +19387,11 @@
         <v>938</v>
       </c>
       <c r="R34" s="9" t="str">
-        <f>IF(
-  AND(
-    $A34&lt;&gt;"",
-    COUNTIF(C:C,$A34)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S34" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T34" s="13" t="str">
@@ -19675,7 +19514,7 @@
         <v>171</v>
       </c>
       <c r="AC34" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD34" s="13" t="str">
@@ -19709,11 +19548,11 @@
         <v/>
       </c>
       <c r="AG34" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH34" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI34" s="13" t="str">
@@ -19787,18 +19626,11 @@
         <v>938</v>
       </c>
       <c r="R35" s="9" t="str">
-        <f>IF(
-  AND(
-    $A35&lt;&gt;"",
-    COUNTIF(C:C,$A35)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S35" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T35" s="13" t="str">
@@ -19921,7 +19753,7 @@
         <v>171</v>
       </c>
       <c r="AC35" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD35" s="13" t="str">
@@ -19955,11 +19787,11 @@
         <v/>
       </c>
       <c r="AG35" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH35" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI35" s="13" t="str">
@@ -20033,18 +19865,11 @@
         <v>938</v>
       </c>
       <c r="R36" s="9" t="str">
-        <f>IF(
-  AND(
-    $A36&lt;&gt;"",
-    COUNTIF(C:C,$A36)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S36" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T36" s="13" t="str">
@@ -20167,7 +19992,7 @@
         <v>111</v>
       </c>
       <c r="AC36" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD36" s="13" t="str">
@@ -20201,11 +20026,11 @@
         <v/>
       </c>
       <c r="AG36" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH36" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI36" s="13" t="str">
@@ -20279,18 +20104,11 @@
         <v>938</v>
       </c>
       <c r="R37" s="9" t="str">
-        <f>IF(
-  AND(
-    $A37&lt;&gt;"",
-    COUNTIF(C:C,$A37)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S37" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T37" s="13" t="str">
@@ -20413,7 +20231,7 @@
         <v>172</v>
       </c>
       <c r="AC37" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD37" s="13" t="str">
@@ -20447,11 +20265,11 @@
         <v/>
       </c>
       <c r="AG37" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH37" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI37" s="13" t="str">
@@ -20525,18 +20343,11 @@
         <v>938</v>
       </c>
       <c r="R38" s="9" t="str">
-        <f>IF(
-  AND(
-    $A38&lt;&gt;"",
-    COUNTIF(C:C,$A38)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S38" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T38" s="13" t="str">
@@ -20659,7 +20470,7 @@
         <v>134</v>
       </c>
       <c r="AC38" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD38" s="13" t="str">
@@ -20693,11 +20504,11 @@
         <v/>
       </c>
       <c r="AG38" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH38" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI38" s="13" t="str">
@@ -20771,18 +20582,11 @@
         <v>938</v>
       </c>
       <c r="R39" s="9" t="str">
-        <f>IF(
-  AND(
-    $A39&lt;&gt;"",
-    COUNTIF(C:C,$A39)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S39" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T39" s="13" t="str">
@@ -20905,7 +20709,7 @@
         <v>121</v>
       </c>
       <c r="AC39" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD39" s="13" t="str">
@@ -20939,11 +20743,11 @@
         <v/>
       </c>
       <c r="AG39" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH39" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI39" s="13" t="str">
@@ -21017,18 +20821,11 @@
         <v>938</v>
       </c>
       <c r="R40" s="9" t="str">
-        <f>IF(
-  AND(
-    $A40&lt;&gt;"",
-    COUNTIF(C:C,$A40)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S40" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T40" s="13" t="str">
@@ -21151,7 +20948,7 @@
         <v>121</v>
       </c>
       <c r="AC40" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD40" s="13" t="str">
@@ -21185,11 +20982,11 @@
         <v/>
       </c>
       <c r="AG40" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH40" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI40" s="13" t="str">
@@ -21263,18 +21060,11 @@
         <v>938</v>
       </c>
       <c r="R41" s="9" t="str">
-        <f>IF(
-  AND(
-    $A41&lt;&gt;"",
-    COUNTIF(C:C,$A41)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S41" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T41" s="13" t="str">
@@ -21397,7 +21187,7 @@
         <v>112</v>
       </c>
       <c r="AC41" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD41" s="13" t="str">
@@ -21431,11 +21221,11 @@
         <v/>
       </c>
       <c r="AG41" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH41" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI41" s="13" t="str">
@@ -21509,18 +21299,11 @@
         <v>938</v>
       </c>
       <c r="R42" s="9" t="str">
-        <f>IF(
-  AND(
-    $A42&lt;&gt;"",
-    COUNTIF(C:C,$A42)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S42" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T42" s="13" t="str">
@@ -21643,7 +21426,7 @@
         <v>111</v>
       </c>
       <c r="AC42" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD42" s="13" t="str">
@@ -21677,11 +21460,11 @@
         <v/>
       </c>
       <c r="AG42" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH42" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI42" s="13" t="str">
@@ -21755,18 +21538,11 @@
         <v>938</v>
       </c>
       <c r="R43" s="9" t="str">
-        <f>IF(
-  AND(
-    $A43&lt;&gt;"",
-    COUNTIF(C:C,$A43)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S43" s="9" t="str">
-        <f t="shared" ref="S43:S73" si="4">IF(
+        <f t="shared" ref="S43:S73" si="5">IF(
   OR(
     $H43="",
     $H43="-",
@@ -21897,7 +21673,7 @@
         <v>121</v>
       </c>
       <c r="AC43" s="20" t="str">
-        <f t="shared" ref="AC43:AC73" si="5">IF(AND($M43&lt;&gt;"",$M43&lt;&gt;"-")," (&amp;"&amp;$M43&amp;")","")</f>
+        <f t="shared" ref="AC43:AC73" si="6">IF(AND($M43&lt;&gt;"",$M43&lt;&gt;"-")," (&amp;"&amp;$M43&amp;")","")</f>
         <v/>
       </c>
       <c r="AD43" s="13" t="str">
@@ -21931,7 +21707,7 @@
         <v/>
       </c>
       <c r="AG43" s="13" t="str">
-        <f t="shared" ref="AG43:AG73" si="6">IF(
+        <f t="shared" ref="AG43:AG73" si="7">IF(
   AND($A43&lt;&gt;"",$O43&lt;&gt;"-",$O43&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O43&amp;""" /tr """&amp;$C43&amp;""" /sc daily /st "&amp;$P43&amp;" /rl highest"
@@ -21941,7 +21717,7 @@
         <v/>
       </c>
       <c r="AH43" s="13" t="str">
-        <f t="shared" ref="AH43:AH73" si="7">IF(
+        <f t="shared" ref="AH43:AH73" si="8">IF(
   AND($A43&lt;&gt;"",$O43&lt;&gt;"-",$O43&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O43&amp;""""
@@ -22021,18 +21797,11 @@
         <v>938</v>
       </c>
       <c r="R44" s="9" t="str">
-        <f>IF(
-  AND(
-    $A44&lt;&gt;"",
-    COUNTIF(C:C,$A44)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S44" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T44" s="13" t="str">
@@ -22155,7 +21924,7 @@
         <v>113</v>
       </c>
       <c r="AC44" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD44" s="13" t="str">
@@ -22189,11 +21958,11 @@
         <v/>
       </c>
       <c r="AG44" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH44" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI44" s="13" t="str">
@@ -22267,18 +22036,11 @@
         <v>938</v>
       </c>
       <c r="R45" s="9" t="str">
-        <f>IF(
-  AND(
-    $A45&lt;&gt;"",
-    COUNTIF(C:C,$A45)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S45" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T45" s="13" t="str">
@@ -22401,7 +22163,7 @@
         <v>161</v>
       </c>
       <c r="AC45" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD45" s="13" t="str">
@@ -22435,11 +22197,11 @@
         <v/>
       </c>
       <c r="AG45" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH45" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI45" s="13" t="str">
@@ -22513,18 +22275,11 @@
         <v>938</v>
       </c>
       <c r="R46" s="9" t="str">
-        <f>IF(
-  AND(
-    $A46&lt;&gt;"",
-    COUNTIF(C:C,$A46)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S46" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T46" s="13" t="str">
@@ -22647,7 +22402,7 @@
         <v>121</v>
       </c>
       <c r="AC46" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD46" s="13" t="str">
@@ -22681,11 +22436,11 @@
         <v/>
       </c>
       <c r="AG46" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH46" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI46" s="13" t="str">
@@ -22759,18 +22514,11 @@
         <v>938</v>
       </c>
       <c r="R47" s="9" t="str">
-        <f>IF(
-  AND(
-    $A47&lt;&gt;"",
-    COUNTIF(C:C,$A47)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S47" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T47" s="13" t="str">
@@ -22893,7 +22641,7 @@
         <v>123</v>
       </c>
       <c r="AC47" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD47" s="13" t="str">
@@ -22927,11 +22675,11 @@
         <v/>
       </c>
       <c r="AG47" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH47" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI47" s="13" t="str">
@@ -23005,18 +22753,11 @@
         <v>938</v>
       </c>
       <c r="R48" s="9" t="str">
-        <f>IF(
-  AND(
-    $A48&lt;&gt;"",
-    COUNTIF(C:C,$A48)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S48" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T48" s="13" t="str">
@@ -23139,7 +22880,7 @@
         <v>133</v>
       </c>
       <c r="AC48" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD48" s="13" t="str">
@@ -23173,11 +22914,11 @@
         <v/>
       </c>
       <c r="AG48" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH48" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI48" s="13" t="str">
@@ -23251,18 +22992,11 @@
         <v>938</v>
       </c>
       <c r="R49" s="9" t="str">
-        <f>IF(
-  AND(
-    $A49&lt;&gt;"",
-    COUNTIF(C:C,$A49)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S49" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T49" s="13" t="str">
@@ -23385,7 +23119,7 @@
         <v>123</v>
       </c>
       <c r="AC49" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD49" s="13" t="str">
@@ -23419,11 +23153,11 @@
         <v/>
       </c>
       <c r="AG49" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH49" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI49" s="13" t="str">
@@ -23497,18 +23231,11 @@
         <v>938</v>
       </c>
       <c r="R50" s="9" t="str">
-        <f>IF(
-  AND(
-    $A50&lt;&gt;"",
-    COUNTIF(C:C,$A50)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S50" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T50" s="13" t="str">
@@ -23631,7 +23358,7 @@
         <v>153</v>
       </c>
       <c r="AC50" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD50" s="13" t="str">
@@ -23665,11 +23392,11 @@
         <v/>
       </c>
       <c r="AG50" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH50" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI50" s="13" t="str">
@@ -23743,18 +23470,11 @@
         <v>938</v>
       </c>
       <c r="R51" s="9" t="str">
-        <f>IF(
-  AND(
-    $A51&lt;&gt;"",
-    COUNTIF(C:C,$A51)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S51" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T51" s="13" t="str">
@@ -23877,7 +23597,7 @@
         <v>122</v>
       </c>
       <c r="AC51" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD51" s="13" t="str">
@@ -23911,11 +23631,11 @@
         <v/>
       </c>
       <c r="AG51" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH51" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI51" s="13" t="str">
@@ -23989,18 +23709,11 @@
         <v>938</v>
       </c>
       <c r="R52" s="9" t="str">
-        <f>IF(
-  AND(
-    $A52&lt;&gt;"",
-    COUNTIF(C:C,$A52)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S52" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T52" s="13" t="str">
@@ -24123,7 +23836,7 @@
         <v>161</v>
       </c>
       <c r="AC52" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD52" s="13" t="str">
@@ -24157,11 +23870,11 @@
         <v/>
       </c>
       <c r="AG52" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH52" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI52" s="13" t="str">
@@ -24235,18 +23948,11 @@
         <v>938</v>
       </c>
       <c r="R53" s="9" t="str">
-        <f>IF(
-  AND(
-    $A53&lt;&gt;"",
-    COUNTIF(C:C,$A53)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S53" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T53" s="13" t="str">
@@ -24369,7 +24075,7 @@
         <v>121</v>
       </c>
       <c r="AC53" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD53" s="13" t="str">
@@ -24403,11 +24109,11 @@
         <v/>
       </c>
       <c r="AG53" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH53" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI53" s="13" t="str">
@@ -24481,18 +24187,11 @@
         <v>938</v>
       </c>
       <c r="R54" s="9" t="str">
-        <f>IF(
-  AND(
-    $A54&lt;&gt;"",
-    COUNTIF(C:C,$A54)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S54" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T54" s="13" t="str">
@@ -24615,7 +24314,7 @@
         <v>123</v>
       </c>
       <c r="AC54" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD54" s="13" t="str">
@@ -24649,11 +24348,11 @@
         <v/>
       </c>
       <c r="AG54" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH54" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI54" s="13" t="str">
@@ -24727,18 +24426,11 @@
         <v>938</v>
       </c>
       <c r="R55" s="9" t="str">
-        <f>IF(
-  AND(
-    $A55&lt;&gt;"",
-    COUNTIF(C:C,$A55)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S55" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T55" s="13" t="str">
@@ -24861,7 +24553,7 @@
         <v>121</v>
       </c>
       <c r="AC55" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD55" s="13" t="str">
@@ -24895,11 +24587,11 @@
         <v/>
       </c>
       <c r="AG55" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH55" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI55" s="13" t="str">
@@ -24973,18 +24665,11 @@
         <v>938</v>
       </c>
       <c r="R56" s="9" t="str">
-        <f>IF(
-  AND(
-    $A56&lt;&gt;"",
-    COUNTIF(C:C,$A56)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S56" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T56" s="13" t="str">
@@ -25107,7 +24792,7 @@
         <v>171</v>
       </c>
       <c r="AC56" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD56" s="13" t="str">
@@ -25141,11 +24826,11 @@
         <v/>
       </c>
       <c r="AG56" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH56" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI56" s="13" t="str">
@@ -25219,18 +24904,11 @@
         <v>938</v>
       </c>
       <c r="R57" s="9" t="str">
-        <f>IF(
-  AND(
-    $A57&lt;&gt;"",
-    COUNTIF(C:C,$A57)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S57" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T57" s="13" t="str">
@@ -25353,7 +25031,7 @@
         <v>171</v>
       </c>
       <c r="AC57" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD57" s="13" t="str">
@@ -25387,11 +25065,11 @@
         <v/>
       </c>
       <c r="AG57" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH57" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI57" s="13" t="str">
@@ -25465,18 +25143,11 @@
         <v>938</v>
       </c>
       <c r="R58" s="9" t="str">
-        <f>IF(
-  AND(
-    $A58&lt;&gt;"",
-    COUNTIF(C:C,$A58)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S58" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T58" s="13" t="str">
@@ -25599,7 +25270,7 @@
         <v>171</v>
       </c>
       <c r="AC58" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD58" s="13" t="str">
@@ -25633,11 +25304,11 @@
         <v/>
       </c>
       <c r="AG58" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH58" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI58" s="13" t="str">
@@ -25711,18 +25382,11 @@
         <v>938</v>
       </c>
       <c r="R59" s="9" t="str">
-        <f>IF(
-  AND(
-    $A59&lt;&gt;"",
-    COUNTIF(C:C,$A59)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S59" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T59" s="13" t="str">
@@ -25845,7 +25509,7 @@
         <v>113</v>
       </c>
       <c r="AC59" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD59" s="13" t="str">
@@ -25879,11 +25543,11 @@
         <v/>
       </c>
       <c r="AG59" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH59" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI59" s="13" t="str">
@@ -25957,18 +25621,11 @@
         <v>938</v>
       </c>
       <c r="R60" s="9" t="str">
-        <f>IF(
-  AND(
-    $A60&lt;&gt;"",
-    COUNTIF(C:C,$A60)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S60" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T60" s="13" t="str">
@@ -26091,7 +25748,7 @@
         <v>153</v>
       </c>
       <c r="AC60" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD60" s="13" t="str">
@@ -26125,11 +25782,11 @@
         <v/>
       </c>
       <c r="AG60" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH60" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI60" s="13" t="str">
@@ -26203,18 +25860,11 @@
         <v>938</v>
       </c>
       <c r="R61" s="9" t="str">
-        <f>IF(
-  AND(
-    $A61&lt;&gt;"",
-    COUNTIF(C:C,$A61)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S61" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T61" s="13" t="str">
@@ -26337,7 +25987,7 @@
         <v>123</v>
       </c>
       <c r="AC61" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD61" s="13" t="str">
@@ -26371,11 +26021,11 @@
         <v/>
       </c>
       <c r="AG61" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH61" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI61" s="13" t="str">
@@ -26449,18 +26099,11 @@
         <v>938</v>
       </c>
       <c r="R62" s="9" t="str">
-        <f>IF(
-  AND(
-    $A62&lt;&gt;"",
-    COUNTIF(C:C,$A62)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S62" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T62" s="13" t="str">
@@ -26583,7 +26226,7 @@
         <v>153</v>
       </c>
       <c r="AC62" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD62" s="13" t="str">
@@ -26617,11 +26260,11 @@
         <v/>
       </c>
       <c r="AG62" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH62" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI62" s="13" t="str">
@@ -26695,18 +26338,11 @@
         <v>938</v>
       </c>
       <c r="R63" s="9" t="str">
-        <f>IF(
-  AND(
-    $A63&lt;&gt;"",
-    COUNTIF(C:C,$A63)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S63" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T63" s="13" t="str">
@@ -26829,7 +26465,7 @@
         <v>121</v>
       </c>
       <c r="AC63" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD63" s="13" t="str">
@@ -26863,11 +26499,11 @@
         <v/>
       </c>
       <c r="AG63" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH63" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI63" s="13" t="str">
@@ -26941,18 +26577,11 @@
         <v>938</v>
       </c>
       <c r="R64" s="9" t="str">
-        <f>IF(
-  AND(
-    $A64&lt;&gt;"",
-    COUNTIF(C:C,$A64)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S64" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T64" s="13" t="str">
@@ -27075,7 +26704,7 @@
         <v>172</v>
       </c>
       <c r="AC64" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD64" s="13" t="str">
@@ -27109,11 +26738,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\KeePass（パスワード管理）.lnk</v>
       </c>
       <c r="AG64" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH64" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI64" s="13" t="str">
@@ -27187,18 +26816,11 @@
         <v>938</v>
       </c>
       <c r="R65" s="9" t="str">
-        <f>IF(
-  AND(
-    $A65&lt;&gt;"",
-    COUNTIF(C:C,$A65)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S65" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T65" s="13" t="str">
@@ -27321,7 +26943,7 @@
         <v>113</v>
       </c>
       <c r="AC65" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD65" s="13" t="str">
@@ -27355,11 +26977,11 @@
         <v/>
       </c>
       <c r="AG65" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH65" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI65" s="13" t="str">
@@ -27433,18 +27055,11 @@
         <v>938</v>
       </c>
       <c r="R66" s="9" t="str">
-        <f>IF(
-  AND(
-    $A66&lt;&gt;"",
-    COUNTIF(C:C,$A66)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S66" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T66" s="13" t="str">
@@ -27567,7 +27182,7 @@
         <v>172</v>
       </c>
       <c r="AC66" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD66" s="13" t="str">
@@ -27601,11 +27216,11 @@
         <v/>
       </c>
       <c r="AG66" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH66" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI66" s="13" t="str">
@@ -27679,18 +27294,11 @@
         <v>938</v>
       </c>
       <c r="R67" s="9" t="str">
-        <f>IF(
-  AND(
-    $A67&lt;&gt;"",
-    COUNTIF(C:C,$A67)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S67" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T67" s="13" t="str">
@@ -27813,7 +27421,7 @@
         <v>143</v>
       </c>
       <c r="AC67" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD67" s="13" t="str">
@@ -27847,11 +27455,11 @@
         <v/>
       </c>
       <c r="AG67" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH67" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI67" s="13" t="str">
@@ -27925,18 +27533,11 @@
         <v>938</v>
       </c>
       <c r="R68" s="9" t="str">
-        <f>IF(
-  AND(
-    $A68&lt;&gt;"",
-    COUNTIF(C:C,$A68)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S68" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T68" s="13" t="str">
@@ -28059,7 +27660,7 @@
         <v>113</v>
       </c>
       <c r="AC68" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD68" s="13" t="str">
@@ -28093,11 +27694,11 @@
         <v/>
       </c>
       <c r="AG68" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH68" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI68" s="13" t="str">
@@ -28171,18 +27772,11 @@
         <v>938</v>
       </c>
       <c r="R69" s="9" t="str">
-        <f>IF(
-  AND(
-    $A69&lt;&gt;"",
-    COUNTIF(C:C,$A69)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S69" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T69" s="13" t="str">
@@ -28305,7 +27899,7 @@
         <v>154</v>
       </c>
       <c r="AC69" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD69" s="13" t="str">
@@ -28339,11 +27933,11 @@
         <v/>
       </c>
       <c r="AG69" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH69" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI69" s="13" t="str">
@@ -28417,18 +28011,11 @@
         <v>938</v>
       </c>
       <c r="R70" s="9" t="str">
-        <f>IF(
-  AND(
-    $A70&lt;&gt;"",
-    COUNTIF(C:C,$A70)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S70" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T70" s="13" t="str">
@@ -28551,7 +28138,7 @@
         <v>121</v>
       </c>
       <c r="AC70" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD70" s="13" t="str">
@@ -28585,11 +28172,11 @@
         <v/>
       </c>
       <c r="AG70" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH70" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI70" s="13" t="str">
@@ -28663,14 +28250,7 @@
         <v>39</v>
       </c>
       <c r="R71" s="9" t="str">
-        <f>IF(
-  AND(
-    $A71&lt;&gt;"",
-    COUNTIF(C:C,$A71)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S71" s="9" t="str">
@@ -28929,18 +28509,11 @@
         <v>938</v>
       </c>
       <c r="R72" s="9" t="str">
-        <f>IF(
-  AND(
-    $A72&lt;&gt;"",
-    COUNTIF(C:C,$A72)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S72" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T72" s="13" t="str">
@@ -29063,7 +28636,7 @@
         <v>134</v>
       </c>
       <c r="AC72" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD72" s="13" t="str">
@@ -29097,11 +28670,11 @@
         <v/>
       </c>
       <c r="AG72" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH72" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI72" s="13" t="str">
@@ -29175,18 +28748,11 @@
         <v>938</v>
       </c>
       <c r="R73" s="9" t="str">
-        <f>IF(
-  AND(
-    $A73&lt;&gt;"",
-    COUNTIF(C:C,$A73)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S73" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T73" s="13" t="str">
@@ -29309,7 +28875,7 @@
         <v>144</v>
       </c>
       <c r="AC73" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD73" s="13" t="str">
@@ -29343,11 +28909,11 @@
         <v/>
       </c>
       <c r="AG73" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH73" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI73" s="13" t="str">
@@ -29421,18 +28987,11 @@
         <v>938</v>
       </c>
       <c r="R74" s="9" t="str">
-        <f>IF(
-  AND(
-    $A74&lt;&gt;"",
-    COUNTIF(C:C,$A74)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S74" s="9" t="str">
-        <f t="shared" ref="S74:S105" si="8">IF(
+        <f t="shared" ref="S74:S105" si="9">IF(
   OR(
     $H74="",
     $H74="-",
@@ -29563,7 +29122,7 @@
         <v>154</v>
       </c>
       <c r="AC74" s="20" t="str">
-        <f t="shared" ref="AC74:AC105" si="9">IF(AND($M74&lt;&gt;"",$M74&lt;&gt;"-")," (&amp;"&amp;$M74&amp;")","")</f>
+        <f t="shared" ref="AC74:AC105" si="10">IF(AND($M74&lt;&gt;"",$M74&lt;&gt;"-")," (&amp;"&amp;$M74&amp;")","")</f>
         <v/>
       </c>
       <c r="AD74" s="13" t="str">
@@ -29597,7 +29156,7 @@
         <v/>
       </c>
       <c r="AG74" s="13" t="str">
-        <f t="shared" ref="AG74:AG105" si="10">IF(
+        <f t="shared" ref="AG74:AG105" si="11">IF(
   AND($A74&lt;&gt;"",$O74&lt;&gt;"-",$O74&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O74&amp;""" /tr """&amp;$C74&amp;""" /sc daily /st "&amp;$P74&amp;" /rl highest"
@@ -29607,7 +29166,7 @@
         <v/>
       </c>
       <c r="AH74" s="13" t="str">
-        <f t="shared" ref="AH74:AH105" si="11">IF(
+        <f t="shared" ref="AH74:AH105" si="12">IF(
   AND($A74&lt;&gt;"",$O74&lt;&gt;"-",$O74&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O74&amp;""""
@@ -29687,7 +29246,7 @@
         <v>938</v>
       </c>
       <c r="R75" s="9" t="str">
-        <f>IF(
+        <f t="shared" ref="R75:R138" si="13">IF(
   AND(
     $A75&lt;&gt;"",
     COUNTIF(C:C,$A75)&gt;1
@@ -29698,7 +29257,7 @@
         <v/>
       </c>
       <c r="S75" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T75" s="13" t="str">
@@ -29821,7 +29380,7 @@
         <v>162</v>
       </c>
       <c r="AC75" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD75" s="13" t="str">
@@ -29855,11 +29414,11 @@
         <v/>
       </c>
       <c r="AG75" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH75" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI75" s="13" t="str">
@@ -29933,18 +29492,11 @@
         <v>938</v>
       </c>
       <c r="R76" s="9" t="str">
-        <f>IF(
-  AND(
-    $A76&lt;&gt;"",
-    COUNTIF(C:C,$A76)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S76" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T76" s="13" t="str">
@@ -30067,7 +29619,7 @@
         <v>111</v>
       </c>
       <c r="AC76" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD76" s="13" t="str">
@@ -30101,11 +29653,11 @@
         <v/>
       </c>
       <c r="AG76" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH76" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI76" s="13" t="str">
@@ -30179,18 +29731,11 @@
         <v>938</v>
       </c>
       <c r="R77" s="9" t="str">
-        <f>IF(
-  AND(
-    $A77&lt;&gt;"",
-    COUNTIF(C:C,$A77)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S77" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T77" s="13" t="str">
@@ -30313,7 +29858,7 @@
         <v>172</v>
       </c>
       <c r="AC77" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD77" s="13" t="str">
@@ -30347,11 +29892,11 @@
         <v/>
       </c>
       <c r="AG77" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH77" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI77" s="13" t="str">
@@ -30425,18 +29970,11 @@
         <v>938</v>
       </c>
       <c r="R78" s="9" t="str">
-        <f>IF(
-  AND(
-    $A78&lt;&gt;"",
-    COUNTIF(C:C,$A78)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S78" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T78" s="13" t="str">
@@ -30559,7 +30097,7 @@
         <v>162</v>
       </c>
       <c r="AC78" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD78" s="13" t="str">
@@ -30593,11 +30131,11 @@
         <v/>
       </c>
       <c r="AG78" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH78" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI78" s="13" t="str">
@@ -30671,18 +30209,11 @@
         <v>938</v>
       </c>
       <c r="R79" s="9" t="str">
-        <f>IF(
-  AND(
-    $A79&lt;&gt;"",
-    COUNTIF(C:C,$A79)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S79" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T79" s="13" t="str">
@@ -30805,7 +30336,7 @@
         <v>122</v>
       </c>
       <c r="AC79" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD79" s="13" t="str">
@@ -30839,11 +30370,11 @@
         <v/>
       </c>
       <c r="AG79" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH79" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI79" s="13" t="str">
@@ -30917,18 +30448,11 @@
         <v>938</v>
       </c>
       <c r="R80" s="9" t="str">
-        <f>IF(
-  AND(
-    $A80&lt;&gt;"",
-    COUNTIF(C:C,$A80)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S80" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T80" s="13" t="str">
@@ -31051,7 +30575,7 @@
         <v>122</v>
       </c>
       <c r="AC80" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD80" s="13" t="str">
@@ -31085,11 +30609,11 @@
         <v/>
       </c>
       <c r="AG80" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH80" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI80" s="13" t="str">
@@ -31163,18 +30687,11 @@
         <v>938</v>
       </c>
       <c r="R81" s="9" t="str">
-        <f>IF(
-  AND(
-    $A81&lt;&gt;"",
-    COUNTIF(C:C,$A81)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S81" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T81" s="13" t="str">
@@ -31297,7 +30814,7 @@
         <v>122</v>
       </c>
       <c r="AC81" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD81" s="13" t="str">
@@ -31331,11 +30848,11 @@
         <v/>
       </c>
       <c r="AG81" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH81" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI81" s="13" t="str">
@@ -31409,18 +30926,11 @@
         <v>938</v>
       </c>
       <c r="R82" s="9" t="str">
-        <f>IF(
-  AND(
-    $A82&lt;&gt;"",
-    COUNTIF(C:C,$A82)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S82" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T82" s="13" t="str">
@@ -31543,7 +31053,7 @@
         <v>123</v>
       </c>
       <c r="AC82" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD82" s="13" t="str">
@@ -31577,11 +31087,11 @@
         <v/>
       </c>
       <c r="AG82" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH82" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI82" s="13" t="str">
@@ -31655,18 +31165,11 @@
         <v>938</v>
       </c>
       <c r="R83" s="9" t="str">
-        <f>IF(
-  AND(
-    $A83&lt;&gt;"",
-    COUNTIF(C:C,$A83)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S83" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T83" s="13" t="str">
@@ -31789,7 +31292,7 @@
         <v>113</v>
       </c>
       <c r="AC83" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD83" s="13" t="str">
@@ -31823,11 +31326,11 @@
         <v/>
       </c>
       <c r="AG83" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH83" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI83" s="13" t="str">
@@ -31901,18 +31404,11 @@
         <v>938</v>
       </c>
       <c r="R84" s="9" t="str">
-        <f>IF(
-  AND(
-    $A84&lt;&gt;"",
-    COUNTIF(C:C,$A84)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S84" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T84" s="13" t="str">
@@ -32035,7 +31531,7 @@
         <v>172</v>
       </c>
       <c r="AC84" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD84" s="13" t="str">
@@ -32069,11 +31565,11 @@
         <v/>
       </c>
       <c r="AG84" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH84" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI84" s="13" t="str">
@@ -32148,18 +31644,11 @@
         <v>938</v>
       </c>
       <c r="R85" s="9" t="str">
-        <f>IF(
-  AND(
-    $A85&lt;&gt;"",
-    COUNTIF(C:C,$A85)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S85" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T85" s="13" t="str">
@@ -32282,7 +31771,7 @@
         <v>172</v>
       </c>
       <c r="AC85" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD85" s="13" t="str">
@@ -32316,11 +31805,11 @@
         <v/>
       </c>
       <c r="AG85" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH85" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI85" s="13" t="str">
@@ -32394,18 +31883,11 @@
         <v>938</v>
       </c>
       <c r="R86" s="9" t="str">
-        <f>IF(
-  AND(
-    $A86&lt;&gt;"",
-    COUNTIF(C:C,$A86)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S86" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T86" s="13" t="str">
@@ -32528,7 +32010,7 @@
         <v>113</v>
       </c>
       <c r="AC86" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD86" s="13" t="str">
@@ -32562,11 +32044,11 @@
         <v/>
       </c>
       <c r="AG86" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH86" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI86" s="13" t="str">
@@ -32640,18 +32122,11 @@
         <v>938</v>
       </c>
       <c r="R87" s="9" t="str">
-        <f>IF(
-  AND(
-    $A87&lt;&gt;"",
-    COUNTIF(C:C,$A87)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S87" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T87" s="13" t="str">
@@ -32774,7 +32249,7 @@
         <v>171</v>
       </c>
       <c r="AC87" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD87" s="13" t="str">
@@ -32808,11 +32283,11 @@
         <v/>
       </c>
       <c r="AG87" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH87" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI87" s="13" t="str">
@@ -32886,18 +32361,11 @@
         <v>938</v>
       </c>
       <c r="R88" s="9" t="str">
-        <f>IF(
-  AND(
-    $A88&lt;&gt;"",
-    COUNTIF(C:C,$A88)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S88" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T88" s="13" t="str">
@@ -33020,7 +32488,7 @@
         <v>162</v>
       </c>
       <c r="AC88" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD88" s="13" t="str">
@@ -33054,11 +32522,11 @@
         <v/>
       </c>
       <c r="AG88" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH88" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI88" s="13" t="str">
@@ -33132,18 +32600,11 @@
         <v>938</v>
       </c>
       <c r="R89" s="9" t="str">
-        <f>IF(
-  AND(
-    $A89&lt;&gt;"",
-    COUNTIF(C:C,$A89)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S89" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T89" s="13" t="str">
@@ -33266,7 +32727,7 @@
         <v>123</v>
       </c>
       <c r="AC89" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD89" s="13" t="str">
@@ -33300,11 +32761,11 @@
         <v/>
       </c>
       <c r="AG89" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH89" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI89" s="13" t="str">
@@ -33378,18 +32839,11 @@
         <v>938</v>
       </c>
       <c r="R90" s="9" t="str">
-        <f>IF(
-  AND(
-    $A90&lt;&gt;"",
-    COUNTIF(C:C,$A90)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S90" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T90" s="13" t="str">
@@ -33512,7 +32966,7 @@
         <v>111</v>
       </c>
       <c r="AC90" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD90" s="13" t="str">
@@ -33546,11 +33000,11 @@
         <v/>
       </c>
       <c r="AG90" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH90" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI90" s="13" t="str">
@@ -33624,18 +33078,11 @@
         <v>938</v>
       </c>
       <c r="R91" s="9" t="str">
-        <f>IF(
-  AND(
-    $A91&lt;&gt;"",
-    COUNTIF(C:C,$A91)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S91" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T91" s="13" t="str">
@@ -33758,7 +33205,7 @@
         <v>153</v>
       </c>
       <c r="AC91" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD91" s="13" t="str">
@@ -33792,11 +33239,11 @@
         <v/>
       </c>
       <c r="AG91" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH91" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI91" s="13" t="str">
@@ -33870,18 +33317,11 @@
         <v>938</v>
       </c>
       <c r="R92" s="9" t="str">
-        <f>IF(
-  AND(
-    $A92&lt;&gt;"",
-    COUNTIF(C:C,$A92)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S92" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T92" s="13" t="str">
@@ -34004,7 +33444,7 @@
         <v>161</v>
       </c>
       <c r="AC92" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD92" s="13" t="str">
@@ -34038,11 +33478,11 @@
         <v/>
       </c>
       <c r="AG92" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH92" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI92" s="13" t="str">
@@ -34116,18 +33556,11 @@
         <v>938</v>
       </c>
       <c r="R93" s="9" t="str">
-        <f>IF(
-  AND(
-    $A93&lt;&gt;"",
-    COUNTIF(C:C,$A93)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S93" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T93" s="13" t="str">
@@ -34250,7 +33683,7 @@
         <v>113</v>
       </c>
       <c r="AC93" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD93" s="13" t="str">
@@ -34284,11 +33717,11 @@
         <v/>
       </c>
       <c r="AG93" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH93" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI93" s="13" t="str">
@@ -34362,18 +33795,11 @@
         <v>938</v>
       </c>
       <c r="R94" s="9" t="str">
-        <f>IF(
-  AND(
-    $A94&lt;&gt;"",
-    COUNTIF(C:C,$A94)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S94" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T94" s="13" t="str">
@@ -34496,7 +33922,7 @@
         <v>123</v>
       </c>
       <c r="AC94" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD94" s="13" t="str">
@@ -34530,11 +33956,11 @@
         <v/>
       </c>
       <c r="AG94" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH94" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI94" s="13" t="str">
@@ -34608,18 +34034,11 @@
         <v>938</v>
       </c>
       <c r="R95" s="9" t="str">
-        <f>IF(
-  AND(
-    $A95&lt;&gt;"",
-    COUNTIF(C:C,$A95)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S95" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T95" s="13" t="str">
@@ -34742,7 +34161,7 @@
         <v>134</v>
       </c>
       <c r="AC95" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD95" s="13" t="str">
@@ -34776,11 +34195,11 @@
         <v/>
       </c>
       <c r="AG95" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH95" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI95" s="13" t="str">
@@ -34854,18 +34273,11 @@
         <v>938</v>
       </c>
       <c r="R96" s="9" t="str">
-        <f>IF(
-  AND(
-    $A96&lt;&gt;"",
-    COUNTIF(C:C,$A96)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S96" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T96" s="13" t="str">
@@ -34988,7 +34400,7 @@
         <v>122</v>
       </c>
       <c r="AC96" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD96" s="13" t="str">
@@ -35022,11 +34434,11 @@
         <v/>
       </c>
       <c r="AG96" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH96" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI96" s="13" t="str">
@@ -35100,18 +34512,11 @@
         <v>938</v>
       </c>
       <c r="R97" s="9" t="str">
-        <f>IF(
-  AND(
-    $A97&lt;&gt;"",
-    COUNTIF(C:C,$A97)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S97" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T97" s="13" t="str">
@@ -35234,7 +34639,7 @@
         <v>162</v>
       </c>
       <c r="AC97" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD97" s="13" t="str">
@@ -35268,11 +34673,11 @@
         <v/>
       </c>
       <c r="AG97" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH97" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI97" s="13" t="str">
@@ -35346,18 +34751,11 @@
         <v>938</v>
       </c>
       <c r="R98" s="9" t="str">
-        <f>IF(
-  AND(
-    $A98&lt;&gt;"",
-    COUNTIF(C:C,$A98)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S98" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T98" s="13" t="str">
@@ -35480,7 +34878,7 @@
         <v>161</v>
       </c>
       <c r="AC98" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD98" s="13" t="str">
@@ -35514,11 +34912,11 @@
         <v/>
       </c>
       <c r="AG98" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH98" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI98" s="13" t="str">
@@ -35592,18 +34990,11 @@
         <v>938</v>
       </c>
       <c r="R99" s="9" t="str">
-        <f>IF(
-  AND(
-    $A99&lt;&gt;"",
-    COUNTIF(C:C,$A99)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S99" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T99" s="13" t="str">
@@ -35726,7 +35117,7 @@
         <v>121</v>
       </c>
       <c r="AC99" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD99" s="13" t="str">
@@ -35760,11 +35151,11 @@
         <v/>
       </c>
       <c r="AG99" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH99" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI99" s="13" t="str">
@@ -35838,18 +35229,11 @@
         <v>938</v>
       </c>
       <c r="R100" s="9" t="str">
-        <f>IF(
-  AND(
-    $A100&lt;&gt;"",
-    COUNTIF(C:C,$A100)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S100" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T100" s="13" t="str">
@@ -35972,7 +35356,7 @@
         <v>172</v>
       </c>
       <c r="AC100" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD100" s="13" t="str">
@@ -36006,11 +35390,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\TVClock（デスクトップ時計）.lnk</v>
       </c>
       <c r="AG100" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH100" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI100" s="13" t="str">
@@ -36084,18 +35468,11 @@
         <v>938</v>
       </c>
       <c r="R101" s="9" t="str">
-        <f>IF(
-  AND(
-    $A101&lt;&gt;"",
-    COUNTIF(C:C,$A101)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S101" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T101" s="13" t="str">
@@ -36218,7 +35595,7 @@
         <v>111</v>
       </c>
       <c r="AC101" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD101" s="13" t="str">
@@ -36252,11 +35629,11 @@
         <v/>
       </c>
       <c r="AG101" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH101" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI101" s="13" t="str">
@@ -36330,18 +35707,11 @@
         <v>938</v>
       </c>
       <c r="R102" s="9" t="str">
-        <f>IF(
-  AND(
-    $A102&lt;&gt;"",
-    COUNTIF(C:C,$A102)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S102" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T102" s="13" t="str">
@@ -36464,7 +35834,7 @@
         <v>172</v>
       </c>
       <c r="AC102" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD102" s="13" t="str">
@@ -36498,11 +35868,11 @@
         <v/>
       </c>
       <c r="AG102" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH102" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI102" s="13" t="str">
@@ -36576,18 +35946,11 @@
         <v>938</v>
       </c>
       <c r="R103" s="9" t="str">
-        <f>IF(
-  AND(
-    $A103&lt;&gt;"",
-    COUNTIF(C:C,$A103)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S103" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T103" s="13" t="str">
@@ -36710,7 +36073,7 @@
         <v>172</v>
       </c>
       <c r="AC103" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD103" s="13" t="str">
@@ -36744,11 +36107,11 @@
         <v/>
       </c>
       <c r="AG103" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH103" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI103" s="13" t="str">
@@ -36822,18 +36185,11 @@
         <v>938</v>
       </c>
       <c r="R104" s="9" t="str">
-        <f>IF(
-  AND(
-    $A104&lt;&gt;"",
-    COUNTIF(C:C,$A104)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S104" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T104" s="13" t="str">
@@ -36956,7 +36312,7 @@
         <v>123</v>
       </c>
       <c r="AC104" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve"> (&amp;V)</v>
       </c>
       <c r="AD104" s="13" t="str">
@@ -36990,11 +36346,11 @@
         <v/>
       </c>
       <c r="AG104" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH104" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI104" s="13" t="str">
@@ -37068,18 +36424,11 @@
         <v>938</v>
       </c>
       <c r="R105" s="9" t="str">
-        <f>IF(
-  AND(
-    $A105&lt;&gt;"",
-    COUNTIF(C:C,$A105)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S105" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T105" s="13" t="str">
@@ -37202,7 +36551,7 @@
         <v>123</v>
       </c>
       <c r="AC105" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve"> (&amp;C)</v>
       </c>
       <c r="AD105" s="13" t="str">
@@ -37236,11 +36585,11 @@
         <v/>
       </c>
       <c r="AG105" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH105" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI105" s="13" t="str">
@@ -37314,18 +36663,11 @@
         <v>938</v>
       </c>
       <c r="R106" s="9" t="str">
-        <f>IF(
-  AND(
-    $A106&lt;&gt;"",
-    COUNTIF(C:C,$A106)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S106" s="9" t="str">
-        <f t="shared" ref="S106:S151" si="12">IF(
+        <f t="shared" ref="S106:S151" si="14">IF(
   OR(
     $H106="",
     $H106="-",
@@ -37456,7 +36798,7 @@
         <v>113</v>
       </c>
       <c r="AC106" s="20" t="str">
-        <f t="shared" ref="AC106:AC151" si="13">IF(AND($M106&lt;&gt;"",$M106&lt;&gt;"-")," (&amp;"&amp;$M106&amp;")","")</f>
+        <f t="shared" ref="AC106:AC151" si="15">IF(AND($M106&lt;&gt;"",$M106&lt;&gt;"-")," (&amp;"&amp;$M106&amp;")","")</f>
         <v/>
       </c>
       <c r="AD106" s="13" t="str">
@@ -37490,7 +36832,7 @@
         <v/>
       </c>
       <c r="AG106" s="13" t="str">
-        <f t="shared" ref="AG106:AG151" si="14">IF(
+        <f t="shared" ref="AG106:AG151" si="16">IF(
   AND($A106&lt;&gt;"",$O106&lt;&gt;"-",$O106&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O106&amp;""" /tr """&amp;$C106&amp;""" /sc daily /st "&amp;$P106&amp;" /rl highest"
@@ -37500,7 +36842,7 @@
         <v/>
       </c>
       <c r="AH106" s="13" t="str">
-        <f t="shared" ref="AH106:AH151" si="15">IF(
+        <f t="shared" ref="AH106:AH151" si="17">IF(
   AND($A106&lt;&gt;"",$O106&lt;&gt;"-",$O106&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O106&amp;""""
@@ -37580,18 +36922,11 @@
         <v>938</v>
       </c>
       <c r="R107" s="9" t="str">
-        <f>IF(
-  AND(
-    $A107&lt;&gt;"",
-    COUNTIF(C:C,$A107)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S107" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T107" s="13" t="str">
@@ -37714,7 +37049,7 @@
         <v>171</v>
       </c>
       <c r="AC107" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD107" s="13" t="str">
@@ -37748,11 +37083,11 @@
         <v/>
       </c>
       <c r="AG107" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH107" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI107" s="13" t="str">
@@ -37826,18 +37161,11 @@
         <v>938</v>
       </c>
       <c r="R108" s="9" t="str">
-        <f>IF(
-  AND(
-    $A108&lt;&gt;"",
-    COUNTIF(C:C,$A108)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S108" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T108" s="13" t="str">
@@ -37960,7 +37288,7 @@
         <v>123</v>
       </c>
       <c r="AC108" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD108" s="13" t="str">
@@ -37994,11 +37322,11 @@
         <v/>
       </c>
       <c r="AG108" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH108" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI108" s="13" t="str">
@@ -38072,18 +37400,11 @@
         <v>938</v>
       </c>
       <c r="R109" s="9" t="str">
-        <f>IF(
-  AND(
-    $A109&lt;&gt;"",
-    COUNTIF(C:C,$A109)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S109" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T109" s="13" t="str">
@@ -38206,7 +37527,7 @@
         <v>122</v>
       </c>
       <c r="AC109" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD109" s="13" t="str">
@@ -38240,11 +37561,11 @@
         <v/>
       </c>
       <c r="AG109" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH109" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI109" s="13" t="str">
@@ -38318,18 +37639,11 @@
         <v>938</v>
       </c>
       <c r="R110" s="9" t="str">
-        <f>IF(
-  AND(
-    $A110&lt;&gt;"",
-    COUNTIF(C:C,$A110)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S110" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T110" s="13" t="str">
@@ -38452,7 +37766,7 @@
         <v>172</v>
       </c>
       <c r="AC110" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD110" s="13" t="str">
@@ -38486,11 +37800,11 @@
         <v/>
       </c>
       <c r="AG110" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH110" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI110" s="13" t="str">
@@ -38564,18 +37878,11 @@
         <v>938</v>
       </c>
       <c r="R111" s="9" t="str">
-        <f>IF(
-  AND(
-    $A111&lt;&gt;"",
-    COUNTIF(C:C,$A111)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S111" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T111" s="13" t="str">
@@ -38698,7 +38005,7 @@
         <v>172</v>
       </c>
       <c r="AC111" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD111" s="13" t="str">
@@ -38732,11 +38039,11 @@
         <v/>
       </c>
       <c r="AG111" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH111" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI111" s="13" t="str">
@@ -38810,18 +38117,11 @@
         <v>938</v>
       </c>
       <c r="R112" s="9" t="str">
-        <f>IF(
-  AND(
-    $A112&lt;&gt;"",
-    COUNTIF(C:C,$A112)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S112" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T112" s="13" t="str">
@@ -38944,7 +38244,7 @@
         <v>122</v>
       </c>
       <c r="AC112" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD112" s="13" t="str">
@@ -38978,11 +38278,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\X-Finder（ファイラー）.lnk</v>
       </c>
       <c r="AG112" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH112" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI112" s="13" t="str">
@@ -39056,18 +38356,11 @@
         <v>938</v>
       </c>
       <c r="R113" s="9" t="str">
-        <f>IF(
-  AND(
-    $A113&lt;&gt;"",
-    COUNTIF(C:C,$A113)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S113" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T113" s="13" t="str">
@@ -39190,7 +38483,7 @@
         <v>162</v>
       </c>
       <c r="AC113" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD113" s="13" t="str">
@@ -39224,11 +38517,11 @@
         <v/>
       </c>
       <c r="AG113" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH113" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI113" s="13" t="str">
@@ -39302,18 +38595,11 @@
         <v>938</v>
       </c>
       <c r="R114" s="9" t="str">
-        <f>IF(
-  AND(
-    $A114&lt;&gt;"",
-    COUNTIF(C:C,$A114)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S114" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T114" s="13" t="str">
@@ -39436,7 +38722,7 @@
         <v>172</v>
       </c>
       <c r="AC114" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD114" s="13" t="str">
@@ -39470,11 +38756,11 @@
         <v/>
       </c>
       <c r="AG114" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH114" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI114" s="13" t="str">
@@ -39548,18 +38834,11 @@
         <v>1115</v>
       </c>
       <c r="R115" s="9" t="str">
-        <f>IF(
-  AND(
-    $A115&lt;&gt;"",
-    COUNTIF(C:C,$A115)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S115" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T115" s="13" t="str">
@@ -39682,7 +38961,7 @@
         <v>162</v>
       </c>
       <c r="AC115" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD115" s="13" t="str">
@@ -39716,11 +38995,11 @@
         <v/>
       </c>
       <c r="AG115" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH115" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI115" s="13" t="str">
@@ -39794,18 +39073,11 @@
         <v>1165</v>
       </c>
       <c r="R116" s="9" t="str">
-        <f>IF(
-  AND(
-    $A116&lt;&gt;"",
-    COUNTIF(C:C,$A116)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S116" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T116" s="13" t="str">
@@ -39928,7 +39200,7 @@
         <v>171</v>
       </c>
       <c r="AC116" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD116" s="13" t="str">
@@ -39962,11 +39234,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\HiddeX（ボスが来た）.lnk</v>
       </c>
       <c r="AG116" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH116" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI116" s="13" t="str">
@@ -40040,18 +39312,11 @@
         <v>937</v>
       </c>
       <c r="R117" s="9" t="str">
-        <f>IF(
-  AND(
-    $A117&lt;&gt;"",
-    COUNTIF(C:C,$A117)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S117" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T117" s="13" t="str">
@@ -40174,7 +39439,7 @@
         <v>113</v>
       </c>
       <c r="AC117" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD117" s="13" t="str">
@@ -40208,11 +39473,11 @@
         <v/>
       </c>
       <c r="AG117" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH117" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI117" s="13" t="str">
@@ -40286,18 +39551,11 @@
         <v>937</v>
       </c>
       <c r="R118" s="9" t="str">
-        <f>IF(
-  AND(
-    $A118&lt;&gt;"",
-    COUNTIF(C:C,$A118)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S118" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T118" s="13" t="str">
@@ -40420,7 +39678,7 @@
         <v>113</v>
       </c>
       <c r="AC118" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD118" s="13" t="str">
@@ -40454,11 +39712,11 @@
         <v/>
       </c>
       <c r="AG118" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH118" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI118" s="13" t="str">
@@ -40532,14 +39790,7 @@
         <v>1408</v>
       </c>
       <c r="R119" s="9" t="str">
-        <f>IF(
-  AND(
-    $A119&lt;&gt;"",
-    COUNTIF(C:C,$A119)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S119" s="9" t="str">
@@ -40798,18 +40049,11 @@
         <v>1249</v>
       </c>
       <c r="R120" s="9" t="str">
-        <f>IF(
-  AND(
-    $A120&lt;&gt;"",
-    COUNTIF(C:C,$A120)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S120" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T120" s="13" t="str">
@@ -40932,7 +40176,7 @@
         <v>143</v>
       </c>
       <c r="AC120" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD120" s="13" t="str">
@@ -40966,11 +40210,11 @@
         <v/>
       </c>
       <c r="AG120" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH120" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI120" s="13" t="str">
@@ -41044,18 +40288,11 @@
         <v>39</v>
       </c>
       <c r="R121" s="9" t="str">
-        <f>IF(
-  AND(
-    $A121&lt;&gt;"",
-    COUNTIF(C:C,$A121)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S121" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T121" s="13" t="str">
@@ -41178,7 +40415,7 @@
         <v>171</v>
       </c>
       <c r="AC121" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD121" s="13" t="str">
@@ -41212,11 +40449,11 @@
         <v/>
       </c>
       <c r="AG121" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH121" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI121" s="13" t="str">
@@ -41290,18 +40527,11 @@
         <v>1376</v>
       </c>
       <c r="R122" s="9" t="str">
-        <f>IF(
-  AND(
-    $A122&lt;&gt;"",
-    COUNTIF(C:C,$A122)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S122" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T122" s="13" t="str">
@@ -41424,7 +40654,7 @@
         <v>123</v>
       </c>
       <c r="AC122" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD122" s="13" t="str">
@@ -41458,11 +40688,11 @@
         <v/>
       </c>
       <c r="AG122" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH122" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI122" s="13" t="str">
@@ -41536,18 +40766,11 @@
         <v>1379</v>
       </c>
       <c r="R123" s="9" t="str">
-        <f>IF(
-  AND(
-    $A123&lt;&gt;"",
-    COUNTIF(C:C,$A123)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S123" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T123" s="13" t="str">
@@ -41670,7 +40893,7 @@
         <v>153</v>
       </c>
       <c r="AC123" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD123" s="13" t="str">
@@ -41704,11 +40927,11 @@
         <v/>
       </c>
       <c r="AG123" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH123" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI123" s="13" t="str">
@@ -41782,14 +41005,7 @@
         <v>1401</v>
       </c>
       <c r="R124" s="9" t="str">
-        <f>IF(
-  AND(
-    $A124&lt;&gt;"",
-    COUNTIF(C:C,$A124)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S124" s="9" t="str">
@@ -42048,14 +41264,7 @@
         <v>1412</v>
       </c>
       <c r="R125" s="9" t="str">
-        <f>IF(
-  AND(
-    $A125&lt;&gt;"",
-    COUNTIF(C:C,$A125)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S125" s="9" t="str">
@@ -42314,14 +41523,7 @@
         <v>1420</v>
       </c>
       <c r="R126" s="9" t="str">
-        <f>IF(
-  AND(
-    $A126&lt;&gt;"",
-    COUNTIF(C:C,$A126)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S126" s="9" t="str">
@@ -42580,18 +41782,11 @@
         <v>39</v>
       </c>
       <c r="R127" s="9" t="str">
-        <f>IF(
-  AND(
-    $A127&lt;&gt;"",
-    COUNTIF(C:C,$A127)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S127" s="9" t="str">
-        <f t="shared" ref="S127" si="16">IF(
+        <f t="shared" ref="S127" si="18">IF(
   OR(
     $H127="",
     $H127="-",
@@ -42722,7 +41917,7 @@
         <v>113</v>
       </c>
       <c r="AC127" s="20" t="str">
-        <f t="shared" ref="AC127" si="17">IF(AND($M127&lt;&gt;"",$M127&lt;&gt;"-")," (&amp;"&amp;$M127&amp;")","")</f>
+        <f t="shared" ref="AC127" si="19">IF(AND($M127&lt;&gt;"",$M127&lt;&gt;"-")," (&amp;"&amp;$M127&amp;")","")</f>
         <v/>
       </c>
       <c r="AD127" s="13" t="str">
@@ -42756,7 +41951,7 @@
         <v/>
       </c>
       <c r="AG127" s="13" t="str">
-        <f t="shared" ref="AG127" si="18">IF(
+        <f t="shared" ref="AG127" si="20">IF(
   AND($A127&lt;&gt;"",$O127&lt;&gt;"-",$O127&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O127&amp;""" /tr """&amp;$C127&amp;""" /sc daily /st "&amp;$P127&amp;" /rl highest"
@@ -42766,7 +41961,7 @@
         <v/>
       </c>
       <c r="AH127" s="13" t="str">
-        <f t="shared" ref="AH127" si="19">IF(
+        <f t="shared" ref="AH127" si="21">IF(
   AND($A127&lt;&gt;"",$O127&lt;&gt;"-",$O127&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O127&amp;""""
@@ -42846,14 +42041,7 @@
         <v>1444</v>
       </c>
       <c r="R128" s="9" t="str">
-        <f>IF(
-  AND(
-    $A128&lt;&gt;"",
-    COUNTIF(C:C,$A128)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S128" s="9" t="str">
@@ -43112,14 +42300,7 @@
         <v>39</v>
       </c>
       <c r="R129" s="9" t="str">
-        <f>IF(
-  AND(
-    $A129&lt;&gt;"",
-    COUNTIF(C:C,$A129)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S129" s="9" t="str">
@@ -43378,14 +42559,7 @@
         <v>39</v>
       </c>
       <c r="R130" s="9" t="str">
-        <f>IF(
-  AND(
-    $A130&lt;&gt;"",
-    COUNTIF(C:C,$A130)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S130" s="9" t="str">
@@ -43644,18 +42818,11 @@
         <v>938</v>
       </c>
       <c r="R131" s="9" t="str">
-        <f>IF(
-  AND(
-    $A131&lt;&gt;"",
-    COUNTIF(C:C,$A131)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S131" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T131" s="13" t="str">
@@ -43778,7 +42945,7 @@
         <v>123</v>
       </c>
       <c r="AC131" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD131" s="13" t="str">
@@ -43812,11 +42979,11 @@
         <v/>
       </c>
       <c r="AG131" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH131" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI131" s="13" t="str">
@@ -43890,18 +43057,11 @@
         <v>938</v>
       </c>
       <c r="R132" s="9" t="str">
-        <f>IF(
-  AND(
-    $A132&lt;&gt;"",
-    COUNTIF(C:C,$A132)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S132" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T132" s="13" t="str">
@@ -44024,7 +43184,7 @@
         <v>133</v>
       </c>
       <c r="AC132" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD132" s="13" t="str">
@@ -44058,11 +43218,11 @@
         <v/>
       </c>
       <c r="AG132" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH132" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI132" s="13" t="str">
@@ -44136,18 +43296,11 @@
         <v>938</v>
       </c>
       <c r="R133" s="9" t="str">
-        <f>IF(
-  AND(
-    $A133&lt;&gt;"",
-    COUNTIF(C:C,$A133)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S133" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T133" s="13" t="str">
@@ -44270,7 +43423,7 @@
         <v>172</v>
       </c>
       <c r="AC133" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD133" s="13" t="str">
@@ -44304,11 +43457,11 @@
         <v/>
       </c>
       <c r="AG133" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH133" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI133" s="13" t="str">
@@ -44382,18 +43535,11 @@
         <v>938</v>
       </c>
       <c r="R134" s="9" t="str">
-        <f>IF(
-  AND(
-    $A134&lt;&gt;"",
-    COUNTIF(C:C,$A134)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S134" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T134" s="13" t="str">
@@ -44516,7 +43662,7 @@
         <v>123</v>
       </c>
       <c r="AC134" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD134" s="13" t="str">
@@ -44550,11 +43696,11 @@
         <v/>
       </c>
       <c r="AG134" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH134" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI134" s="13" t="str">
@@ -44628,18 +43774,11 @@
         <v>938</v>
       </c>
       <c r="R135" s="9" t="str">
-        <f>IF(
-  AND(
-    $A135&lt;&gt;"",
-    COUNTIF(C:C,$A135)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S135" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T135" s="13" t="str">
@@ -44762,7 +43901,7 @@
         <v>123</v>
       </c>
       <c r="AC135" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD135" s="13" t="str">
@@ -44796,11 +43935,11 @@
         <v/>
       </c>
       <c r="AG135" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH135" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI135" s="13" t="str">
@@ -44874,18 +44013,11 @@
         <v>39</v>
       </c>
       <c r="R136" s="9" t="str">
-        <f>IF(
-  AND(
-    $A136&lt;&gt;"",
-    COUNTIF(C:C,$A136)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S136" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T136" s="13" t="str">
@@ -45008,7 +44140,7 @@
         <v>113</v>
       </c>
       <c r="AC136" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD136" s="13" t="str">
@@ -45042,11 +44174,11 @@
         <v/>
       </c>
       <c r="AG136" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH136" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI136" s="13" t="str">
@@ -45120,18 +44252,11 @@
         <v>1379</v>
       </c>
       <c r="R137" s="9" t="str">
-        <f>IF(
-  AND(
-    $A137&lt;&gt;"",
-    COUNTIF(C:C,$A137)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S137" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T137" s="13" t="str">
@@ -45254,7 +44379,7 @@
         <v>123</v>
       </c>
       <c r="AC137" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD137" s="13" t="str">
@@ -45288,11 +44413,11 @@
         <v/>
       </c>
       <c r="AG137" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH137" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI137" s="13" t="str">
@@ -45366,14 +44491,7 @@
         <v>1392</v>
       </c>
       <c r="R138" s="9" t="str">
-        <f>IF(
-  AND(
-    $A138&lt;&gt;"",
-    COUNTIF(C:C,$A138)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S138" s="9" t="str">
@@ -45632,7 +44750,7 @@
         <v>39</v>
       </c>
       <c r="R139" s="9" t="str">
-        <f>IF(
+        <f t="shared" ref="R139:R202" si="22">IF(
   AND(
     $A139&lt;&gt;"",
     COUNTIF(C:C,$A139)&gt;1
@@ -45898,14 +45016,7 @@
         <v>1441</v>
       </c>
       <c r="R140" s="9" t="str">
-        <f>IF(
-  AND(
-    $A140&lt;&gt;"",
-    COUNTIF(C:C,$A140)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S140" s="9" t="str">
@@ -46164,14 +45275,7 @@
         <v>39</v>
       </c>
       <c r="R141" s="9" t="str">
-        <f>IF(
-  AND(
-    $A141&lt;&gt;"",
-    COUNTIF(C:C,$A141)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S141" s="9" t="str">
@@ -46430,14 +45534,7 @@
         <v>39</v>
       </c>
       <c r="R142" s="9" t="str">
-        <f>IF(
-  AND(
-    $A142&lt;&gt;"",
-    COUNTIF(C:C,$A142)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S142" s="9" t="str">
@@ -46696,18 +45793,11 @@
         <v>39</v>
       </c>
       <c r="R143" s="9" t="str">
-        <f>IF(
-  AND(
-    $A143&lt;&gt;"",
-    COUNTIF(C:C,$A143)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S143" s="9" t="str">
-        <f t="shared" ref="S143" si="20">IF(
+        <f t="shared" ref="S143" si="23">IF(
   OR(
     $H143="",
     $H143="-",
@@ -46838,7 +45928,7 @@
         <v>162</v>
       </c>
       <c r="AC143" s="20" t="str">
-        <f t="shared" ref="AC143" si="21">IF(AND($M143&lt;&gt;"",$M143&lt;&gt;"-")," (&amp;"&amp;$M143&amp;")","")</f>
+        <f t="shared" ref="AC143" si="24">IF(AND($M143&lt;&gt;"",$M143&lt;&gt;"-")," (&amp;"&amp;$M143&amp;")","")</f>
         <v/>
       </c>
       <c r="AD143" s="13" t="str">
@@ -46872,7 +45962,7 @@
         <v/>
       </c>
       <c r="AG143" s="13" t="str">
-        <f t="shared" ref="AG143" si="22">IF(
+        <f t="shared" ref="AG143" si="25">IF(
   AND($A143&lt;&gt;"",$O143&lt;&gt;"-",$O143&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O143&amp;""" /tr """&amp;$C143&amp;""" /sc daily /st "&amp;$P143&amp;" /rl highest"
@@ -46882,7 +45972,7 @@
         <v/>
       </c>
       <c r="AH143" s="13" t="str">
-        <f t="shared" ref="AH143" si="23">IF(
+        <f t="shared" ref="AH143" si="26">IF(
   AND($A143&lt;&gt;"",$O143&lt;&gt;"-",$O143&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O143&amp;""""
@@ -46962,18 +46052,11 @@
         <v>938</v>
       </c>
       <c r="R144" s="9" t="str">
-        <f>IF(
-  AND(
-    $A144&lt;&gt;"",
-    COUNTIF(C:C,$A144)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S144" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T144" s="13" t="str">
@@ -47096,7 +46179,7 @@
         <v>161</v>
       </c>
       <c r="AC144" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD144" s="13" t="str">
@@ -47130,11 +46213,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\MicrosoftEdge（ブラウザ）.lnk</v>
       </c>
       <c r="AG144" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH144" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI144" s="13" t="str">
@@ -47208,18 +46291,11 @@
         <v>938</v>
       </c>
       <c r="R145" s="9" t="str">
-        <f>IF(
-  AND(
-    $A145&lt;&gt;"",
-    COUNTIF(C:C,$A145)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S145" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T145" s="13" t="str">
@@ -47342,7 +46418,7 @@
         <v>123</v>
       </c>
       <c r="AC145" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD145" s="13" t="str">
@@ -47376,11 +46452,11 @@
         <v/>
       </c>
       <c r="AG145" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH145" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI145" s="13" t="str">
@@ -47454,18 +46530,11 @@
         <v>938</v>
       </c>
       <c r="R146" s="9" t="str">
-        <f>IF(
-  AND(
-    $A146&lt;&gt;"",
-    COUNTIF(C:C,$A146)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S146" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T146" s="13" t="str">
@@ -47588,7 +46657,7 @@
         <v>123</v>
       </c>
       <c r="AC146" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD146" s="13" t="str">
@@ -47622,11 +46691,11 @@
         <v/>
       </c>
       <c r="AG146" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH146" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI146" s="13" t="str">
@@ -47700,18 +46769,11 @@
         <v>938</v>
       </c>
       <c r="R147" s="9" t="str">
-        <f>IF(
-  AND(
-    $A147&lt;&gt;"",
-    COUNTIF(C:C,$A147)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S147" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T147" s="13" t="str">
@@ -47834,7 +46896,7 @@
         <v>123</v>
       </c>
       <c r="AC147" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD147" s="13" t="str">
@@ -47868,11 +46930,11 @@
         <v/>
       </c>
       <c r="AG147" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH147" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI147" s="13" t="str">
@@ -47946,18 +47008,11 @@
         <v>938</v>
       </c>
       <c r="R148" s="9" t="str">
-        <f>IF(
-  AND(
-    $A148&lt;&gt;"",
-    COUNTIF(C:C,$A148)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S148" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T148" s="13" t="str">
@@ -48080,7 +47135,7 @@
         <v>161</v>
       </c>
       <c r="AC148" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD148" s="13" t="str">
@@ -48114,11 +47169,11 @@
         <v/>
       </c>
       <c r="AG148" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH148" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI148" s="13" t="str">
@@ -48192,18 +47247,11 @@
         <v>938</v>
       </c>
       <c r="R149" s="9" t="str">
-        <f>IF(
-  AND(
-    $A149&lt;&gt;"",
-    COUNTIF(C:C,$A149)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S149" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T149" s="13" t="str">
@@ -48326,7 +47374,7 @@
         <v>153</v>
       </c>
       <c r="AC149" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD149" s="13" t="str">
@@ -48360,11 +47408,11 @@
         <v/>
       </c>
       <c r="AG149" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH149" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI149" s="13" t="str">
@@ -48438,18 +47486,11 @@
         <v>938</v>
       </c>
       <c r="R150" s="9" t="str">
-        <f>IF(
-  AND(
-    $A150&lt;&gt;"",
-    COUNTIF(C:C,$A150)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S150" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T150" s="13" t="str">
@@ -48572,7 +47613,7 @@
         <v>122</v>
       </c>
       <c r="AC150" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD150" s="13" t="str">
@@ -48606,11 +47647,11 @@
         <v/>
       </c>
       <c r="AG150" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH150" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI150" s="13" t="str">
@@ -48684,18 +47725,11 @@
         <v>938</v>
       </c>
       <c r="R151" s="9" t="str">
-        <f>IF(
-  AND(
-    $A151&lt;&gt;"",
-    COUNTIF(C:C,$A151)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S151" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T151" s="13" t="str">
@@ -48818,7 +47852,7 @@
         <v>161</v>
       </c>
       <c r="AC151" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD151" s="13" t="str">
@@ -48852,11 +47886,11 @@
         <v/>
       </c>
       <c r="AG151" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH151" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI151" s="13" t="str">
@@ -48930,14 +47964,7 @@
         <v>1435</v>
       </c>
       <c r="R152" s="9" t="str">
-        <f>IF(
-  AND(
-    $A152&lt;&gt;"",
-    COUNTIF(C:C,$A152)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S152" s="9" t="str">
@@ -49196,18 +48223,11 @@
         <v>938</v>
       </c>
       <c r="R153" s="9" t="str">
-        <f>IF(
-  AND(
-    $A153&lt;&gt;"",
-    COUNTIF(C:C,$A153)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S153" s="9" t="str">
-        <f t="shared" ref="S153:S185" si="24">IF(
+        <f t="shared" ref="S153:S185" si="27">IF(
   OR(
     $H153="",
     $H153="-",
@@ -49338,7 +48358,7 @@
         <v>161</v>
       </c>
       <c r="AC153" s="20" t="str">
-        <f t="shared" ref="AC153:AC185" si="25">IF(AND($M153&lt;&gt;"",$M153&lt;&gt;"-")," (&amp;"&amp;$M153&amp;")","")</f>
+        <f t="shared" ref="AC153:AC185" si="28">IF(AND($M153&lt;&gt;"",$M153&lt;&gt;"-")," (&amp;"&amp;$M153&amp;")","")</f>
         <v/>
       </c>
       <c r="AD153" s="13" t="str">
@@ -49372,7 +48392,7 @@
         <v/>
       </c>
       <c r="AG153" s="13" t="str">
-        <f t="shared" ref="AG153:AG185" si="26">IF(
+        <f t="shared" ref="AG153:AG185" si="29">IF(
   AND($A153&lt;&gt;"",$O153&lt;&gt;"-",$O153&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O153&amp;""" /tr """&amp;$C153&amp;""" /sc daily /st "&amp;$P153&amp;" /rl highest"
@@ -49382,7 +48402,7 @@
         <v/>
       </c>
       <c r="AH153" s="13" t="str">
-        <f t="shared" ref="AH153:AH185" si="27">IF(
+        <f t="shared" ref="AH153:AH185" si="30">IF(
   AND($A153&lt;&gt;"",$O153&lt;&gt;"-",$O153&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O153&amp;""""
@@ -49462,18 +48482,11 @@
         <v>39</v>
       </c>
       <c r="R154" s="9" t="str">
-        <f>IF(
-  AND(
-    $A154&lt;&gt;"",
-    COUNTIF(C:C,$A154)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S154" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T154" s="13" t="str">
@@ -49596,7 +48609,7 @@
         <v>172</v>
       </c>
       <c r="AC154" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD154" s="13" t="str">
@@ -49630,11 +48643,11 @@
         <v/>
       </c>
       <c r="AG154" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH154" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI154" s="13" t="str">
@@ -49708,18 +48721,11 @@
         <v>39</v>
       </c>
       <c r="R155" s="9" t="str">
-        <f>IF(
-  AND(
-    $A155&lt;&gt;"",
-    COUNTIF(C:C,$A155)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S155" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T155" s="13" t="str">
@@ -49842,7 +48848,7 @@
         <v>172</v>
       </c>
       <c r="AC155" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD155" s="13" t="str">
@@ -49876,11 +48882,11 @@
         <v/>
       </c>
       <c r="AG155" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH155" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI155" s="13" t="str">
@@ -49954,18 +48960,11 @@
         <v>39</v>
       </c>
       <c r="R156" s="9" t="str">
-        <f>IF(
-  AND(
-    $A156&lt;&gt;"",
-    COUNTIF(C:C,$A156)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S156" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T156" s="13" t="str">
@@ -50088,7 +49087,7 @@
         <v>200</v>
       </c>
       <c r="AC156" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD156" s="13" t="str">
@@ -50122,11 +49121,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\UserDefHotKey2.bat（ホットキー）.lnk</v>
       </c>
       <c r="AG156" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH156" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI156" s="13" t="str">
@@ -50200,14 +49199,7 @@
         <v>1507</v>
       </c>
       <c r="R157" s="9" t="str">
-        <f>IF(
-  AND(
-    $A157&lt;&gt;"",
-    COUNTIF(C:C,$A157)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S157" s="9" t="str">
@@ -50466,18 +49458,11 @@
         <v>938</v>
       </c>
       <c r="R158" s="9" t="str">
-        <f>IF(
-  AND(
-    $A158&lt;&gt;"",
-    COUNTIF(C:C,$A158)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S158" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T158" s="13" t="str">
@@ -50600,7 +49585,7 @@
         <v>200</v>
       </c>
       <c r="AC158" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD158" s="13" t="str">
@@ -50634,11 +49619,11 @@
         <v/>
       </c>
       <c r="AG158" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH158" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI158" s="13" t="str">
@@ -50712,18 +49697,11 @@
         <v>938</v>
       </c>
       <c r="R159" s="9" t="str">
-        <f>IF(
-  AND(
-    $A159&lt;&gt;"",
-    COUNTIF(C:C,$A159)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S159" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T159" s="13" t="str">
@@ -50846,7 +49824,7 @@
         <v>200</v>
       </c>
       <c r="AC159" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD159" s="13" t="str">
@@ -50880,11 +49858,11 @@
         <v/>
       </c>
       <c r="AG159" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH159" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI159" s="13" t="str">
@@ -50958,18 +49936,11 @@
         <v>938</v>
       </c>
       <c r="R160" s="9" t="str">
-        <f>IF(
-  AND(
-    $A160&lt;&gt;"",
-    COUNTIF(C:C,$A160)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S160" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T160" s="13" t="str">
@@ -51092,7 +50063,7 @@
         <v>200</v>
       </c>
       <c r="AC160" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD160" s="13" t="str">
@@ -51126,11 +50097,11 @@
         <v/>
       </c>
       <c r="AG160" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH160" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI160" s="13" t="str">
@@ -51204,18 +50175,11 @@
         <v>938</v>
       </c>
       <c r="R161" s="9" t="str">
-        <f>IF(
-  AND(
-    $A161&lt;&gt;"",
-    COUNTIF(C:C,$A161)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S161" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T161" s="13" t="str">
@@ -51338,7 +50302,7 @@
         <v>200</v>
       </c>
       <c r="AC161" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD161" s="13" t="str">
@@ -51372,11 +50336,11 @@
         <v/>
       </c>
       <c r="AG161" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH161" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI161" s="13" t="str">
@@ -51450,18 +50414,11 @@
         <v>938</v>
       </c>
       <c r="R162" s="9" t="str">
-        <f>IF(
-  AND(
-    $A162&lt;&gt;"",
-    COUNTIF(C:C,$A162)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S162" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T162" s="13" t="str">
@@ -51584,7 +50541,7 @@
         <v>200</v>
       </c>
       <c r="AC162" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD162" s="13" t="str">
@@ -51618,11 +50575,11 @@
         <v/>
       </c>
       <c r="AG162" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH162" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI162" s="13" t="str">
@@ -51696,18 +50653,11 @@
         <v>938</v>
       </c>
       <c r="R163" s="9" t="str">
-        <f>IF(
-  AND(
-    $A163&lt;&gt;"",
-    COUNTIF(C:C,$A163)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S163" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T163" s="13" t="str">
@@ -51830,7 +50780,7 @@
         <v>200</v>
       </c>
       <c r="AC163" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD163" s="13" t="str">
@@ -51864,11 +50814,11 @@
         <v/>
       </c>
       <c r="AG163" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH163" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI163" s="13" t="str">
@@ -51942,18 +50892,11 @@
         <v>938</v>
       </c>
       <c r="R164" s="9" t="str">
-        <f>IF(
-  AND(
-    $A164&lt;&gt;"",
-    COUNTIF(C:C,$A164)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S164" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T164" s="13" t="str">
@@ -52076,7 +51019,7 @@
         <v>200</v>
       </c>
       <c r="AC164" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD164" s="13" t="str">
@@ -52110,11 +51053,11 @@
         <v/>
       </c>
       <c r="AG164" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH164" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI164" s="13" t="str">
@@ -52188,18 +51131,11 @@
         <v>938</v>
       </c>
       <c r="R165" s="9" t="str">
-        <f>IF(
-  AND(
-    $A165&lt;&gt;"",
-    COUNTIF(C:C,$A165)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S165" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T165" s="13" t="str">
@@ -52322,7 +51258,7 @@
         <v>200</v>
       </c>
       <c r="AC165" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD165" s="13" t="str">
@@ -52356,11 +51292,11 @@
         <v/>
       </c>
       <c r="AG165" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH165" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI165" s="13" t="str">
@@ -52434,18 +51370,11 @@
         <v>938</v>
       </c>
       <c r="R166" s="9" t="str">
-        <f>IF(
-  AND(
-    $A166&lt;&gt;"",
-    COUNTIF(C:C,$A166)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S166" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T166" s="13" t="str">
@@ -52568,7 +51497,7 @@
         <v>200</v>
       </c>
       <c r="AC166" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD166" s="13" t="str">
@@ -52602,11 +51531,11 @@
         <v/>
       </c>
       <c r="AG166" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH166" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI166" s="13" t="str">
@@ -52680,18 +51609,11 @@
         <v>938</v>
       </c>
       <c r="R167" s="9" t="str">
-        <f>IF(
-  AND(
-    $A167&lt;&gt;"",
-    COUNTIF(C:C,$A167)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S167" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T167" s="13" t="str">
@@ -52814,7 +51736,7 @@
         <v>200</v>
       </c>
       <c r="AC167" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD167" s="13" t="str">
@@ -52848,11 +51770,11 @@
         <v/>
       </c>
       <c r="AG167" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH167" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI167" s="13" t="str">
@@ -52926,18 +51848,11 @@
         <v>938</v>
       </c>
       <c r="R168" s="9" t="str">
-        <f>IF(
-  AND(
-    $A168&lt;&gt;"",
-    COUNTIF(C:C,$A168)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S168" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T168" s="13" t="str">
@@ -53060,7 +51975,7 @@
         <v>200</v>
       </c>
       <c r="AC168" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD168" s="13" t="str">
@@ -53094,11 +52009,11 @@
         <v/>
       </c>
       <c r="AG168" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH168" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI168" s="13" t="str">
@@ -53172,18 +52087,11 @@
         <v>938</v>
       </c>
       <c r="R169" s="9" t="str">
-        <f>IF(
-  AND(
-    $A169&lt;&gt;"",
-    COUNTIF(C:C,$A169)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S169" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T169" s="13" t="str">
@@ -53306,7 +52214,7 @@
         <v>200</v>
       </c>
       <c r="AC169" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD169" s="13" t="str">
@@ -53340,11 +52248,11 @@
         <v/>
       </c>
       <c r="AG169" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH169" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI169" s="13" t="str">
@@ -53418,18 +52326,11 @@
         <v>938</v>
       </c>
       <c r="R170" s="9" t="str">
-        <f>IF(
-  AND(
-    $A170&lt;&gt;"",
-    COUNTIF(C:C,$A170)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S170" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T170" s="13" t="str">
@@ -53552,7 +52453,7 @@
         <v>200</v>
       </c>
       <c r="AC170" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD170" s="13" t="str">
@@ -53586,11 +52487,11 @@
         <v/>
       </c>
       <c r="AG170" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH170" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI170" s="13" t="str">
@@ -53664,18 +52565,11 @@
         <v>938</v>
       </c>
       <c r="R171" s="9" t="str">
-        <f>IF(
-  AND(
-    $A171&lt;&gt;"",
-    COUNTIF(C:C,$A171)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S171" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T171" s="13" t="str">
@@ -53798,7 +52692,7 @@
         <v>200</v>
       </c>
       <c r="AC171" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD171" s="13" t="str">
@@ -53832,11 +52726,11 @@
         <v/>
       </c>
       <c r="AG171" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH171" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI171" s="13" t="str">
@@ -53910,18 +52804,11 @@
         <v>938</v>
       </c>
       <c r="R172" s="9" t="str">
-        <f>IF(
-  AND(
-    $A172&lt;&gt;"",
-    COUNTIF(C:C,$A172)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S172" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T172" s="13" t="str">
@@ -54044,7 +52931,7 @@
         <v>200</v>
       </c>
       <c r="AC172" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD172" s="13" t="str">
@@ -54078,11 +52965,11 @@
         <v/>
       </c>
       <c r="AG172" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH172" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI172" s="13" t="str">
@@ -54156,18 +53043,11 @@
         <v>938</v>
       </c>
       <c r="R173" s="9" t="str">
-        <f>IF(
-  AND(
-    $A173&lt;&gt;"",
-    COUNTIF(C:C,$A173)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S173" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T173" s="13" t="str">
@@ -54290,7 +53170,7 @@
         <v>200</v>
       </c>
       <c r="AC173" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD173" s="13" t="str">
@@ -54324,11 +53204,11 @@
         <v/>
       </c>
       <c r="AG173" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH173" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI173" s="13" t="str">
@@ -54402,18 +53282,11 @@
         <v>938</v>
       </c>
       <c r="R174" s="9" t="str">
-        <f>IF(
-  AND(
-    $A174&lt;&gt;"",
-    COUNTIF(C:C,$A174)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S174" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T174" s="13" t="str">
@@ -54536,7 +53409,7 @@
         <v>200</v>
       </c>
       <c r="AC174" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD174" s="13" t="str">
@@ -54570,11 +53443,11 @@
         <v/>
       </c>
       <c r="AG174" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH174" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI174" s="13" t="str">
@@ -54648,18 +53521,11 @@
         <v>938</v>
       </c>
       <c r="R175" s="9" t="str">
-        <f>IF(
-  AND(
-    $A175&lt;&gt;"",
-    COUNTIF(C:C,$A175)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S175" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T175" s="13" t="str">
@@ -54782,7 +53648,7 @@
         <v>200</v>
       </c>
       <c r="AC175" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD175" s="13" t="str">
@@ -54816,11 +53682,11 @@
         <v/>
       </c>
       <c r="AG175" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH175" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI175" s="13" t="str">
@@ -54894,18 +53760,11 @@
         <v>938</v>
       </c>
       <c r="R176" s="9" t="str">
-        <f>IF(
-  AND(
-    $A176&lt;&gt;"",
-    COUNTIF(C:C,$A176)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S176" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T176" s="13" t="str">
@@ -55028,7 +53887,7 @@
         <v>200</v>
       </c>
       <c r="AC176" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD176" s="13" t="str">
@@ -55062,11 +53921,11 @@
         <v/>
       </c>
       <c r="AG176" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH176" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI176" s="13" t="str">
@@ -55140,18 +53999,11 @@
         <v>938</v>
       </c>
       <c r="R177" s="9" t="str">
-        <f>IF(
-  AND(
-    $A177&lt;&gt;"",
-    COUNTIF(C:C,$A177)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S177" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T177" s="13" t="str">
@@ -55274,7 +54126,7 @@
         <v>200</v>
       </c>
       <c r="AC177" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD177" s="13" t="str">
@@ -55308,11 +54160,11 @@
         <v/>
       </c>
       <c r="AG177" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH177" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI177" s="13" t="str">
@@ -55386,18 +54238,11 @@
         <v>938</v>
       </c>
       <c r="R178" s="9" t="str">
-        <f>IF(
-  AND(
-    $A178&lt;&gt;"",
-    COUNTIF(C:C,$A178)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S178" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T178" s="13" t="str">
@@ -55520,7 +54365,7 @@
         <v>200</v>
       </c>
       <c r="AC178" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD178" s="13" t="str">
@@ -55554,11 +54399,11 @@
         <v/>
       </c>
       <c r="AG178" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH178" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI178" s="13" t="str">
@@ -55632,18 +54477,11 @@
         <v>938</v>
       </c>
       <c r="R179" s="9" t="str">
-        <f>IF(
-  AND(
-    $A179&lt;&gt;"",
-    COUNTIF(C:C,$A179)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S179" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T179" s="13" t="str">
@@ -55766,7 +54604,7 @@
         <v>200</v>
       </c>
       <c r="AC179" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD179" s="13" t="str">
@@ -55800,11 +54638,11 @@
         <v/>
       </c>
       <c r="AG179" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH179" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI179" s="13" t="str">
@@ -55878,18 +54716,11 @@
         <v>938</v>
       </c>
       <c r="R180" s="9" t="str">
-        <f>IF(
-  AND(
-    $A180&lt;&gt;"",
-    COUNTIF(C:C,$A180)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S180" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T180" s="13" t="str">
@@ -56012,7 +54843,7 @@
         <v>200</v>
       </c>
       <c r="AC180" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD180" s="13" t="str">
@@ -56046,11 +54877,11 @@
         <v/>
       </c>
       <c r="AG180" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH180" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI180" s="13" t="str">
@@ -56124,18 +54955,11 @@
         <v>938</v>
       </c>
       <c r="R181" s="9" t="str">
-        <f>IF(
-  AND(
-    $A181&lt;&gt;"",
-    COUNTIF(C:C,$A181)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S181" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T181" s="13" t="str">
@@ -56258,7 +55082,7 @@
         <v>200</v>
       </c>
       <c r="AC181" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD181" s="13" t="str">
@@ -56292,11 +55116,11 @@
         <v/>
       </c>
       <c r="AG181" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH181" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI181" s="13" t="str">
@@ -56370,18 +55194,11 @@
         <v>938</v>
       </c>
       <c r="R182" s="9" t="str">
-        <f>IF(
-  AND(
-    $A182&lt;&gt;"",
-    COUNTIF(C:C,$A182)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S182" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T182" s="13" t="str">
@@ -56504,7 +55321,7 @@
         <v>200</v>
       </c>
       <c r="AC182" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD182" s="13" t="str">
@@ -56538,11 +55355,11 @@
         <v/>
       </c>
       <c r="AG182" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH182" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI182" s="13" t="str">
@@ -56616,18 +55433,11 @@
         <v>938</v>
       </c>
       <c r="R183" s="9" t="str">
-        <f>IF(
-  AND(
-    $A183&lt;&gt;"",
-    COUNTIF(C:C,$A183)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S183" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T183" s="13" t="str">
@@ -56750,7 +55560,7 @@
         <v>200</v>
       </c>
       <c r="AC183" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD183" s="13" t="str">
@@ -56784,11 +55594,11 @@
         <v/>
       </c>
       <c r="AG183" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH183" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI183" s="13" t="str">
@@ -56862,18 +55672,11 @@
         <v>938</v>
       </c>
       <c r="R184" s="9" t="str">
-        <f>IF(
-  AND(
-    $A184&lt;&gt;"",
-    COUNTIF(C:C,$A184)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S184" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T184" s="13" t="str">
@@ -56996,7 +55799,7 @@
         <v>200</v>
       </c>
       <c r="AC184" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD184" s="13" t="str">
@@ -57030,11 +55833,11 @@
         <v/>
       </c>
       <c r="AG184" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH184" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI184" s="13" t="str">
@@ -57108,18 +55911,11 @@
         <v>938</v>
       </c>
       <c r="R185" s="9" t="str">
-        <f>IF(
-  AND(
-    $A185&lt;&gt;"",
-    COUNTIF(C:C,$A185)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S185" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T185" s="13" t="str">
@@ -57242,7 +56038,7 @@
         <v>200</v>
       </c>
       <c r="AC185" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD185" s="13" t="str">
@@ -57276,11 +56072,11 @@
         <v/>
       </c>
       <c r="AG185" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH185" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI185" s="13" t="str">
@@ -57354,18 +56150,11 @@
         <v>938</v>
       </c>
       <c r="R186" s="9" t="str">
-        <f>IF(
-  AND(
-    $A186&lt;&gt;"",
-    COUNTIF(C:C,$A186)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S186" s="9" t="str">
-        <f t="shared" ref="S186:S225" si="28">IF(
+        <f t="shared" ref="S186:S225" si="31">IF(
   OR(
     $H186="",
     $H186="-",
@@ -57496,7 +56285,7 @@
         <v>200</v>
       </c>
       <c r="AC186" s="20" t="str">
-        <f t="shared" ref="AC186:AC225" si="29">IF(AND($M186&lt;&gt;"",$M186&lt;&gt;"-")," (&amp;"&amp;$M186&amp;")","")</f>
+        <f t="shared" ref="AC186:AC225" si="32">IF(AND($M186&lt;&gt;"",$M186&lt;&gt;"-")," (&amp;"&amp;$M186&amp;")","")</f>
         <v/>
       </c>
       <c r="AD186" s="13" t="str">
@@ -57530,7 +56319,7 @@
         <v/>
       </c>
       <c r="AG186" s="13" t="str">
-        <f t="shared" ref="AG186:AG225" si="30">IF(
+        <f t="shared" ref="AG186:AG225" si="33">IF(
   AND($A186&lt;&gt;"",$O186&lt;&gt;"-",$O186&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O186&amp;""" /tr """&amp;$C186&amp;""" /sc daily /st "&amp;$P186&amp;" /rl highest"
@@ -57540,7 +56329,7 @@
         <v/>
       </c>
       <c r="AH186" s="13" t="str">
-        <f t="shared" ref="AH186:AH225" si="31">IF(
+        <f t="shared" ref="AH186:AH225" si="34">IF(
   AND($A186&lt;&gt;"",$O186&lt;&gt;"-",$O186&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O186&amp;""""
@@ -57620,18 +56409,11 @@
         <v>938</v>
       </c>
       <c r="R187" s="9" t="str">
-        <f>IF(
-  AND(
-    $A187&lt;&gt;"",
-    COUNTIF(C:C,$A187)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S187" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T187" s="13" t="str">
@@ -57754,7 +56536,7 @@
         <v>200</v>
       </c>
       <c r="AC187" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v xml:space="preserve"> (&amp;D)</v>
       </c>
       <c r="AD187" s="13" t="str">
@@ -57788,11 +56570,11 @@
         <v/>
       </c>
       <c r="AG187" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH187" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI187" s="13" t="str">
@@ -57866,18 +56648,11 @@
         <v>938</v>
       </c>
       <c r="R188" s="9" t="str">
-        <f>IF(
-  AND(
-    $A188&lt;&gt;"",
-    COUNTIF(C:C,$A188)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S188" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T188" s="13" t="str">
@@ -58000,7 +56775,7 @@
         <v>200</v>
       </c>
       <c r="AC188" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD188" s="13" t="str">
@@ -58034,11 +56809,11 @@
         <v/>
       </c>
       <c r="AG188" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH188" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI188" s="13" t="str">
@@ -58112,18 +56887,11 @@
         <v>938</v>
       </c>
       <c r="R189" s="9" t="str">
-        <f>IF(
-  AND(
-    $A189&lt;&gt;"",
-    COUNTIF(C:C,$A189)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S189" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T189" s="13" t="str">
@@ -58246,7 +57014,7 @@
         <v>200</v>
       </c>
       <c r="AC189" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD189" s="13" t="str">
@@ -58280,11 +57048,11 @@
         <v/>
       </c>
       <c r="AG189" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH189" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI189" s="13" t="str">
@@ -58358,18 +57126,11 @@
         <v>938</v>
       </c>
       <c r="R190" s="9" t="str">
-        <f>IF(
-  AND(
-    $A190&lt;&gt;"",
-    COUNTIF(C:C,$A190)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S190" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T190" s="13" t="str">
@@ -58492,7 +57253,7 @@
         <v>200</v>
       </c>
       <c r="AC190" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v xml:space="preserve"> (&amp;U)</v>
       </c>
       <c r="AD190" s="13" t="str">
@@ -58526,11 +57287,11 @@
         <v/>
       </c>
       <c r="AG190" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH190" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI190" s="13" t="str">
@@ -58604,18 +57365,11 @@
         <v>938</v>
       </c>
       <c r="R191" s="9" t="str">
-        <f>IF(
-  AND(
-    $A191&lt;&gt;"",
-    COUNTIF(C:C,$A191)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S191" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T191" s="13" t="str">
@@ -58738,7 +57492,7 @@
         <v>200</v>
       </c>
       <c r="AC191" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v xml:space="preserve"> (&amp;Z)</v>
       </c>
       <c r="AD191" s="13" t="str">
@@ -58772,11 +57526,11 @@
         <v/>
       </c>
       <c r="AG191" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH191" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI191" s="13" t="str">
@@ -58850,18 +57604,11 @@
         <v>938</v>
       </c>
       <c r="R192" s="9" t="str">
-        <f>IF(
-  AND(
-    $A192&lt;&gt;"",
-    COUNTIF(C:C,$A192)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S192" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T192" s="13" t="str">
@@ -58984,7 +57731,7 @@
         <v>200</v>
       </c>
       <c r="AC192" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD192" s="13" t="str">
@@ -59018,11 +57765,11 @@
         <v/>
       </c>
       <c r="AG192" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH192" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI192" s="13" t="str">
@@ -59096,18 +57843,11 @@
         <v>938</v>
       </c>
       <c r="R193" s="9" t="str">
-        <f>IF(
-  AND(
-    $A193&lt;&gt;"",
-    COUNTIF(C:C,$A193)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S193" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T193" s="13" t="str">
@@ -59230,7 +57970,7 @@
         <v>200</v>
       </c>
       <c r="AC193" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD193" s="13" t="str">
@@ -59264,11 +58004,11 @@
         <v/>
       </c>
       <c r="AG193" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH193" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI193" s="13" t="str">
@@ -59342,18 +58082,11 @@
         <v>938</v>
       </c>
       <c r="R194" s="9" t="str">
-        <f>IF(
-  AND(
-    $A194&lt;&gt;"",
-    COUNTIF(C:C,$A194)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S194" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T194" s="13" t="str">
@@ -59476,7 +58209,7 @@
         <v>200</v>
       </c>
       <c r="AC194" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD194" s="13" t="str">
@@ -59510,11 +58243,11 @@
         <v/>
       </c>
       <c r="AG194" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH194" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI194" s="13" t="str">
@@ -59588,18 +58321,11 @@
         <v>938</v>
       </c>
       <c r="R195" s="9" t="str">
-        <f>IF(
-  AND(
-    $A195&lt;&gt;"",
-    COUNTIF(C:C,$A195)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S195" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T195" s="13" t="str">
@@ -59722,7 +58448,7 @@
         <v>200</v>
       </c>
       <c r="AC195" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD195" s="13" t="str">
@@ -59756,11 +58482,11 @@
         <v/>
       </c>
       <c r="AG195" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH195" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI195" s="13" t="str">
@@ -59834,18 +58560,11 @@
         <v>39</v>
       </c>
       <c r="R196" s="9" t="str">
-        <f>IF(
-  AND(
-    $A196&lt;&gt;"",
-    COUNTIF(C:C,$A196)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S196" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T196" s="13" t="str">
@@ -59968,7 +58687,7 @@
         <v>200</v>
       </c>
       <c r="AC196" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD196" s="13" t="str">
@@ -60002,11 +58721,11 @@
         <v/>
       </c>
       <c r="AG196" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH196" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI196" s="13" t="str">
@@ -60080,18 +58799,11 @@
         <v>938</v>
       </c>
       <c r="R197" s="9" t="str">
-        <f>IF(
-  AND(
-    $A197&lt;&gt;"",
-    COUNTIF(C:C,$A197)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S197" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T197" s="13" t="str">
@@ -60214,7 +58926,7 @@
         <v>200</v>
       </c>
       <c r="AC197" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD197" s="13" t="str">
@@ -60248,11 +58960,11 @@
         <v/>
       </c>
       <c r="AG197" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH197" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI197" s="13" t="str">
@@ -60326,18 +59038,11 @@
         <v>938</v>
       </c>
       <c r="R198" s="9" t="str">
-        <f>IF(
-  AND(
-    $A198&lt;&gt;"",
-    COUNTIF(C:C,$A198)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S198" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T198" s="13" t="str">
@@ -60460,7 +59165,7 @@
         <v>200</v>
       </c>
       <c r="AC198" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD198" s="13" t="str">
@@ -60494,11 +59199,11 @@
         <v/>
       </c>
       <c r="AG198" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH198" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI198" s="13" t="str">
@@ -60572,18 +59277,11 @@
         <v>938</v>
       </c>
       <c r="R199" s="9" t="str">
-        <f>IF(
-  AND(
-    $A199&lt;&gt;"",
-    COUNTIF(C:C,$A199)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S199" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T199" s="13" t="str">
@@ -60706,7 +59404,7 @@
         <v>200</v>
       </c>
       <c r="AC199" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD199" s="13" t="str">
@@ -60740,11 +59438,11 @@
         <v/>
       </c>
       <c r="AG199" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH199" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI199" s="13" t="str">
@@ -60818,18 +59516,11 @@
         <v>938</v>
       </c>
       <c r="R200" s="9" t="str">
-        <f>IF(
-  AND(
-    $A200&lt;&gt;"",
-    COUNTIF(C:C,$A200)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S200" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T200" s="13" t="str">
@@ -60952,7 +59643,7 @@
         <v>200</v>
       </c>
       <c r="AC200" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD200" s="13" t="str">
@@ -60986,11 +59677,11 @@
         <v/>
       </c>
       <c r="AG200" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH200" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI200" s="13" t="str">
@@ -61064,18 +59755,11 @@
         <v>938</v>
       </c>
       <c r="R201" s="9" t="str">
-        <f>IF(
-  AND(
-    $A201&lt;&gt;"",
-    COUNTIF(C:C,$A201)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S201" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T201" s="13" t="str">
@@ -61198,7 +59882,7 @@
         <v>200</v>
       </c>
       <c r="AC201" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD201" s="13" t="str">
@@ -61232,11 +59916,11 @@
         <v/>
       </c>
       <c r="AG201" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH201" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI201" s="13" t="str">
@@ -61310,18 +59994,11 @@
         <v>938</v>
       </c>
       <c r="R202" s="9" t="str">
-        <f>IF(
-  AND(
-    $A202&lt;&gt;"",
-    COUNTIF(C:C,$A202)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S202" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T202" s="13" t="str">
@@ -61444,7 +60121,7 @@
         <v>200</v>
       </c>
       <c r="AC202" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD202" s="13" t="str">
@@ -61478,11 +60155,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\XF_BackupIniToTabbak.bat（X-Finder.iniタブバックアップ）.lnk</v>
       </c>
       <c r="AG202" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH202" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI202" s="13" t="str">
@@ -61556,7 +60233,7 @@
         <v>39</v>
       </c>
       <c r="R203" s="9" t="str">
-        <f>IF(
+        <f t="shared" ref="R203:R226" si="35">IF(
   AND(
     $A203&lt;&gt;"",
     COUNTIF(C:C,$A203)&gt;1
@@ -61822,18 +60499,11 @@
         <v>938</v>
       </c>
       <c r="R204" s="9" t="str">
-        <f>IF(
-  AND(
-    $A204&lt;&gt;"",
-    COUNTIF(C:C,$A204)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S204" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T204" s="13" t="str">
@@ -61956,7 +60626,7 @@
         <v>200</v>
       </c>
       <c r="AC204" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD204" s="13" t="str">
@@ -61990,11 +60660,11 @@
         <v/>
       </c>
       <c r="AG204" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH204" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI204" s="13" t="str">
@@ -62068,18 +60738,11 @@
         <v>938</v>
       </c>
       <c r="R205" s="9" t="str">
-        <f>IF(
-  AND(
-    $A205&lt;&gt;"",
-    COUNTIF(C:C,$A205)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S205" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T205" s="13" t="str">
@@ -62202,7 +60865,7 @@
         <v>200</v>
       </c>
       <c r="AC205" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD205" s="13" t="str">
@@ -62236,11 +60899,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\ScheduledBackup.bat（定期ファイルバックアップ）.lnk</v>
       </c>
       <c r="AG205" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH205" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI205" s="13" t="str">
@@ -62314,18 +60977,11 @@
         <v>938</v>
       </c>
       <c r="R206" s="9" t="str">
-        <f>IF(
-  AND(
-    $A206&lt;&gt;"",
-    COUNTIF(C:C,$A206)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S206" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T206" s="13" t="str">
@@ -62448,7 +61104,7 @@
         <v>200</v>
       </c>
       <c r="AC206" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD206" s="13" t="str">
@@ -62482,11 +61138,11 @@
         <v/>
       </c>
       <c r="AG206" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH206" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI206" s="13" t="str">
@@ -62560,18 +61216,11 @@
         <v>938</v>
       </c>
       <c r="R207" s="9" t="str">
-        <f>IF(
-  AND(
-    $A207&lt;&gt;"",
-    COUNTIF(C:C,$A207)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S207" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T207" s="13" t="str">
@@ -62694,7 +61343,7 @@
         <v>200</v>
       </c>
       <c r="AC207" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD207" s="13" t="str">
@@ -62728,11 +61377,11 @@
         <v/>
       </c>
       <c r="AG207" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH207" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI207" s="13" t="str">
@@ -62806,14 +61455,7 @@
         <v>39</v>
       </c>
       <c r="R208" s="9" t="str">
-        <f>IF(
-  AND(
-    $A208&lt;&gt;"",
-    COUNTIF(C:C,$A208)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S208" s="9" t="str">
@@ -63072,18 +61714,11 @@
         <v>938</v>
       </c>
       <c r="R209" s="9" t="str">
-        <f>IF(
-  AND(
-    $A209&lt;&gt;"",
-    COUNTIF(C:C,$A209)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S209" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T209" s="13" t="str">
@@ -63206,7 +61841,7 @@
         <v>200</v>
       </c>
       <c r="AC209" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD209" s="13" t="str">
@@ -63240,11 +61875,11 @@
         <v/>
       </c>
       <c r="AG209" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH209" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI209" s="13" t="str">
@@ -63318,14 +61953,7 @@
         <v>1451</v>
       </c>
       <c r="R210" s="9" t="str">
-        <f>IF(
-  AND(
-    $A210&lt;&gt;"",
-    COUNTIF(C:C,$A210)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S210" s="9" t="str">
@@ -63584,18 +62212,11 @@
         <v>937</v>
       </c>
       <c r="R211" s="9" t="str">
-        <f>IF(
-  AND(
-    $A211&lt;&gt;"",
-    COUNTIF(C:C,$A211)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S211" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T211" s="13" t="str">
@@ -63718,7 +62339,7 @@
         <v>200</v>
       </c>
       <c r="AC211" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v xml:space="preserve"> (&amp;R)</v>
       </c>
       <c r="AD211" s="13" t="str">
@@ -63752,11 +62373,11 @@
         <v/>
       </c>
       <c r="AG211" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH211" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI211" s="13" t="str">
@@ -63830,18 +62451,11 @@
         <v>937</v>
       </c>
       <c r="R212" s="9" t="str">
-        <f>IF(
-  AND(
-    $A212&lt;&gt;"",
-    COUNTIF(C:C,$A212)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S212" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T212" s="13" t="str">
@@ -63964,7 +62578,7 @@
         <v>200</v>
       </c>
       <c r="AC212" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD212" s="13" t="str">
@@ -63998,11 +62612,11 @@
         <v/>
       </c>
       <c r="AG212" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH212" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI212" s="13" t="str">
@@ -64076,14 +62690,7 @@
         <v>1432</v>
       </c>
       <c r="R213" s="9" t="str">
-        <f>IF(
-  AND(
-    $A213&lt;&gt;"",
-    COUNTIF(C:C,$A213)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S213" s="9" t="str">
@@ -64342,18 +62949,11 @@
         <v>39</v>
       </c>
       <c r="R214" s="9" t="str">
-        <f>IF(
-  AND(
-    $A214&lt;&gt;"",
-    COUNTIF(C:C,$A214)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S214" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T214" s="13" t="str">
@@ -64476,7 +63076,7 @@
         <v>200</v>
       </c>
       <c r="AC214" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD214" s="13" t="str">
@@ -64510,11 +63110,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\CreateProgramList.bat（インストールプログラム一覧作成）.lnk</v>
       </c>
       <c r="AG214" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH214" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI214" s="13" t="str">
@@ -64588,18 +63188,11 @@
         <v>39</v>
       </c>
       <c r="R215" s="9" t="str">
-        <f>IF(
-  AND(
-    $A215&lt;&gt;"",
-    COUNTIF(C:C,$A215)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S215" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T215" s="13" t="str">
@@ -64722,7 +63315,7 @@
         <v>200</v>
       </c>
       <c r="AC215" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD215" s="13" t="str">
@@ -64756,11 +63349,11 @@
         <v/>
       </c>
       <c r="AG215" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH215" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI215" s="13" t="str">
@@ -64834,18 +63427,11 @@
         <v>39</v>
       </c>
       <c r="R216" s="9" t="str">
-        <f>IF(
-  AND(
-    $A216&lt;&gt;"",
-    COUNTIF(C:C,$A216)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S216" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T216" s="13" t="str">
@@ -64968,7 +63554,7 @@
         <v>200</v>
       </c>
       <c r="AC216" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD216" s="13" t="str">
@@ -65002,11 +63588,11 @@
         <v/>
       </c>
       <c r="AG216" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH216" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI216" s="13" t="str">
@@ -65080,18 +63666,11 @@
         <v>39</v>
       </c>
       <c r="R217" s="9" t="str">
-        <f>IF(
-  AND(
-    $A217&lt;&gt;"",
-    COUNTIF(C:C,$A217)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S217" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T217" s="13" t="str">
@@ -65214,7 +63793,7 @@
         <v>200</v>
       </c>
       <c r="AC217" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD217" s="13" t="str">
@@ -65248,11 +63827,11 @@
         <v/>
       </c>
       <c r="AG217" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH217" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI217" s="13" t="str">
@@ -65326,18 +63905,11 @@
         <v>39</v>
       </c>
       <c r="R218" s="9" t="str">
-        <f>IF(
-  AND(
-    $A218&lt;&gt;"",
-    COUNTIF(C:C,$A218)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S218" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T218" s="13" t="str">
@@ -65460,7 +64032,7 @@
         <v>200</v>
       </c>
       <c r="AC218" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD218" s="13" t="str">
@@ -65494,11 +64066,11 @@
         <v/>
       </c>
       <c r="AG218" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH218" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI218" s="13" t="str">
@@ -65572,18 +64144,11 @@
         <v>39</v>
       </c>
       <c r="R219" s="9" t="str">
-        <f>IF(
-  AND(
-    $A219&lt;&gt;"",
-    COUNTIF(C:C,$A219)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S219" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T219" s="13" t="str">
@@ -65706,7 +64271,7 @@
         <v>200</v>
       </c>
       <c r="AC219" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD219" s="13" t="str">
@@ -65740,11 +64305,11 @@
         <v/>
       </c>
       <c r="AG219" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>schtasks /create /tn "_scheduled_backup_root" /tr "C:\codes\bat\tools\other\BackupRoot.bat" /sc daily /st 17:56 /rl highest</v>
       </c>
       <c r="AH219" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>schtasks /delete /tn "_scheduled_backup_root"</v>
       </c>
       <c r="AI219" s="13" t="str">
@@ -65818,18 +64383,11 @@
         <v>1256</v>
       </c>
       <c r="R220" s="9" t="str">
-        <f>IF(
-  AND(
-    $A220&lt;&gt;"",
-    COUNTIF(C:C,$A220)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S220" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T220" s="13" t="str">
@@ -65952,7 +64510,7 @@
         <v>200</v>
       </c>
       <c r="AC220" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD220" s="13" t="str">
@@ -65986,11 +64544,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\BackupOtherPrgSettings.bat（各種プログラム設定バックアップ）.lnk</v>
       </c>
       <c r="AG220" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH220" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI220" s="13" t="str">
@@ -66064,14 +64622,7 @@
         <v>1424</v>
       </c>
       <c r="R221" s="9" t="str">
-        <f>IF(
-  AND(
-    $A221&lt;&gt;"",
-    COUNTIF(C:C,$A221)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S221" s="9" t="str">
@@ -66330,18 +64881,11 @@
         <v>1386</v>
       </c>
       <c r="R222" s="9" t="str">
-        <f>IF(
-  AND(
-    $A222&lt;&gt;"",
-    COUNTIF(C:C,$A222)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S222" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T222" s="13" t="str">
@@ -66464,7 +65008,7 @@
         <v>200</v>
       </c>
       <c r="AC222" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD222" s="13" t="str">
@@ -66498,11 +65042,11 @@
         <v/>
       </c>
       <c r="AG222" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH222" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI222" s="13" t="str">
@@ -66542,18 +65086,11 @@
       <c r="P223" s="157"/>
       <c r="Q223" s="26"/>
       <c r="R223" s="9" t="str">
-        <f>IF(
-  AND(
-    $A223&lt;&gt;"",
-    COUNTIF(C:C,$A223)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S223" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T223" s="13" t="str">
@@ -66676,7 +65213,7 @@
         <v/>
       </c>
       <c r="AC223" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD223" s="13" t="str">
@@ -66710,11 +65247,11 @@
         <v/>
       </c>
       <c r="AG223" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH223" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI223" s="13" t="str">
@@ -66754,18 +65291,11 @@
       <c r="P224" s="157"/>
       <c r="Q224" s="26"/>
       <c r="R224" s="9" t="str">
-        <f>IF(
-  AND(
-    $A224&lt;&gt;"",
-    COUNTIF(C:C,$A224)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S224" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T224" s="13" t="str">
@@ -66888,7 +65418,7 @@
         <v/>
       </c>
       <c r="AC224" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD224" s="13" t="str">
@@ -66922,11 +65452,11 @@
         <v/>
       </c>
       <c r="AG224" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH224" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI224" s="13" t="str">
@@ -66966,18 +65496,11 @@
       <c r="P225" s="157"/>
       <c r="Q225" s="26"/>
       <c r="R225" s="9" t="str">
-        <f>IF(
-  AND(
-    $A225&lt;&gt;"",
-    COUNTIF(C:C,$A225)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S225" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T225" s="13" t="str">
@@ -67100,7 +65623,7 @@
         <v/>
       </c>
       <c r="AC225" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD225" s="13" t="str">
@@ -67134,11 +65657,11 @@
         <v/>
       </c>
       <c r="AG225" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH225" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI225" s="13" t="str">
@@ -67178,18 +65701,11 @@
       <c r="P226" s="157"/>
       <c r="Q226" s="26"/>
       <c r="R226" s="9" t="str">
-        <f>IF(
-  AND(
-    $A226&lt;&gt;"",
-    COUNTIF(C:C,$A226)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S226" s="9" t="str">
-        <f t="shared" ref="S226" si="32">IF(
+        <f t="shared" ref="S226" si="36">IF(
   OR(
     $H226="",
     $H226="-",
@@ -67320,7 +65836,7 @@
         <v/>
       </c>
       <c r="AC226" s="20" t="str">
-        <f t="shared" ref="AC226" si="33">IF(AND($M226&lt;&gt;"",$M226&lt;&gt;"-")," (&amp;"&amp;$M226&amp;")","")</f>
+        <f t="shared" ref="AC226" si="37">IF(AND($M226&lt;&gt;"",$M226&lt;&gt;"-")," (&amp;"&amp;$M226&amp;")","")</f>
         <v/>
       </c>
       <c r="AD226" s="13" t="str">
@@ -67354,7 +65870,7 @@
         <v/>
       </c>
       <c r="AG226" s="13" t="str">
-        <f t="shared" ref="AG226" si="34">IF(
+        <f t="shared" ref="AG226" si="38">IF(
   AND($A226&lt;&gt;"",$O226&lt;&gt;"-",$O226&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O226&amp;""" /tr """&amp;$C226&amp;""" /sc daily /st "&amp;$P226&amp;" /rl highest"
@@ -67364,7 +65880,7 @@
         <v/>
       </c>
       <c r="AH226" s="13" t="str">
-        <f t="shared" ref="AH226" si="35">IF(
+        <f t="shared" ref="AH226" si="39">IF(
   AND($A226&lt;&gt;"",$O226&lt;&gt;"-",$O226&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O226&amp;""""
@@ -67484,7 +66000,7 @@
         <v>938</v>
       </c>
       <c r="R229" s="9" t="str">
-        <f>IF(
+        <f t="shared" ref="R229:R234" si="40">IF(
   AND(
     $A229&lt;&gt;"",
     COUNTIF(C:C,$A229)&gt;1
@@ -67495,7 +66011,7 @@
         <v/>
       </c>
       <c r="S229" s="9" t="str">
-        <f t="shared" ref="S229:S234" si="36">IF(
+        <f t="shared" ref="S229:S234" si="41">IF(
   OR(
     $H229="",
     $H229="-",
@@ -67626,7 +66142,7 @@
         <v>153</v>
       </c>
       <c r="AC229" s="20" t="str">
-        <f t="shared" ref="AC229:AC234" si="37">IF(AND($M229&lt;&gt;"",$M229&lt;&gt;"-")," (&amp;"&amp;$M229&amp;")","")</f>
+        <f t="shared" ref="AC229:AC234" si="42">IF(AND($M229&lt;&gt;"",$M229&lt;&gt;"-")," (&amp;"&amp;$M229&amp;")","")</f>
         <v/>
       </c>
       <c r="AD229" s="13" t="str">
@@ -67660,7 +66176,7 @@
         <v/>
       </c>
       <c r="AG229" s="13" t="str">
-        <f t="shared" ref="AG229:AG234" si="38">IF(
+        <f t="shared" ref="AG229:AG234" si="43">IF(
   AND($A229&lt;&gt;"",$O229&lt;&gt;"-",$O229&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O229&amp;""" /tr """&amp;$C229&amp;""" /sc daily /st "&amp;$P229&amp;" /rl highest"
@@ -67670,7 +66186,7 @@
         <v/>
       </c>
       <c r="AH229" s="13" t="str">
-        <f t="shared" ref="AH229:AH234" si="39">IF(
+        <f t="shared" ref="AH229:AH234" si="44">IF(
   AND($A229&lt;&gt;"",$O229&lt;&gt;"-",$O229&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O229&amp;""""
@@ -67750,18 +66266,11 @@
         <v>938</v>
       </c>
       <c r="R230" s="9" t="str">
-        <f>IF(
-  AND(
-    $A230&lt;&gt;"",
-    COUNTIF(C:C,$A230)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="S230" s="9" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="T230" s="13" t="str">
@@ -67884,7 +66393,7 @@
         <v>161</v>
       </c>
       <c r="AC230" s="20" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AD230" s="13" t="str">
@@ -67918,11 +66427,11 @@
         <v/>
       </c>
       <c r="AG230" s="13" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AH230" s="13" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AI230" s="13" t="str">
@@ -67996,18 +66505,11 @@
         <v>39</v>
       </c>
       <c r="R231" s="9" t="str">
-        <f>IF(
-  AND(
-    $A231&lt;&gt;"",
-    COUNTIF(C:C,$A231)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="S231" s="9" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="T231" s="13" t="str">
@@ -68130,7 +66632,7 @@
         <v>172</v>
       </c>
       <c r="AC231" s="20" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AD231" s="13" t="str">
@@ -68164,11 +66666,11 @@
         <v/>
       </c>
       <c r="AG231" s="13" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AH231" s="13" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AI231" s="13" t="str">
@@ -68242,18 +66744,11 @@
         <v>938</v>
       </c>
       <c r="R232" s="9" t="str">
-        <f>IF(
-  AND(
-    $A232&lt;&gt;"",
-    COUNTIF(C:C,$A232)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="S232" s="9" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="T232" s="13" t="str">
@@ -68376,7 +66871,7 @@
         <v>143</v>
       </c>
       <c r="AC232" s="20" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AD232" s="13" t="str">
@@ -68410,11 +66905,11 @@
         <v/>
       </c>
       <c r="AG232" s="13" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AH232" s="13" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AI232" s="13" t="str">
@@ -68488,18 +66983,11 @@
         <v>938</v>
       </c>
       <c r="R233" s="9" t="str">
-        <f>IF(
-  AND(
-    $A233&lt;&gt;"",
-    COUNTIF(C:C,$A233)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="S233" s="9" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="T233" s="13" t="str">
@@ -68622,7 +67110,7 @@
         <v>162</v>
       </c>
       <c r="AC233" s="20" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AD233" s="13" t="str">
@@ -68656,11 +67144,11 @@
         <v/>
       </c>
       <c r="AG233" s="13" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AH233" s="13" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AI233" s="13" t="str">
@@ -68734,18 +67222,11 @@
         <v>39</v>
       </c>
       <c r="R234" s="9" t="str">
-        <f>IF(
-  AND(
-    $A234&lt;&gt;"",
-    COUNTIF(C:C,$A234)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="S234" s="9" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="T234" s="13" t="str">
@@ -68868,7 +67349,7 @@
         <v>161</v>
       </c>
       <c r="AC234" s="20" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AD234" s="13" t="str">
@@ -68902,11 +67383,11 @@
         <v/>
       </c>
       <c r="AG234" s="13" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AH234" s="13" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AI234" s="13" t="str">

--- a/PC移行時チェックリスト.xlsx
+++ b/PC移行時チェックリスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F01687A-D9EF-4AA0-860B-F80D91783400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F179486-39F2-4EE0-8364-DB41D2151382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28815" yWindow="-5580" windowWidth="38385" windowHeight="41970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28815" yWindow="-5580" windowWidth="38385" windowHeight="41970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="セットアップ事項" sheetId="21" r:id="rId1"/>
@@ -35,12 +35,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">linux環境構築!#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">shortcut!$A$9:$AJ$227</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">symlink!$A$11:$L$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">セットアップ事項!$A$2:$M$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">セットアップ事項!$A$2:$M$83</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">linux環境構築!$A$6:$H$102</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">shortcut!$A$8:$AI$227</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">shortcut設定!$A$1:$O$38</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">symlink!$A$10:$L$66</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">セットアップ事項!$A$1:$H$82</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">セットアップ事項!$A$1:$H$83</definedName>
     <definedName name="カテゴリ" localSheetId="7">[1]shortcut設定!$F$13:$F$37</definedName>
     <definedName name="カテゴリ">shortcut設定!$F$13:$F$37</definedName>
   </definedNames>
@@ -757,7 +757,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6367" uniqueCount="1543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6374" uniqueCount="1545">
   <si>
     <t>○</t>
   </si>
@@ -8102,6 +8102,35 @@
   </si>
   <si>
     <t>https://github.com/draemonash2/repos.git</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>不要なアイコンオーバーレイ無効化＠ShellExView</t>
+    <rPh sb="0" eb="2">
+      <t>フヨウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ムコウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アイコンオーバーレイは15個以上は設定できないため、不要なソフトのオーバーレイはShellExViewで無効化する</t>
+    <rPh sb="13" eb="14">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>フヨウ</t>
+    </rPh>
+    <rPh sb="52" eb="55">
+      <t>ムコウカ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -9757,7 +9786,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="28.33203125" style="101" bestFit="1" customWidth="1"/>
@@ -11763,7 +11792,7 @@
     </row>
     <row r="76" spans="1:13" s="104" customFormat="1">
       <c r="A76" s="113" t="s">
-        <v>1359</v>
+        <v>146</v>
       </c>
       <c r="B76" s="114" t="s">
         <v>149</v>
@@ -11772,14 +11801,16 @@
         <v>0</v>
       </c>
       <c r="D76" s="116" t="s">
-        <v>1344</v>
+        <v>1543</v>
       </c>
       <c r="E76" s="142" t="s">
         <v>937</v>
       </c>
       <c r="F76" s="143"/>
       <c r="G76" s="117"/>
-      <c r="H76" s="117"/>
+      <c r="H76" s="171" t="s">
+        <v>1544</v>
+      </c>
       <c r="I76" s="104" t="s">
         <v>28</v>
       </c>
@@ -11793,13 +11824,13 @@
         <v>1359</v>
       </c>
       <c r="B77" s="114" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="C77" s="115" t="s">
         <v>0</v>
       </c>
       <c r="D77" s="116" t="s">
-        <v>1358</v>
+        <v>1344</v>
       </c>
       <c r="E77" s="142" t="s">
         <v>937</v>
@@ -11826,7 +11857,7 @@
         <v>0</v>
       </c>
       <c r="D78" s="116" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="E78" s="142" t="s">
         <v>937</v>
@@ -11842,53 +11873,63 @@
       <c r="L78" s="103"/>
       <c r="M78" s="103"/>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" s="104" customFormat="1">
       <c r="A79" s="113" t="s">
         <v>1359</v>
       </c>
       <c r="B79" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="C79" s="115" t="s">
         <v>0</v>
       </c>
-      <c r="C79" s="115" t="s">
-        <v>149</v>
-      </c>
       <c r="D79" s="116" t="s">
-        <v>983</v>
+        <v>1360</v>
       </c>
       <c r="E79" s="142" t="s">
         <v>937</v>
       </c>
       <c r="F79" s="143"/>
       <c r="G79" s="117"/>
-      <c r="H79" s="117" t="s">
-        <v>988</v>
-      </c>
+      <c r="H79" s="117"/>
       <c r="I79" s="104" t="s">
         <v>28</v>
       </c>
+      <c r="J79" s="103"/>
+      <c r="K79" s="103"/>
+      <c r="L79" s="103"/>
+      <c r="M79" s="103"/>
     </row>
-    <row r="80" spans="1:13" s="104" customFormat="1">
-      <c r="A80" s="113"/>
-      <c r="B80" s="114"/>
-      <c r="C80" s="115"/>
-      <c r="D80" s="116"/>
-      <c r="E80" s="142"/>
+    <row r="80" spans="1:13">
+      <c r="A80" s="113" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B80" s="114" t="s">
+        <v>0</v>
+      </c>
+      <c r="C80" s="115" t="s">
+        <v>149</v>
+      </c>
+      <c r="D80" s="116" t="s">
+        <v>983</v>
+      </c>
+      <c r="E80" s="142" t="s">
+        <v>937</v>
+      </c>
       <c r="F80" s="143"/>
       <c r="G80" s="117"/>
-      <c r="H80" s="117"/>
+      <c r="H80" s="117" t="s">
+        <v>988</v>
+      </c>
       <c r="I80" s="104" t="s">
         <v>28</v>
       </c>
-      <c r="J80" s="103"/>
-      <c r="K80" s="103"/>
-      <c r="L80" s="103"/>
-      <c r="M80" s="103"/>
     </row>
     <row r="81" spans="1:13" s="104" customFormat="1">
-      <c r="A81" s="127"/>
-      <c r="B81" s="128"/>
-      <c r="C81" s="129"/>
-      <c r="D81" s="130"/>
+      <c r="A81" s="113"/>
+      <c r="B81" s="114"/>
+      <c r="C81" s="115"/>
+      <c r="D81" s="116"/>
       <c r="E81" s="142"/>
       <c r="F81" s="143"/>
       <c r="G81" s="117"/>
@@ -11901,46 +11942,63 @@
       <c r="L81" s="103"/>
       <c r="M81" s="103"/>
     </row>
-    <row r="82" spans="1:13" ht="1.5" customHeight="1">
-      <c r="A82" s="108" t="s">
+    <row r="82" spans="1:13" s="104" customFormat="1">
+      <c r="A82" s="127"/>
+      <c r="B82" s="128"/>
+      <c r="C82" s="129"/>
+      <c r="D82" s="130"/>
+      <c r="E82" s="142"/>
+      <c r="F82" s="143"/>
+      <c r="G82" s="117"/>
+      <c r="H82" s="117"/>
+      <c r="I82" s="104" t="s">
         <v>28</v>
       </c>
-      <c r="B82" s="109" t="s">
+      <c r="J82" s="103"/>
+      <c r="K82" s="103"/>
+      <c r="L82" s="103"/>
+      <c r="M82" s="103"/>
+    </row>
+    <row r="83" spans="1:13" ht="1.5" customHeight="1">
+      <c r="A83" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="C82" s="109" t="s">
+      <c r="B83" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="D82" s="110" t="s">
+      <c r="C83" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="E82" s="110"/>
-      <c r="F82" s="110" t="s">
+      <c r="D83" s="110" t="s">
         <v>28</v>
       </c>
-      <c r="G82" s="110" t="s">
+      <c r="E83" s="110"/>
+      <c r="F83" s="110" t="s">
         <v>28</v>
       </c>
-      <c r="H82" s="109" t="s">
+      <c r="G83" s="110" t="s">
         <v>28</v>
       </c>
-      <c r="I82" s="103" t="s">
+      <c r="H83" s="109" t="s">
+        <v>28</v>
+      </c>
+      <c r="I83" s="103" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M82" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:M83" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="E3:F82">
+  <conditionalFormatting sqref="E3:F83">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>E3="-"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:F81" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:F82" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"★,○,-"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:C81" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:C82" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"○,×"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11960,13 +12018,14 @@
     <hyperlink ref="D69" r:id="rId13" display="SD Zドライブ化" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
     <hyperlink ref="D50" r:id="rId14" xr:uid="{57866A10-A79A-4E50-985C-5260837DD435}"/>
     <hyperlink ref="G5" r:id="rId15" display="https://github.com/draemonash2/codes/archive/master.zip" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="H76" r:id="rId16" xr:uid="{08566955-7B50-448B-B66D-93E080703859}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="35" orientation="portrait" r:id="rId16"/>
+  <pageSetup paperSize="9" scale="35" orientation="portrait" r:id="rId17"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="8" max="76" man="1"/>
   </colBreaks>
-  <legacyDrawing r:id="rId17"/>
+  <legacyDrawing r:id="rId18"/>
 </worksheet>
 </file>
 
